--- a/docs/reports/內在價值報告_20260911.xlsx
+++ b/docs/reports/內在價值報告_20260911.xlsx
@@ -829,25 +829,25 @@
       </c>
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="4" t="n">
-        <v>3.545</v>
+        <v>3.33</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>13.2423</v>
+        <v>13.2428</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>6.861</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>11.2315</v>
+        <v>11.2318</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>-73.2</v>
+        <v>-74.90000000000001</v>
       </c>
       <c r="M2" s="5" t="n">
         <v>25</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>9.931699999999999</v>
+        <v>9.9321</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
       </c>
       <c r="AE2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF2" s="3" t="inlineStr">
@@ -1073,10 +1073,10 @@
       </c>
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="4" t="n">
-        <v>38.29</v>
+        <v>38.8</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>142.5437</v>
+        <v>142.5145</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>55.8024</v>
@@ -1085,13 +1085,13 @@
         <v>151.0522</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>-73.09999999999999</v>
+        <v>-72.8</v>
       </c>
       <c r="M4" s="5" t="n">
         <v>25</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>106.9078</v>
+        <v>106.8858</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="AE4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr"/>
@@ -1191,25 +1191,25 @@
       </c>
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="4" t="n">
-        <v>1.395</v>
+        <v>1.315</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>3.7982</v>
+        <v>3.8007</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>2.2063</v>
+        <v>2.2071</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>2.9007</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>-63.3</v>
+        <v>-65.40000000000001</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>25</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>2.8486</v>
+        <v>2.8506</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="AE5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF5" s="3" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="4" t="n">
-        <v>18.9</v>
+        <v>18.68</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>53.4079</v>
@@ -1325,7 +1325,7 @@
         <v>62.7</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>-64.59999999999999</v>
+        <v>-65</v>
       </c>
       <c r="M6" s="5" t="n">
         <v>25</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF6" s="3" t="inlineStr"/>
@@ -1431,10 +1431,10 @@
       </c>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="4" t="n">
-        <v>10.35</v>
+        <v>10.07</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>22.5194</v>
+        <v>22.5292</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>12.6307</v>
@@ -1443,13 +1443,13 @@
         <v>15.4965</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>-54</v>
+        <v>-55.3</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>25</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>16.8895</v>
+        <v>16.8969</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="AE7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF7" s="3" t="inlineStr">
@@ -1553,25 +1553,25 @@
       </c>
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="4" t="n">
-        <v>25.86</v>
+        <v>24.88</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>71.7223</v>
+        <v>71.7325</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>41.3289</v>
+        <v>41.3341</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>67.77670000000001</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>-63.9</v>
+        <v>-65.3</v>
       </c>
       <c r="M8" s="5" t="n">
         <v>25</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>53.7918</v>
+        <v>53.7994</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="AE8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF8" s="3" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="4" t="n">
-        <v>51.9</v>
+        <v>51.65</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>588.5381</v>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="AE9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="4" t="n">
-        <v>9.56</v>
+        <v>9.734999999999999</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>130.7854</v>
@@ -1807,7 +1807,7 @@
         <v>20.1692</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>-92.7</v>
+        <v>-92.59999999999999</v>
       </c>
       <c r="M10" s="5" t="n">
         <v>25</v>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="AE10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="4" t="n">
-        <v>7.51</v>
+        <v>7.565</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>98.4873</v>
@@ -1927,7 +1927,7 @@
         <v>13.1093</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>-92.40000000000001</v>
+        <v>-92.3</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>25</v>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="AE11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="4" t="n">
-        <v>55.25</v>
+        <v>53.5</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>699.6943</v>
@@ -2291,7 +2291,7 @@
         <v>136.5623</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>-92.09999999999999</v>
+        <v>-92.40000000000001</v>
       </c>
       <c r="M14" s="5" t="n">
         <v>25</v>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AE14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
@@ -2399,25 +2399,25 @@
       </c>
       <c r="G15" s="8" t="inlineStr"/>
       <c r="H15" s="9" t="n">
-        <v>61.96</v>
+        <v>57.6</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>100.9205</v>
+        <v>100.9378</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>56.3433</v>
+        <v>56.4344</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>94.1225</v>
       </c>
       <c r="L15" s="10" t="n">
-        <v>-38.6</v>
+        <v>-42.9</v>
       </c>
       <c r="M15" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>75.6904</v>
+        <v>75.7033</v>
       </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="AE15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF15" s="8" t="inlineStr"/>
@@ -2491,17 +2491,17 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>605117</t>
+          <t>03998</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>德业股份</t>
+          <t>波司登</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr"/>
@@ -2512,30 +2512,30 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>HKD</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr"/>
       <c r="H16" s="9" t="n">
-        <v>81.33</v>
+        <v>4.35</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>113.1392</v>
+        <v>8.3026</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>55.5052</v>
+        <v>3.8731</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>108.9394</v>
+        <v>7.0633</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>-28.1</v>
+        <v>-47.6</v>
       </c>
       <c r="M16" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>84.8544</v>
+        <v>6.2269</v>
       </c>
       <c r="O16" s="7" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="R16" s="7" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
@@ -2561,52 +2561,52 @@
         </is>
       </c>
       <c r="T16" s="7" t="n">
-        <v>8.9</v>
+        <v>8</v>
       </c>
       <c r="U16" s="7" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="V16" s="7" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="W16" s="7" t="n">
-        <v>91.5</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="X16" s="8" t="inlineStr">
         <is>
-          <t>ROE中位35.87%、毛利率38.04%、負債權益比0.175924（規則式）</t>
+          <t>高毛利57.22%、ROIC 28.22%穩定成長，現金流強勁，資產負債健康。</t>
         </is>
       </c>
       <c r="Y16" s="10" t="n">
-        <v>38</v>
+        <v>21.9</v>
       </c>
       <c r="Z16" s="10" t="n">
-        <v>58.5</v>
+        <v>28.2</v>
       </c>
       <c r="AA16" s="10" t="n">
-        <v>38</v>
+        <v>57.2</v>
       </c>
       <c r="AB16" s="10" t="n">
-        <v>53.9</v>
+        <v>37.5</v>
       </c>
       <c r="AC16" s="7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AD16" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AE16" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF16" s="8" t="inlineStr">
         <is>
-          <t>行情總股本(1,273,282,072)與財報EPS反推(902,750,991)差異&gt;25%，已改用反推值</t>
+          <t>報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
         </is>
       </c>
     </row>
@@ -2618,18 +2618,18 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>03998</t>
+          <t>00700</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>波司登</t>
+          <t>腾讯控股</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr"/>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>growth</t>
+          <t>mature</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -2639,25 +2639,25 @@
       </c>
       <c r="G17" s="8" t="inlineStr"/>
       <c r="H17" s="9" t="n">
-        <v>4.48</v>
+        <v>429.4</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>8.302</v>
+        <v>659.8955</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>3.8731</v>
+        <v>459.3594</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>7.0629</v>
+        <v>609.7471</v>
       </c>
       <c r="L17" s="10" t="n">
-        <v>-46</v>
+        <v>-34.9</v>
       </c>
       <c r="M17" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>6.2265</v>
+        <v>494.9216</v>
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="R17" s="7" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="T17" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U17" s="7" t="n">
         <v>9</v>
@@ -2692,38 +2692,38 @@
         <v>8.5</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>93.09999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="X17" s="8" t="inlineStr">
         <is>
-          <t>高毛利57.22%、ROIC 28.22%穩定成長，現金流強勁，資產負債健康。</t>
+          <t>ROE中位22.71%穩，ROIC 18.73%，自由現金流率24.83%，負債比0.415</t>
         </is>
       </c>
       <c r="Y17" s="10" t="n">
-        <v>21.9</v>
+        <v>20.7</v>
       </c>
       <c r="Z17" s="10" t="n">
-        <v>28.2</v>
+        <v>18.7</v>
       </c>
       <c r="AA17" s="10" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="AB17" s="10" t="n">
-        <v>37.5</v>
+        <v>43.4</v>
       </c>
       <c r="AC17" s="7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="AD17" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AE17" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF17" s="8" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>00700</t>
+          <t>02688</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>腾讯控股</t>
+          <t>新奥能源</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr"/>
@@ -2761,25 +2761,25 @@
       </c>
       <c r="G18" s="8" t="inlineStr"/>
       <c r="H18" s="9" t="n">
-        <v>435.4</v>
+        <v>50.05</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>659.8262999999999</v>
+        <v>84.1289</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>459.3317</v>
+        <v>83.2593</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>609.7472</v>
+        <v>106.0289</v>
       </c>
       <c r="L18" s="10" t="n">
-        <v>-34</v>
+        <v>-40.5</v>
       </c>
       <c r="M18" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>494.8698</v>
+        <v>63.0967</v>
       </c>
       <c r="O18" s="7" t="inlineStr">
         <is>
@@ -2808,30 +2808,30 @@
         <v>7</v>
       </c>
       <c r="U18" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="V18" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="V18" s="7" t="n">
-        <v>8.5</v>
-      </c>
       <c r="W18" s="7" t="n">
-        <v>95.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="X18" s="8" t="inlineStr">
         <is>
-          <t>ROE中位22.71%穩，ROIC 18.73%，自由現金流率24.83%，負債比0.415</t>
+          <t>ROE穩定10年獲利，自由現金流健康，但流動比率偏低。</t>
         </is>
       </c>
       <c r="Y18" s="10" t="n">
-        <v>20.7</v>
+        <v>12.8</v>
       </c>
       <c r="Z18" s="10" t="n">
-        <v>18.7</v>
+        <v>11.4</v>
       </c>
       <c r="AA18" s="10" t="n">
-        <v>57.4</v>
+        <v>11.9</v>
       </c>
       <c r="AB18" s="10" t="n">
-        <v>43.4</v>
+        <v>48.6</v>
       </c>
       <c r="AC18" s="7" t="inlineStr">
         <is>
@@ -2845,12 +2845,12 @@
       </c>
       <c r="AE18" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF18" s="8" t="inlineStr">
         <is>
-          <t>報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
+          <t>缺關鍵科目：d_and_a / 報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
         </is>
       </c>
     </row>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>02688</t>
+          <t>09999</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>新奥能源</t>
+          <t>网易</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr"/>
@@ -2883,25 +2883,25 @@
       </c>
       <c r="G19" s="8" t="inlineStr"/>
       <c r="H19" s="9" t="n">
-        <v>51.4</v>
+        <v>182</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>84.0279</v>
+        <v>300.1444</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>83.2593</v>
+        <v>153.404</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>106.0289</v>
+        <v>378.6999</v>
       </c>
       <c r="L19" s="10" t="n">
-        <v>-38.8</v>
+        <v>-39.4</v>
       </c>
       <c r="M19" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>63.0209</v>
+        <v>225.1083</v>
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
@@ -2927,33 +2927,33 @@
         </is>
       </c>
       <c r="T19" s="7" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="U19" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V19" s="7" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W19" s="7" t="n">
-        <v>93</v>
+        <v>84.8</v>
       </c>
       <c r="X19" s="8" t="inlineStr">
         <is>
-          <t>ROE穩定10年獲利，自由現金流健康，但流動比率偏低。</t>
+          <t>高毛利率67.15%、ROE中位21.06%、淨現金162788.7百萬，財務極穩健。</t>
         </is>
       </c>
       <c r="Y19" s="10" t="n">
-        <v>12.8</v>
+        <v>19.5</v>
       </c>
       <c r="Z19" s="10" t="n">
-        <v>11.4</v>
+        <v>777.9</v>
       </c>
       <c r="AA19" s="10" t="n">
-        <v>11.9</v>
+        <v>67.2</v>
       </c>
       <c r="AB19" s="10" t="n">
-        <v>48.6</v>
+        <v>26.1</v>
       </c>
       <c r="AC19" s="7" t="inlineStr">
         <is>
@@ -2967,63 +2967,63 @@
       </c>
       <c r="AE19" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF19" s="8" t="inlineStr">
         <is>
-          <t>缺關鍵科目：d_and_a / 報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
+          <t>報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>09999</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>网易</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr"/>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>mature</t>
+          <t>growth</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>HKD</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr"/>
       <c r="H20" s="9" t="n">
-        <v>188.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>300.133</v>
+        <v>126.3713</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>153.3541</v>
+        <v>67.5265</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>378.6999</v>
+        <v>166.782</v>
       </c>
       <c r="L20" s="10" t="n">
-        <v>-37.3</v>
+        <v>-32.8</v>
       </c>
       <c r="M20" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>225.0998</v>
+        <v>94.77849999999999</v>
       </c>
       <c r="O20" s="7" t="inlineStr">
         <is>
@@ -3049,33 +3049,33 @@
         </is>
       </c>
       <c r="T20" s="7" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="U20" s="7" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="V20" s="7" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W20" s="7" t="n">
-        <v>84.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="X20" s="8" t="inlineStr">
         <is>
-          <t>高毛利率67.15%、ROE中位21.06%、淨現金162788.7百萬，財務極穩健。</t>
+          <t>ROIC達41.11%，經營現金流強勁，淨現金23674.1百萬，但流動比率1.64偏低。</t>
         </is>
       </c>
       <c r="Y20" s="10" t="n">
-        <v>19.5</v>
+        <v>21.7</v>
       </c>
       <c r="Z20" s="10" t="n">
-        <v>777.9</v>
+        <v>41.1</v>
       </c>
       <c r="AA20" s="10" t="n">
-        <v>67.2</v>
+        <v>32</v>
       </c>
       <c r="AB20" s="10" t="n">
-        <v>26.1</v>
+        <v>58.2</v>
       </c>
       <c r="AC20" s="7" t="inlineStr">
         <is>
@@ -3089,63 +3089,59 @@
       </c>
       <c r="AE20" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AF20" s="8" t="inlineStr">
-        <is>
-          <t>報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
-        </is>
-      </c>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AF20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>00762</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>中国联通</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr"/>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>growth</t>
+          <t>mature</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>HKD</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr"/>
       <c r="H21" s="9" t="n">
-        <v>87.84999999999999</v>
+        <v>5.815</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>126.3602</v>
+        <v>11.4619</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>67.4669</v>
+        <v>8.3786</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>166.782</v>
+        <v>12.385</v>
       </c>
       <c r="L21" s="10" t="n">
-        <v>-30.5</v>
+        <v>-49.3</v>
       </c>
       <c r="M21" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>94.7702</v>
+        <v>8.596399999999999</v>
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
@@ -3163,7 +3159,7 @@
         </is>
       </c>
       <c r="R21" s="7" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
@@ -3174,30 +3170,30 @@
         <v>7</v>
       </c>
       <c r="U21" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="V21" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="V21" s="7" t="n">
-        <v>8</v>
-      </c>
       <c r="W21" s="7" t="n">
-        <v>85.90000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="X21" s="8" t="inlineStr">
         <is>
-          <t>ROIC達41.11%，經營現金流強勁，淨現金23674.1百萬，但流動比率1.64偏低。</t>
+          <t>獲利穩定十年，ROE僅4.23%，流動比率0.70偏低，自由現金流率5.73%健康</t>
         </is>
       </c>
       <c r="Y21" s="10" t="n">
-        <v>21.7</v>
+        <v>4.2</v>
       </c>
       <c r="Z21" s="10" t="n">
-        <v>41.1</v>
+        <v>3.4</v>
       </c>
       <c r="AA21" s="10" t="n">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="AB21" s="10" t="n">
-        <v>58.2</v>
+        <v>44.4</v>
       </c>
       <c r="AC21" s="7" t="inlineStr">
         <is>
@@ -3211,10 +3207,14 @@
       </c>
       <c r="AE21" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AF21" s="8" t="inlineStr"/>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AF21" s="8" t="inlineStr">
+        <is>
+          <t>報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -3224,12 +3224,12 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>00762</t>
+          <t>09961</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>中国联通</t>
+          <t>携程集团-S</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr"/>
@@ -3245,25 +3245,25 @@
       </c>
       <c r="G22" s="8" t="inlineStr"/>
       <c r="H22" s="9" t="n">
-        <v>5.735</v>
+        <v>304.8</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>11.4648</v>
+        <v>430.9274</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>8.379</v>
+        <v>252.0972</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>12.385</v>
+        <v>428.4491</v>
       </c>
       <c r="L22" s="10" t="n">
-        <v>-50</v>
+        <v>-29.3</v>
       </c>
       <c r="M22" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>8.598599999999999</v>
+        <v>323.1955</v>
       </c>
       <c r="O22" s="7" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="Q22" s="7" t="inlineStr">
         <is>
-          <t>便宜</t>
+          <t>合理</t>
         </is>
       </c>
       <c r="R22" s="7" t="n">
@@ -3289,33 +3289,33 @@
         </is>
       </c>
       <c r="T22" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U22" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V22" s="7" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W22" s="7" t="n">
-        <v>93.7</v>
+        <v>89.2</v>
       </c>
       <c r="X22" s="8" t="inlineStr">
         <is>
-          <t>獲利穩定十年，ROE僅4.23%，流動比率0.70偏低，自由現金流率5.73%健康</t>
+          <t>毛利率89.71%、淨現金496億，ROIC 11.73% ROE不穩</t>
         </is>
       </c>
       <c r="Y22" s="10" t="n">
-        <v>4.2</v>
+        <v>19.1</v>
       </c>
       <c r="Z22" s="10" t="n">
-        <v>3.4</v>
+        <v>11.7</v>
       </c>
       <c r="AA22" s="10" t="n">
-        <v>69</v>
+        <v>89.7</v>
       </c>
       <c r="AB22" s="10" t="n">
-        <v>44.4</v>
+        <v>36.7</v>
       </c>
       <c r="AC22" s="7" t="inlineStr">
         <is>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="AD22" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AE22" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF22" s="8" t="inlineStr">
@@ -3367,25 +3367,25 @@
       </c>
       <c r="G23" s="8" t="inlineStr"/>
       <c r="H23" s="9" t="n">
-        <v>4.915</v>
+        <v>4.795</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>9.1204</v>
+        <v>9.1286</v>
       </c>
       <c r="J23" s="9" t="n">
         <v>3.1723</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>5.6021</v>
+        <v>5.6134</v>
       </c>
       <c r="L23" s="10" t="n">
-        <v>-46.1</v>
+        <v>-47.5</v>
       </c>
       <c r="M23" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>6.8403</v>
+        <v>6.8465</v>
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>5</v>
       </c>
       <c r="W23" s="7" t="n">
-        <v>93.09999999999999</v>
+        <v>93</v>
       </c>
       <c r="X23" s="8" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="AE23" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF23" s="8" t="inlineStr">
@@ -3590,18 +3590,18 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>300760</t>
+          <t>605117</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>迈瑞医疗</t>
+          <t>德业股份</t>
         </is>
       </c>
       <c r="D25" s="13" t="inlineStr"/>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>mature</t>
+          <t>growth</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -3611,25 +3611,25 @@
       </c>
       <c r="G25" s="13" t="inlineStr"/>
       <c r="H25" s="14" t="n">
-        <v>169.95</v>
+        <v>84.91</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>200.2999</v>
+        <v>113.1304</v>
       </c>
       <c r="J25" s="14" t="n">
-        <v>116.6235</v>
+        <v>55.5052</v>
       </c>
       <c r="K25" s="14" t="n">
-        <v>176.872</v>
+        <v>108.9336</v>
       </c>
       <c r="L25" s="15" t="n">
-        <v>-15.2</v>
+        <v>-24.9</v>
       </c>
       <c r="M25" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>150.2249</v>
+        <v>84.84780000000001</v>
       </c>
       <c r="O25" s="12" t="inlineStr">
         <is>
@@ -3643,11 +3643,11 @@
       </c>
       <c r="Q25" s="12" t="inlineStr">
         <is>
-          <t>合理</t>
+          <t>便宜</t>
         </is>
       </c>
       <c r="R25" s="12" t="n">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="S25" s="12" t="inlineStr">
         <is>
@@ -3655,33 +3655,33 @@
         </is>
       </c>
       <c r="T25" s="12" t="n">
-        <v>6</v>
+        <v>8.9</v>
       </c>
       <c r="U25" s="12" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>7.5</v>
+        <v>8.9</v>
       </c>
       <c r="W25" s="12" t="n">
-        <v>94.59999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="X25" s="13" t="inlineStr">
         <is>
-          <t>高毛利59.92%、ROIC 37.79%穩健，現金流強勁，但營收成長放緩至3.1%。</t>
+          <t>ROE中位35.87%、毛利率38.04%、負債權益比0.175924（規則式）</t>
         </is>
       </c>
       <c r="Y25" s="15" t="n">
-        <v>20.4</v>
+        <v>38</v>
       </c>
       <c r="Z25" s="15" t="n">
-        <v>37.8</v>
+        <v>58.5</v>
       </c>
       <c r="AA25" s="15" t="n">
-        <v>59.9</v>
+        <v>38</v>
       </c>
       <c r="AB25" s="15" t="n">
-        <v>25.5</v>
+        <v>53.9</v>
       </c>
       <c r="AC25" s="12" t="inlineStr">
         <is>
@@ -3695,10 +3695,14 @@
       </c>
       <c r="AE25" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AF25" s="13" t="inlineStr"/>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AF25" s="13" t="inlineStr">
+        <is>
+          <t>行情總股本(1,273,282,072)與財報EPS反推(902,750,991)差異&gt;25%，已改用反推值</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
@@ -3708,12 +3712,12 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>300760</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>迈瑞医疗</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr"/>
@@ -3729,25 +3733,25 @@
       </c>
       <c r="G26" s="13" t="inlineStr"/>
       <c r="H26" s="14" t="n">
-        <v>1309.3</v>
+        <v>163.23</v>
       </c>
       <c r="I26" s="14" t="n">
-        <v>1186.834</v>
+        <v>200.3009</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>838.7822</v>
+        <v>116.6281</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>2058.441</v>
+        <v>176.872</v>
       </c>
       <c r="L26" s="15" t="n">
-        <v>10.3</v>
+        <v>-18.5</v>
       </c>
       <c r="M26" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N26" s="14" t="n">
-        <v>890.1255</v>
+        <v>150.2257</v>
       </c>
       <c r="O26" s="12" t="inlineStr">
         <is>
@@ -3773,33 +3777,33 @@
         </is>
       </c>
       <c r="T26" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U26" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W26" s="12" t="n">
-        <v>81.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="X26" s="13" t="inlineStr">
         <is>
-          <t>毛利90.42%，ROIC42.62%，淨現金53275，營收CAGR17.8%，獲利穩。</t>
+          <t>高毛利59.92%、ROIC 37.79%穩健，現金流強勁，但營收成長放緩至3.1%。</t>
         </is>
       </c>
       <c r="Y26" s="15" t="n">
-        <v>33.6</v>
+        <v>20.4</v>
       </c>
       <c r="Z26" s="15" t="n">
-        <v>42.6</v>
+        <v>37.8</v>
       </c>
       <c r="AA26" s="15" t="n">
-        <v>90.40000000000001</v>
+        <v>59.9</v>
       </c>
       <c r="AB26" s="15" t="n">
-        <v>15.2</v>
+        <v>25.5</v>
       </c>
       <c r="AC26" s="12" t="inlineStr">
         <is>
@@ -3813,7 +3817,7 @@
       </c>
       <c r="AE26" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF26" s="13" t="inlineStr"/>
@@ -3821,17 +3825,17 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>00941</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>中国移动</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr"/>
@@ -3842,30 +3846,30 @@
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>HKD</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="G27" s="13" t="inlineStr"/>
       <c r="H27" s="14" t="n">
-        <v>78.90000000000001</v>
+        <v>1268.64</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>89.6108</v>
+        <v>1186.8347</v>
       </c>
       <c r="J27" s="14" t="n">
-        <v>87.0635</v>
+        <v>838.7851000000001</v>
       </c>
       <c r="K27" s="14" t="n">
-        <v>92.48090000000001</v>
+        <v>2058.441</v>
       </c>
       <c r="L27" s="15" t="n">
-        <v>-12</v>
+        <v>6.9</v>
       </c>
       <c r="M27" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>67.2081</v>
+        <v>890.126</v>
       </c>
       <c r="O27" s="12" t="inlineStr">
         <is>
@@ -3883,7 +3887,7 @@
         </is>
       </c>
       <c r="R27" s="12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="S27" s="12" t="inlineStr">
         <is>
@@ -3891,33 +3895,33 @@
         </is>
       </c>
       <c r="T27" s="12" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="U27" s="12" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="V27" s="12" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W27" s="12" t="n">
-        <v>98.90000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="X27" s="13" t="inlineStr">
         <is>
-          <t>高毛利率67.59%，ROE穩定9.75%，淨現金2149.85億，10年全獲利。</t>
+          <t>毛利90.42%，ROIC42.62%，淨現金53275，營收CAGR17.8%，獲利穩。</t>
         </is>
       </c>
       <c r="Y27" s="15" t="n">
-        <v>9</v>
+        <v>33.6</v>
       </c>
       <c r="Z27" s="15" t="n">
-        <v>8.699999999999999</v>
+        <v>42.6</v>
       </c>
       <c r="AA27" s="15" t="n">
-        <v>67.59999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AB27" s="15" t="n">
-        <v>32.2</v>
+        <v>15.2</v>
       </c>
       <c r="AC27" s="12" t="inlineStr">
         <is>
@@ -3931,29 +3935,25 @@
       </c>
       <c r="AE27" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AF27" s="13" t="inlineStr">
-        <is>
-          <t>報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
-        </is>
-      </c>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AF27" s="13" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>00941</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>中国移动</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr"/>
@@ -3964,30 +3964,30 @@
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>HKD</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr"/>
       <c r="H28" s="14" t="n">
-        <v>85.15000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="I28" s="14" t="n">
-        <v>107.1974</v>
+        <v>89.6123</v>
       </c>
       <c r="J28" s="14" t="n">
-        <v>69.1516</v>
+        <v>87.0705</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>136.1687</v>
+        <v>92.48090000000001</v>
       </c>
       <c r="L28" s="15" t="n">
-        <v>-20.6</v>
+        <v>-12.2</v>
       </c>
       <c r="M28" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>80.398</v>
+        <v>67.2093</v>
       </c>
       <c r="O28" s="12" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="R28" s="12" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S28" s="12" t="inlineStr">
         <is>
@@ -4013,33 +4013,33 @@
         </is>
       </c>
       <c r="T28" s="12" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="U28" s="12" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W28" s="12" t="n">
-        <v>88.7</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="X28" s="13" t="inlineStr">
         <is>
-          <t>ROIC 22.3%穩定，十年獲利持續，負債佔資產64.9%偏高，流動比率1.15不足。</t>
+          <t>高毛利率67.59%，ROE穩定9.75%，淨現金2149.85億，10年全獲利。</t>
         </is>
       </c>
       <c r="Y28" s="15" t="n">
-        <v>20.9</v>
+        <v>9</v>
       </c>
       <c r="Z28" s="15" t="n">
-        <v>22.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA28" s="15" t="n">
-        <v>26.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AB28" s="15" t="n">
-        <v>64.90000000000001</v>
+        <v>32.2</v>
       </c>
       <c r="AC28" s="12" t="inlineStr">
         <is>
@@ -4053,25 +4053,29 @@
       </c>
       <c r="AE28" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AF28" s="13" t="inlineStr"/>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AF28" s="13" t="inlineStr">
+        <is>
+          <t>報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>09961</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>携程集团-S</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr"/>
@@ -4082,30 +4086,30 @@
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>HKD</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="G29" s="13" t="inlineStr"/>
       <c r="H29" s="14" t="n">
-        <v>324.2</v>
+        <v>86.3</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>430.6472</v>
+        <v>107.1812</v>
       </c>
       <c r="J29" s="14" t="n">
-        <v>252.0972</v>
+        <v>69.08240000000001</v>
       </c>
       <c r="K29" s="14" t="n">
-        <v>428.4491</v>
+        <v>136.1669</v>
       </c>
       <c r="L29" s="15" t="n">
-        <v>-24.7</v>
+        <v>-19.5</v>
       </c>
       <c r="M29" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>322.9854</v>
+        <v>80.38590000000001</v>
       </c>
       <c r="O29" s="12" t="inlineStr">
         <is>
@@ -4123,7 +4127,7 @@
         </is>
       </c>
       <c r="R29" s="12" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="S29" s="12" t="inlineStr">
         <is>
@@ -4131,33 +4135,33 @@
         </is>
       </c>
       <c r="T29" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U29" s="12" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="V29" s="12" t="n">
         <v>7.5</v>
       </c>
       <c r="W29" s="12" t="n">
-        <v>89.2</v>
+        <v>88.7</v>
       </c>
       <c r="X29" s="13" t="inlineStr">
         <is>
-          <t>毛利率89.71%、淨現金496億，ROIC 11.73% ROE不穩</t>
+          <t>ROIC 22.3%穩定，十年獲利持續，負債佔資產64.9%偏高，流動比率1.15不足。</t>
         </is>
       </c>
       <c r="Y29" s="15" t="n">
-        <v>19.1</v>
+        <v>20.9</v>
       </c>
       <c r="Z29" s="15" t="n">
-        <v>11.7</v>
+        <v>22.3</v>
       </c>
       <c r="AA29" s="15" t="n">
-        <v>89.7</v>
+        <v>26.5</v>
       </c>
       <c r="AB29" s="15" t="n">
-        <v>36.7</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AC29" s="12" t="inlineStr">
         <is>
@@ -4166,19 +4170,15 @@
       </c>
       <c r="AD29" s="12" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AE29" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AF29" s="13" t="inlineStr">
-        <is>
-          <t>報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
-        </is>
-      </c>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AF29" s="13" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -4209,25 +4209,25 @@
       </c>
       <c r="G30" s="13" t="inlineStr"/>
       <c r="H30" s="14" t="n">
-        <v>30.36</v>
+        <v>31.22</v>
       </c>
       <c r="I30" s="14" t="n">
-        <v>31.629</v>
+        <v>31.6295</v>
       </c>
       <c r="J30" s="14" t="n">
-        <v>16.8704</v>
+        <v>16.8725</v>
       </c>
       <c r="K30" s="14" t="n">
         <v>19.839</v>
       </c>
       <c r="L30" s="15" t="n">
-        <v>-4</v>
+        <v>-1.3</v>
       </c>
       <c r="M30" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>23.7218</v>
+        <v>23.7221</v>
       </c>
       <c r="O30" s="12" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="AE30" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF30" s="13" t="inlineStr">
@@ -4331,25 +4331,25 @@
       </c>
       <c r="G31" s="13" t="inlineStr"/>
       <c r="H31" s="14" t="n">
-        <v>9.145</v>
+        <v>8.994999999999999</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>11.1603</v>
+        <v>11.1691</v>
       </c>
       <c r="J31" s="14" t="n">
-        <v>4.4903</v>
+        <v>4.5312</v>
       </c>
       <c r="K31" s="14" t="n">
         <v>14.7897</v>
       </c>
       <c r="L31" s="15" t="n">
-        <v>-18.1</v>
+        <v>-19.5</v>
       </c>
       <c r="M31" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>8.370200000000001</v>
+        <v>8.376899999999999</v>
       </c>
       <c r="O31" s="12" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>5.5</v>
       </c>
       <c r="W31" s="12" t="n">
-        <v>83.40000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="X31" s="13" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="AE31" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF31" s="13" t="inlineStr">
@@ -4453,25 +4453,25 @@
       </c>
       <c r="G32" s="13" t="inlineStr"/>
       <c r="H32" s="14" t="n">
-        <v>108.6</v>
+        <v>105</v>
       </c>
       <c r="I32" s="14" t="n">
-        <v>136.2006</v>
+        <v>136.1701</v>
       </c>
       <c r="J32" s="14" t="n">
         <v>59.7871</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>129.3837</v>
+        <v>129.2387</v>
       </c>
       <c r="L32" s="15" t="n">
-        <v>-20.3</v>
+        <v>-22.9</v>
       </c>
       <c r="M32" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N32" s="14" t="n">
-        <v>102.1504</v>
+        <v>102.1276</v>
       </c>
       <c r="O32" s="12" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AE32" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF32" s="13" t="inlineStr">
@@ -4575,25 +4575,25 @@
       </c>
       <c r="G33" s="13" t="inlineStr"/>
       <c r="H33" s="14" t="n">
-        <v>26.92</v>
+        <v>26</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>28.7622</v>
+        <v>28.7651</v>
       </c>
       <c r="J33" s="14" t="n">
         <v>18.8996</v>
       </c>
       <c r="K33" s="14" t="n">
-        <v>26.4504</v>
+        <v>26.4515</v>
       </c>
       <c r="L33" s="15" t="n">
-        <v>-6.4</v>
+        <v>-9.6</v>
       </c>
       <c r="M33" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>21.5716</v>
+        <v>21.5739</v>
       </c>
       <c r="O33" s="12" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="AE33" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF33" s="13" t="inlineStr">
@@ -4697,10 +4697,10 @@
       </c>
       <c r="G34" s="13" t="inlineStr"/>
       <c r="H34" s="14" t="n">
-        <v>38.4</v>
+        <v>34.42</v>
       </c>
       <c r="I34" s="14" t="n">
-        <v>40.2619</v>
+        <v>40.8481</v>
       </c>
       <c r="J34" s="14" t="n">
         <v>11.3883</v>
@@ -4709,13 +4709,13 @@
         <v>52.1359</v>
       </c>
       <c r="L34" s="15" t="n">
-        <v>-4.6</v>
+        <v>-15.7</v>
       </c>
       <c r="M34" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>30.1964</v>
+        <v>30.6361</v>
       </c>
       <c r="O34" s="12" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>6.7</v>
       </c>
       <c r="W34" s="12" t="n">
-        <v>81.8</v>
+        <v>82</v>
       </c>
       <c r="X34" s="13" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="AE34" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF34" s="13" t="inlineStr">
@@ -4941,10 +4941,10 @@
       </c>
       <c r="G36" s="18" t="inlineStr"/>
       <c r="H36" s="19" t="n">
-        <v>27.87</v>
+        <v>28.31</v>
       </c>
       <c r="I36" s="19" t="n">
-        <v>20.5832</v>
+        <v>20.5703</v>
       </c>
       <c r="J36" s="19" t="n">
         <v>16.2467</v>
@@ -4953,13 +4953,13 @@
         <v>22.7622</v>
       </c>
       <c r="L36" s="20" t="n">
-        <v>35.4</v>
+        <v>37.6</v>
       </c>
       <c r="M36" s="20" t="n">
         <v>25</v>
       </c>
       <c r="N36" s="19" t="n">
-        <v>15.4374</v>
+        <v>15.4277</v>
       </c>
       <c r="O36" s="17" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="AE36" s="17" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF36" s="18" t="inlineStr"/>
@@ -5063,10 +5063,10 @@
         </is>
       </c>
       <c r="H37" s="19" t="n">
-        <v>562</v>
+        <v>543.5</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>382.5143</v>
+        <v>382.6004</v>
       </c>
       <c r="J37" s="19" t="n">
         <v>170.1479</v>
@@ -5075,13 +5075,13 @@
         <v>309.2153</v>
       </c>
       <c r="L37" s="20" t="n">
-        <v>46.9</v>
+        <v>42.1</v>
       </c>
       <c r="M37" s="20" t="n">
         <v>25</v>
       </c>
       <c r="N37" s="19" t="n">
-        <v>286.8858</v>
+        <v>286.9503</v>
       </c>
       <c r="O37" s="17" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="AE37" s="17" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF37" s="18" t="inlineStr">
@@ -5185,10 +5185,10 @@
       </c>
       <c r="G38" s="18" t="inlineStr"/>
       <c r="H38" s="19" t="n">
-        <v>30.18</v>
+        <v>28.92</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>23.055</v>
+        <v>23.0615</v>
       </c>
       <c r="J38" s="19" t="n">
         <v>8.570600000000001</v>
@@ -5197,13 +5197,13 @@
         <v>15.399</v>
       </c>
       <c r="L38" s="20" t="n">
-        <v>30.9</v>
+        <v>25.4</v>
       </c>
       <c r="M38" s="20" t="n">
         <v>25</v>
       </c>
       <c r="N38" s="19" t="n">
-        <v>17.2913</v>
+        <v>17.2961</v>
       </c>
       <c r="O38" s="17" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="AE38" s="17" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF38" s="18" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="G39" s="18" t="inlineStr"/>
       <c r="H39" s="19" t="n">
-        <v>3.09</v>
+        <v>3.055</v>
       </c>
       <c r="I39" s="19" t="n">
         <v>2.3155</v>
@@ -5319,7 +5319,7 @@
         <v>3.9797</v>
       </c>
       <c r="L39" s="20" t="n">
-        <v>33.4</v>
+        <v>31.9</v>
       </c>
       <c r="M39" s="20" t="n">
         <v>25</v>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="AE39" s="17" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF39" s="18" t="inlineStr">
@@ -5401,126 +5401,122 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="22" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="B40" s="22" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="C40" s="23" t="inlineStr">
-        <is>
-          <t>微软</t>
-        </is>
-      </c>
-      <c r="D40" s="23" t="inlineStr"/>
-      <c r="E40" s="22" t="inlineStr">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>600276</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>恒瑞医药</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="inlineStr"/>
+      <c r="E40" s="17" t="inlineStr">
         <is>
           <t>mature</t>
         </is>
       </c>
-      <c r="F40" s="22" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="G40" s="23" t="inlineStr"/>
-      <c r="H40" s="24" t="n">
-        <v>492.44</v>
-      </c>
-      <c r="I40" s="24" t="n">
-        <v>82.8946</v>
-      </c>
-      <c r="J40" s="24" t="n">
-        <v>6.8997</v>
-      </c>
-      <c r="K40" s="24" t="n">
-        <v>86.59699999999999</v>
-      </c>
-      <c r="L40" s="25" t="n">
-        <v>494.1</v>
-      </c>
-      <c r="M40" s="25" t="n">
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G40" s="18" t="inlineStr"/>
+      <c r="H40" s="19" t="n">
+        <v>42.19</v>
+      </c>
+      <c r="I40" s="19" t="n">
+        <v>28.4781</v>
+      </c>
+      <c r="J40" s="19" t="n">
+        <v>16.1531</v>
+      </c>
+      <c r="K40" s="19" t="n">
+        <v>22.6238</v>
+      </c>
+      <c r="L40" s="20" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="M40" s="20" t="n">
         <v>25</v>
       </c>
-      <c r="N40" s="24" t="n">
-        <v>62.1709</v>
-      </c>
-      <c r="O40" s="22" t="inlineStr">
+      <c r="N40" s="19" t="n">
+        <v>21.3586</v>
+      </c>
+      <c r="O40" s="17" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="P40" s="26" t="inlineStr">
+      <c r="P40" s="21" t="inlineStr">
+        <is>
+          <t>昂貴</t>
+        </is>
+      </c>
+      <c r="Q40" s="17" t="inlineStr">
         <is>
           <t>非常昂貴</t>
         </is>
       </c>
-      <c r="Q40" s="22" t="inlineStr">
-        <is>
-          <t>非常昂貴</t>
-        </is>
-      </c>
-      <c r="R40" s="22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="S40" s="22" t="inlineStr">
+      <c r="R40" s="17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S40" s="17" t="inlineStr">
         <is>
           <t>★★☆☆☆</t>
         </is>
       </c>
-      <c r="T40" s="22" t="n">
+      <c r="T40" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="U40" s="22" t="n">
+      <c r="U40" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="V40" s="22" t="n">
+      <c r="V40" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="W40" s="22" t="n">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="X40" s="23" t="inlineStr">
-        <is>
-          <t>高毛利但ROE波動大，淨現金為負，成長率與估值嚴重脫鉤</t>
-        </is>
-      </c>
-      <c r="Y40" s="25" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="Z40" s="25" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AA40" s="25" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="AB40" s="25" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="AC40" s="22" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AD40" s="22" t="inlineStr">
+      <c r="W40" s="17" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="X40" s="18" t="inlineStr">
+        <is>
+          <t>高毛利率86%、淨現金386億，ROIC 31%但ROE下滑至12%。</t>
+        </is>
+      </c>
+      <c r="Y40" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z40" s="20" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA40" s="20" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="AB40" s="20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC40" s="17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="AD40" s="17" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AE40" s="22" t="inlineStr">
+      <c r="AE40" s="17" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AF40" s="23" t="inlineStr">
-        <is>
-          <t>行情總股本(7,425,545,491)與財報EPS反推(91,781,535,270)差異&gt;25%，已改用反推值 / 缺關鍵科目：cfo,capex,d_and_a</t>
-        </is>
-      </c>
+      <c r="AF40" s="18" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="22" t="inlineStr">
@@ -5530,18 +5526,18 @@
       </c>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C41" s="23" t="inlineStr">
         <is>
-          <t>英伟达</t>
+          <t>微软</t>
         </is>
       </c>
       <c r="D41" s="23" t="inlineStr"/>
       <c r="E41" s="22" t="inlineStr">
         <is>
-          <t>growth</t>
+          <t>mature</t>
         </is>
       </c>
       <c r="F41" s="22" t="inlineStr">
@@ -5551,25 +5547,25 @@
       </c>
       <c r="G41" s="23" t="inlineStr"/>
       <c r="H41" s="24" t="n">
-        <v>218.36</v>
+        <v>492.44</v>
       </c>
       <c r="I41" s="24" t="n">
-        <v>46.2765</v>
+        <v>82.8946</v>
       </c>
       <c r="J41" s="24" t="n">
-        <v>7.2235</v>
+        <v>6.8997</v>
       </c>
       <c r="K41" s="24" t="n">
-        <v>21.2943</v>
+        <v>86.59699999999999</v>
       </c>
       <c r="L41" s="25" t="n">
-        <v>371.9</v>
+        <v>494.1</v>
       </c>
       <c r="M41" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N41" s="24" t="n">
-        <v>34.7074</v>
+        <v>62.1709</v>
       </c>
       <c r="O41" s="22" t="inlineStr">
         <is>
@@ -5598,30 +5594,30 @@
         <v>3</v>
       </c>
       <c r="U41" s="22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V41" s="22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W41" s="22" t="n">
-        <v>88.09999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="X41" s="23" t="inlineStr">
         <is>
-          <t>高成長高利潤率，ROIC 32.54%穩定，但淨現金-21841百萬，資產負債結構健康。</t>
+          <t>高毛利但ROE波動大，淨現金為負，成長率與估值嚴重脫鉤</t>
         </is>
       </c>
       <c r="Y41" s="25" t="n">
-        <v>44.6</v>
+        <v>8.1</v>
       </c>
       <c r="Z41" s="25" t="n">
-        <v>32.5</v>
+        <v>6.7</v>
       </c>
       <c r="AA41" s="25" t="n">
-        <v>75.40000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="AB41" s="25" t="n">
-        <v>28.5</v>
+        <v>41.7</v>
       </c>
       <c r="AC41" s="22" t="inlineStr">
         <is>
@@ -5630,7 +5626,7 @@
       </c>
       <c r="AD41" s="22" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AE41" s="22" t="inlineStr">
@@ -5640,58 +5636,58 @@
       </c>
       <c r="AF41" s="23" t="inlineStr">
         <is>
-          <t>行情總股本(24,100,000,000)與財報EPS反推(88,866,101,695)差異&gt;25%，已改用反推值 / 缺關鍵科目：cfo,capex,d_and_a</t>
+          <t>行情總股本(7,425,545,491)與財報EPS反推(91,781,535,270)差異&gt;25%，已改用反推值 / 缺關鍵科目：cfo,capex,d_and_a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="22" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B42" s="22" t="inlineStr">
         <is>
-          <t>600276</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C42" s="23" t="inlineStr">
         <is>
-          <t>恒瑞医药</t>
+          <t>英伟达</t>
         </is>
       </c>
       <c r="D42" s="23" t="inlineStr"/>
       <c r="E42" s="22" t="inlineStr">
         <is>
-          <t>mature</t>
+          <t>growth</t>
         </is>
       </c>
       <c r="F42" s="22" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G42" s="23" t="inlineStr"/>
       <c r="H42" s="24" t="n">
-        <v>45.71</v>
+        <v>218.36</v>
       </c>
       <c r="I42" s="24" t="n">
-        <v>28.4781</v>
+        <v>46.2765</v>
       </c>
       <c r="J42" s="24" t="n">
-        <v>16.1529</v>
+        <v>7.2235</v>
       </c>
       <c r="K42" s="24" t="n">
-        <v>22.6237</v>
+        <v>21.2943</v>
       </c>
       <c r="L42" s="25" t="n">
-        <v>60.5</v>
+        <v>371.9</v>
       </c>
       <c r="M42" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N42" s="24" t="n">
-        <v>21.3586</v>
+        <v>34.7074</v>
       </c>
       <c r="O42" s="22" t="inlineStr">
         <is>
@@ -5709,7 +5705,7 @@
         </is>
       </c>
       <c r="R42" s="22" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="S42" s="22" t="inlineStr">
         <is>
@@ -5720,47 +5716,51 @@
         <v>3</v>
       </c>
       <c r="U42" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="V42" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="V42" s="22" t="n">
-        <v>4</v>
-      </c>
       <c r="W42" s="22" t="n">
-        <v>95.90000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="X42" s="23" t="inlineStr">
         <is>
-          <t>高毛利率86%、淨現金386億，ROIC 31%但ROE下滑至12%。</t>
+          <t>高成長高利潤率，ROIC 32.54%穩定，但淨現金-21841百萬，資產負債結構健康。</t>
         </is>
       </c>
       <c r="Y42" s="25" t="n">
-        <v>12</v>
+        <v>44.6</v>
       </c>
       <c r="Z42" s="25" t="n">
-        <v>31</v>
+        <v>32.5</v>
       </c>
       <c r="AA42" s="25" t="n">
-        <v>86.09999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="AB42" s="25" t="n">
-        <v>8.199999999999999</v>
+        <v>28.5</v>
       </c>
       <c r="AC42" s="22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AD42" s="22" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AE42" s="22" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AF42" s="23" t="inlineStr"/>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AF42" s="23" t="inlineStr">
+        <is>
+          <t>行情總股本(24,100,000,000)與財報EPS反推(88,866,101,695)差異&gt;25%，已改用反推值 / 缺關鍵科目：cfo,capex,d_and_a</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="22" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="G43" s="23" t="inlineStr"/>
       <c r="H43" s="24" t="n">
-        <v>164.9</v>
+        <v>162.4</v>
       </c>
       <c r="I43" s="24" t="n">
         <v>92.538</v>
@@ -5803,7 +5803,7 @@
         <v>147.259</v>
       </c>
       <c r="L43" s="25" t="n">
-        <v>78.2</v>
+        <v>75.5</v>
       </c>
       <c r="M43" s="25" t="n">
         <v>25</v>
@@ -5873,12 +5873,12 @@
       </c>
       <c r="AE43" s="22" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF43" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">行情總股本(17,160,072,183)與財報EPS反推(163,822,314,050)差異&gt;25%，已改用反推值 / 缺關鍵科目：revenue,cash,total_debt,current_assets,current_liab </t>
+          <t xml:space="preserve">行情總股本(17,160,052,183)與財報EPS反推(163,822,314,050)差異&gt;25%，已改用反推值 / 缺關鍵科目：revenue,cash,total_debt,current_assets,current_liab </t>
         </is>
       </c>
     </row>
@@ -5911,7 +5911,7 @@
       </c>
       <c r="G44" s="23" t="inlineStr"/>
       <c r="H44" s="24" t="n">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="I44" s="24" t="n">
         <v>156.7211</v>
@@ -5923,7 +5923,7 @@
         <v>215.7121</v>
       </c>
       <c r="L44" s="25" t="n">
-        <v>156.5</v>
+        <v>149.5</v>
       </c>
       <c r="M44" s="25" t="n">
         <v>25</v>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AE44" s="22" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF44" s="23" t="inlineStr">
@@ -6029,25 +6029,25 @@
       </c>
       <c r="G45" s="23" t="inlineStr"/>
       <c r="H45" s="24" t="n">
-        <v>195.4</v>
+        <v>188.9</v>
       </c>
       <c r="I45" s="24" t="n">
-        <v>103.4117</v>
+        <v>103.3052</v>
       </c>
       <c r="J45" s="24" t="n">
-        <v>66.6538</v>
+        <v>66.59269999999999</v>
       </c>
       <c r="K45" s="24" t="n">
-        <v>112.279</v>
+        <v>112.1457</v>
       </c>
       <c r="L45" s="25" t="n">
-        <v>89</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="M45" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N45" s="24" t="n">
-        <v>77.55880000000001</v>
+        <v>77.4789</v>
       </c>
       <c r="O45" s="22" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="AE45" s="22" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF45" s="23" t="inlineStr">
@@ -6151,10 +6151,10 @@
       </c>
       <c r="G46" s="23" t="inlineStr"/>
       <c r="H46" s="24" t="n">
-        <v>23.2</v>
+        <v>22.86</v>
       </c>
       <c r="I46" s="24" t="n">
-        <v>12.433</v>
+        <v>12.4346</v>
       </c>
       <c r="J46" s="24" t="n">
         <v>7.2799</v>
@@ -6163,13 +6163,13 @@
         <v>9.681699999999999</v>
       </c>
       <c r="L46" s="25" t="n">
-        <v>86.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="M46" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N46" s="24" t="n">
-        <v>9.3247</v>
+        <v>9.326000000000001</v>
       </c>
       <c r="O46" s="22" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="AE46" s="22" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF46" s="23" t="inlineStr">
@@ -6273,25 +6273,25 @@
       </c>
       <c r="G47" s="23" t="inlineStr"/>
       <c r="H47" s="24" t="n">
-        <v>109.5</v>
+        <v>105.8</v>
       </c>
       <c r="I47" s="24" t="n">
-        <v>68.1579</v>
+        <v>68.1835</v>
       </c>
       <c r="J47" s="24" t="n">
         <v>58.5967</v>
       </c>
       <c r="K47" s="24" t="n">
-        <v>63.9002</v>
+        <v>64.01649999999999</v>
       </c>
       <c r="L47" s="25" t="n">
-        <v>60.7</v>
+        <v>55.2</v>
       </c>
       <c r="M47" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N47" s="24" t="n">
-        <v>51.1184</v>
+        <v>51.1376</v>
       </c>
       <c r="O47" s="22" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="AE47" s="22" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF47" s="23" t="inlineStr">
@@ -6395,10 +6395,10 @@
       </c>
       <c r="G48" s="23" t="inlineStr"/>
       <c r="H48" s="24" t="n">
-        <v>123.34</v>
+        <v>117.62</v>
       </c>
       <c r="I48" s="24" t="n">
-        <v>50.5477</v>
+        <v>50.5525</v>
       </c>
       <c r="J48" s="24" t="n">
         <v>39.5892</v>
@@ -6407,13 +6407,13 @@
         <v>50.2832</v>
       </c>
       <c r="L48" s="25" t="n">
-        <v>144</v>
+        <v>132.7</v>
       </c>
       <c r="M48" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N48" s="24" t="n">
-        <v>37.9108</v>
+        <v>37.9144</v>
       </c>
       <c r="O48" s="22" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="AE48" s="22" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF48" s="23" t="inlineStr"/>
@@ -6513,25 +6513,25 @@
       </c>
       <c r="G49" s="23" t="inlineStr"/>
       <c r="H49" s="24" t="n">
-        <v>64.75</v>
+        <v>64.2</v>
       </c>
       <c r="I49" s="24" t="n">
-        <v>35.7494</v>
+        <v>35.7515</v>
       </c>
       <c r="J49" s="24" t="n">
-        <v>25.4896</v>
+        <v>25.502</v>
       </c>
       <c r="K49" s="24" t="n">
-        <v>36.6829</v>
+        <v>36.6837</v>
       </c>
       <c r="L49" s="25" t="n">
-        <v>81.09999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="M49" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N49" s="24" t="n">
-        <v>26.8121</v>
+        <v>26.8137</v>
       </c>
       <c r="O49" s="22" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="AE49" s="22" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF49" s="23" t="inlineStr">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="G55" s="23" t="inlineStr"/>
       <c r="H55" s="24" t="n">
-        <v>80.59999999999999</v>
+        <v>73.95</v>
       </c>
       <c r="I55" s="24" t="n">
         <v>13.9617</v>
@@ -7257,7 +7257,7 @@
         <v>58.1316</v>
       </c>
       <c r="L55" s="25" t="n">
-        <v>477.3</v>
+        <v>429.7</v>
       </c>
       <c r="M55" s="25" t="n">
         <v>25</v>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="AE55" s="22" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF55" s="23" t="inlineStr">
@@ -7367,25 +7367,25 @@
       </c>
       <c r="G56" s="23" t="inlineStr"/>
       <c r="H56" s="24" t="n">
-        <v>336.01</v>
+        <v>329.87</v>
       </c>
       <c r="I56" s="24" t="n">
-        <v>81.5857</v>
+        <v>81.58629999999999</v>
       </c>
       <c r="J56" s="24" t="n">
         <v>56.4053</v>
       </c>
       <c r="K56" s="24" t="n">
-        <v>81.3643</v>
+        <v>81.3681</v>
       </c>
       <c r="L56" s="25" t="n">
-        <v>311.8</v>
+        <v>304.3</v>
       </c>
       <c r="M56" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N56" s="24" t="n">
-        <v>61.1893</v>
+        <v>61.1898</v>
       </c>
       <c r="O56" s="22" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="AE56" s="22" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF56" s="23" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="G57" s="23" t="inlineStr"/>
       <c r="H57" s="24" t="n">
-        <v>292.54</v>
+        <v>277.5</v>
       </c>
       <c r="I57" s="24" t="n">
         <v>10.4095</v>
@@ -7501,7 +7501,7 @@
         <v>12.8567</v>
       </c>
       <c r="L57" s="25" t="n">
-        <v>2710.3</v>
+        <v>2565.8</v>
       </c>
       <c r="M57" s="25" t="n">
         <v>25</v>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="AE57" s="22" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF57" s="23" t="inlineStr"/>
@@ -8581,7 +8581,7 @@
       </c>
       <c r="G66" s="23" t="inlineStr"/>
       <c r="H66" s="24" t="n">
-        <v>1.365</v>
+        <v>1.285</v>
       </c>
       <c r="I66" s="24" t="n">
         <v>0.0963</v>
@@ -8593,7 +8593,7 @@
         <v>0.1246</v>
       </c>
       <c r="L66" s="25" t="n">
-        <v>1317.4</v>
+        <v>1234.4</v>
       </c>
       <c r="M66" s="25" t="n">
         <v>25</v>
@@ -8665,7 +8665,7 @@
       </c>
       <c r="AE66" s="22" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF66" s="23" t="inlineStr">
@@ -8703,25 +8703,25 @@
       </c>
       <c r="G67" s="23" t="inlineStr"/>
       <c r="H67" s="24" t="n">
-        <v>65.34999999999999</v>
+        <v>62.35</v>
       </c>
       <c r="I67" s="24" t="n">
-        <v>6.9209</v>
+        <v>6.9166</v>
       </c>
       <c r="J67" s="24" t="n">
-        <v>3.7762</v>
+        <v>3.7761</v>
       </c>
       <c r="K67" s="24" t="n">
-        <v>10.4285</v>
+        <v>10.4145</v>
       </c>
       <c r="L67" s="25" t="n">
-        <v>844.2</v>
+        <v>801.5</v>
       </c>
       <c r="M67" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N67" s="24" t="n">
-        <v>5.1907</v>
+        <v>5.1874</v>
       </c>
       <c r="O67" s="22" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="AE67" s="22" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF67" s="23" t="inlineStr">
@@ -8829,7 +8829,7 @@
         </is>
       </c>
       <c r="H68" s="24" t="n">
-        <v>523.6799999999999</v>
+        <v>489.03</v>
       </c>
       <c r="I68" s="24" t="n">
         <v>6.6804</v>
@@ -8841,7 +8841,7 @@
         <v>8.4762</v>
       </c>
       <c r="L68" s="25" t="n">
-        <v>7739.1</v>
+        <v>7220.4</v>
       </c>
       <c r="M68" s="25" t="n">
         <v>25</v>
@@ -8913,7 +8913,7 @@
       </c>
       <c r="AE68" s="22" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF68" s="23" t="inlineStr"/>
@@ -8947,25 +8947,25 @@
       </c>
       <c r="G69" s="28" t="inlineStr"/>
       <c r="H69" s="29" t="n">
-        <v>5.38</v>
+        <v>5.43</v>
       </c>
       <c r="I69" s="29" t="n">
-        <v>3.9282</v>
+        <v>3.914</v>
       </c>
       <c r="J69" s="29" t="n">
-        <v>2.6605</v>
+        <v>2.6415</v>
       </c>
       <c r="K69" s="29" t="n">
         <v>79.6524</v>
       </c>
       <c r="L69" s="30" t="n">
-        <v>37</v>
+        <v>38.7</v>
       </c>
       <c r="M69" s="30" t="n">
         <v>25</v>
       </c>
       <c r="N69" s="29" t="n">
-        <v>2.9462</v>
+        <v>2.9355</v>
       </c>
       <c r="O69" s="27" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
       </c>
       <c r="AE69" s="27" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF69" s="28" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="G72" s="28" t="inlineStr"/>
       <c r="H72" s="29" t="n">
-        <v>6.225</v>
+        <v>5.815</v>
       </c>
       <c r="I72" s="29" t="n">
         <v>158.04</v>
@@ -9325,7 +9325,7 @@
         <v>62.1445</v>
       </c>
       <c r="L72" s="30" t="n">
-        <v>-96.09999999999999</v>
+        <v>-96.3</v>
       </c>
       <c r="M72" s="30" t="n">
         <v>35</v>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="AE72" s="27" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF72" s="28" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="G73" s="28" t="inlineStr"/>
       <c r="H73" s="29" t="n">
-        <v>0.2</v>
+        <v>0.173</v>
       </c>
       <c r="I73" s="29" t="inlineStr"/>
       <c r="J73" s="29" t="inlineStr"/>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="AE73" s="27" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AF73" s="28" t="inlineStr">
@@ -9672,7 +9672,7 @@
         </is>
       </c>
       <c r="C2" s="34" t="n">
-        <v>164.9</v>
+        <v>162.4</v>
       </c>
       <c r="D2" s="34" t="n">
         <v>92.538</v>
@@ -9727,10 +9727,10 @@
         </is>
       </c>
       <c r="C3" s="34" t="n">
-        <v>5.38</v>
+        <v>5.43</v>
       </c>
       <c r="D3" s="34" t="n">
-        <v>3.9282</v>
+        <v>3.914</v>
       </c>
       <c r="E3" s="34" t="inlineStr"/>
       <c r="F3" s="34" t="inlineStr"/>
@@ -9739,7 +9739,7 @@
         <v>7.7314</v>
       </c>
       <c r="I3" s="34" t="n">
-        <v>2.6605</v>
+        <v>2.6415</v>
       </c>
       <c r="J3" s="34" t="inlineStr"/>
       <c r="K3" s="34" t="inlineStr"/>
@@ -9747,7 +9747,7 @@
         <v>79.6524</v>
       </c>
       <c r="M3" s="34" t="n">
-        <v>5.89</v>
+        <v>5.9</v>
       </c>
       <c r="N3" s="34" t="n">
         <v>8.99</v>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="Q3" s="33" t="inlineStr">
         <is>
-          <t>{"ncav": {"NCAV/股": 0.0, "NNWC/股": -12.4752, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 4103328460.0, "g1": -0.0263, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 4890900000.0}, "epv": {"常態營業利益率": 0.1444, "常態NOPAT": 4677046636.0, "WACC": 0.0589, "淨現金": -63645000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.0373, "永續g": 0.03, "目標營業利益率": 0.1444, "WACC": 0.0589, "終值WACC": 0.0995, "有效稅率": 0.2199, "終值佔比": 0.547}, "ddm": {"DPS": 0.7376, "g": 0.0799, "r": 0.0899}}</t>
+          <t>{"ncav": {"NCAV/股": 0.0, "NNWC/股": -12.4752, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 4103328460.0, "g1": -0.0263, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 4890900000.0}, "epv": {"常態營業利益率": 0.1444, "常態NOPAT": 4677046636.0, "WACC": 0.059, "淨現金": -63645000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.0373, "永續g": 0.03, "目標營業利益率": 0.1444, "WACC": 0.059, "終值WACC": 0.0995, "有效稅率": 0.2199, "終值佔比": 0.547}, "ddm": {"DPS": 0.7376, "g": 0.0799, "r": 0.0899}}</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="C4" s="34" t="n">
-        <v>1.365</v>
+        <v>1.285</v>
       </c>
       <c r="D4" s="34" t="n">
         <v>0.0963</v>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="L4" s="34" t="inlineStr"/>
       <c r="M4" s="34" t="n">
-        <v>10.33</v>
+        <v>10.28</v>
       </c>
       <c r="N4" s="34" t="n">
         <v>11.23</v>
@@ -9827,13 +9827,13 @@
         </is>
       </c>
       <c r="C5" s="34" t="n">
-        <v>85.15000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="D5" s="34" t="n">
-        <v>107.1974</v>
+        <v>107.1812</v>
       </c>
       <c r="E5" s="34" t="n">
-        <v>58.4387</v>
+        <v>58.4383</v>
       </c>
       <c r="F5" s="34" t="n">
         <v>147.7494</v>
@@ -9842,22 +9842,22 @@
         <v>2.5941</v>
       </c>
       <c r="H5" s="34" t="n">
-        <v>163.0585</v>
+        <v>163.0562</v>
       </c>
       <c r="I5" s="34" t="n">
-        <v>69.1516</v>
+        <v>69.08240000000001</v>
       </c>
       <c r="J5" s="34" t="n">
-        <v>88.2722</v>
+        <v>88.2657</v>
       </c>
       <c r="K5" s="34" t="n">
-        <v>136.1687</v>
+        <v>136.1669</v>
       </c>
       <c r="L5" s="34" t="n">
-        <v>111.3708</v>
+        <v>111.3692</v>
       </c>
       <c r="M5" s="34" t="n">
-        <v>8.199999999999999</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="N5" s="34" t="n">
         <v>8.9</v>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="Q5" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 5.44, "BVPS": 27.901}, "graham_formula": {"g(上限10%)": 0.081, "Y公司債": 0.04}, "ncav": {"NCAV/股": 2.5941, "NNWC/股": -33.094, "net-net買點": 1.7303}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 51588560000.0, "g1": 0.1206, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 3239763800.0}, "epv": {"常態營業利益率": 0.1079, "常態NOPAT": 41817135357.0, "WACC": 0.082, "淨現金": 14272378000.0}, "damodaran_fcff": {"銷售/資本": 2.353, "g1": 0.0987, "永續g": 0.021, "目標營業利益率": 0.1079, "WACC": 0.082, "終值WACC": 0.089, "有效稅率": 0.1704, "終值佔比": 0.576}, "ri_pb": {"常態ROE": 0.2332, "股權成本r": 0.089, "留存成長g": 0.0518, "合理PB": 4.88}, "ddm": {"DPS": 4.532, "g": 0.0464, "r": 0.089}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 5.44, "BVPS": 27.9006}, "graham_formula": {"g(上限10%)": 0.081, "Y公司債": 0.04}, "ncav": {"NCAV/股": 2.5941, "NNWC/股": -33.0935, "net-net買點": 1.7303}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 51588560000.0, "g1": 0.1206, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 3239763800.0}, "epv": {"常態營業利益率": 0.1079, "常態NOPAT": 41817135357.0, "WACC": 0.0821, "淨現金": 14272378000.0}, "damodaran_fcff": {"銷售/資本": 2.353, "g1": 0.0987, "永續g": 0.021, "目標營業利益率": 0.1079, "WACC": 0.0821, "終值WACC": 0.089, "有效稅率": 0.1704, "終值佔比": 0.576}, "ri_pb": {"常態ROE": 0.2332, "股權成本r": 0.089, "留存成長g": 0.0518, "合理PB": 4.88}, "ddm": {"DPS": 4.5319, "g": 0.0464, "r": 0.089}}</t>
         </is>
       </c>
     </row>
@@ -9888,10 +9888,10 @@
         </is>
       </c>
       <c r="C6" s="34" t="n">
-        <v>38.29</v>
+        <v>38.8</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>142.5437</v>
+        <v>142.5145</v>
       </c>
       <c r="E6" s="34" t="n">
         <v>55.8024</v>
@@ -9906,10 +9906,10 @@
         <v>216.1553</v>
       </c>
       <c r="I6" s="34" t="n">
-        <v>62.3922</v>
+        <v>62.2548</v>
       </c>
       <c r="J6" s="34" t="n">
-        <v>48.7473</v>
+        <v>48.7401</v>
       </c>
       <c r="K6" s="34" t="n">
         <v>808.3745</v>
@@ -9918,7 +9918,7 @@
         <v>151.0522</v>
       </c>
       <c r="M6" s="34" t="n">
-        <v>7.02</v>
+        <v>7.03</v>
       </c>
       <c r="N6" s="34" t="n">
         <v>8.9</v>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="Q6" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 5.22, "BVPS": 26.5126}, "graham_formula": {"g(上限10%)": 0.0699, "Y公司債": 0.04}, "ncav": {"NCAV/股": 1.6956, "NNWC/股": -16.537, "net-net買點": 1.131}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 44665803686.0, "g1": 0.15, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 1998879714.0}, "epv": {"常態營業利益率": 0.1603, "常態NOPAT": 21250243163.0, "WACC": 0.0702, "淨現金": 44611454148.0}, "damodaran_fcff": {"銷售/資本": 1.571, "g1": -0.0345, "永續g": 0.021, "目標營業利益率": 0.1603, "WACC": 0.0702, "終值WACC": 0.089, "有效稅率": 0.1876, "終值佔比": 0.445}, "ri_pb": {"常態ROE": 0.2365, "股權成本r": 0.089, "留存成長g": 0.084, "合理PB": 30.49}, "ddm": {"DPS": 3.1751, "g": 0.0666, "r": 0.089}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 5.22, "BVPS": 26.5126}, "graham_formula": {"g(上限10%)": 0.0699, "Y公司債": 0.04}, "ncav": {"NCAV/股": 1.6956, "NNWC/股": -16.537, "net-net買點": 1.131}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 44665803686.0, "g1": 0.15, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 1998879714.0}, "epv": {"常態營業利益率": 0.1603, "常態NOPAT": 21250243163.0, "WACC": 0.0703, "淨現金": 44611454148.0}, "damodaran_fcff": {"銷售/資本": 1.571, "g1": -0.0345, "永續g": 0.021, "目標營業利益率": 0.1603, "WACC": 0.0703, "終值WACC": 0.089, "有效稅率": 0.1876, "終值佔比": 0.445}, "ri_pb": {"常態ROE": 0.2365, "股權成本r": 0.089, "留存成長g": 0.084, "合理PB": 30.49}, "ddm": {"DPS": 3.1751, "g": 0.0666, "r": 0.089}}</t>
         </is>
       </c>
     </row>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="C7" s="34" t="n">
-        <v>30.18</v>
+        <v>28.92</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>23.055</v>
+        <v>23.0615</v>
       </c>
       <c r="E7" s="34" t="n">
         <v>15.399</v>
@@ -9967,10 +9967,10 @@
         <v>57.4509</v>
       </c>
       <c r="I7" s="34" t="n">
-        <v>10.0809</v>
+        <v>10.1137</v>
       </c>
       <c r="J7" s="34" t="n">
-        <v>8.2784</v>
+        <v>8.278</v>
       </c>
       <c r="K7" s="34" t="n">
         <v>8.570600000000001</v>
@@ -9979,7 +9979,7 @@
         <v>13.1089</v>
       </c>
       <c r="M7" s="34" t="n">
-        <v>8.32</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="N7" s="34" t="n">
         <v>8.9</v>
@@ -9994,7 +9994,7 @@
       </c>
       <c r="Q7" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 0.83, "BVPS": 12.6977}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.04}, "ncav": {"NCAV/股": 1.8941, "NNWC/股": -7.9563, "net-net買點": 1.2634}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 1097085527.0, "g1": 0.15, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 3335130.0}, "epv": {"常態營業利益率": 0.0665, "常態NOPAT": 508532212.0, "WACC": 0.0832, "淨現金": -906634291.0}, "damodaran_fcff": {"銷售/資本": 1.113, "g1": 0.1305, "永續g": 0.021, "目標營業利益率": 0.0665, "WACC": 0.0832, "終值WACC": 0.089, "有效稅率": 0.08, "終值佔比": 1.044}, "ri_pb": {"常態ROE": 0.0708, "股權成本r": 0.089, "留存成長g": 0.0331, "合理PB": 0.675}, "ddm": {"DPS": 0.5995, "g": 0.0414, "r": 0.089}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 0.83, "BVPS": 12.6977}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.04}, "ncav": {"NCAV/股": 1.8941, "NNWC/股": -7.9563, "net-net買點": 1.2634}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 1097085527.0, "g1": 0.15, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 3335130.0}, "epv": {"常態營業利益率": 0.0665, "常態NOPAT": 508532212.0, "WACC": 0.083, "淨現金": -906634291.0}, "damodaran_fcff": {"銷售/資本": 1.113, "g1": 0.1305, "永續g": 0.021, "目標營業利益率": 0.0665, "WACC": 0.083, "終值WACC": 0.089, "有效稅率": 0.08, "終值佔比": 1.044}, "ri_pb": {"常態ROE": 0.0708, "股權成本r": 0.089, "留存成長g": 0.0331, "合理PB": 0.675}, "ddm": {"DPS": 0.5995, "g": 0.0414, "r": 0.089}}</t>
         </is>
       </c>
     </row>
@@ -10010,10 +10010,10 @@
         </is>
       </c>
       <c r="C8" s="34" t="n">
-        <v>1.395</v>
+        <v>1.315</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>3.7982</v>
+        <v>3.8007</v>
       </c>
       <c r="E8" s="34" t="n">
         <v>2.8029</v>
@@ -10028,10 +10028,10 @@
         <v>7.9395</v>
       </c>
       <c r="I8" s="34" t="n">
-        <v>2.3645</v>
+        <v>2.3764</v>
       </c>
       <c r="J8" s="34" t="n">
-        <v>2.2063</v>
+        <v>2.2071</v>
       </c>
       <c r="K8" s="34" t="n">
         <v>1.2252</v>
@@ -10040,7 +10040,7 @@
         <v>2.9007</v>
       </c>
       <c r="M8" s="34" t="n">
-        <v>8.720000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="N8" s="34" t="n">
         <v>9.949999999999999</v>
@@ -10055,7 +10055,7 @@
       </c>
       <c r="Q8" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 0.1511, "BVPS": 1.7052}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.4212, "NNWC/股": -0.3809, "net-net買點": 0.281}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 1650620000.0, "g1": 0.15, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 1933444800.0}, "epv": {"常態營業利益率": 0.0458, "常態NOPAT": 894448196.0, "WACC": 0.0872, "淨現金": 2074648000.0}, "damodaran_fcff": {"銷售/資本": 2.507, "g1": 0.0038, "永續g": 0.03, "目標營業利益率": 0.0458, "WACC": 0.0872, "終值WACC": 0.0995, "有效稅率": 0.2132, "終值佔比": 0.477}, "ri_pb": {"常態ROE": 0.08, "股權成本r": 0.0995, "留存成長g": 0.0485, "合理PB": 0.617}, "ddm": {"DPS": 0.0748, "g": 0.0675, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 0.1511, "BVPS": 1.7052}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.4212, "NNWC/股": -0.3809, "net-net買點": 0.281}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 1650620000.0, "g1": 0.15, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 1933444800.0}, "epv": {"常態營業利益率": 0.0458, "常態NOPAT": 894448196.0, "WACC": 0.0866, "淨現金": 2074648000.0}, "damodaran_fcff": {"銷售/資本": 2.507, "g1": 0.0038, "永續g": 0.03, "目標營業利益率": 0.0458, "WACC": 0.0866, "終值WACC": 0.0995, "有效稅率": 0.2132, "終值佔比": 0.477}, "ri_pb": {"常態ROE": 0.08, "股權成本r": 0.0995, "留存成長g": 0.0485, "合理PB": 0.617}, "ddm": {"DPS": 0.0748, "g": 0.0675, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -10071,10 +10071,10 @@
         </is>
       </c>
       <c r="C9" s="34" t="n">
-        <v>38.4</v>
+        <v>34.42</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>40.2619</v>
+        <v>40.8481</v>
       </c>
       <c r="E9" s="34" t="n">
         <v>39.2855</v>
@@ -10087,7 +10087,7 @@
       </c>
       <c r="H9" s="34" t="inlineStr"/>
       <c r="I9" s="34" t="n">
-        <v>19.6524</v>
+        <v>21.1765</v>
       </c>
       <c r="J9" s="34" t="inlineStr"/>
       <c r="K9" s="34" t="n">
@@ -10097,7 +10097,7 @@
         <v>144.2784</v>
       </c>
       <c r="M9" s="34" t="n">
-        <v>6.27</v>
+        <v>6.09</v>
       </c>
       <c r="N9" s="34" t="n">
         <v>9.949999999999999</v>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="Q9" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 2.0, "BVPS": 25.3079}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 3.4455, "NNWC/股": -35.366, "net-net買點": 2.2982}, "epv": {"常態營業利益率": 0.0217, "常態NOPAT": 9489066287.0, "WACC": 0.0627, "淨現金": -107039386000.0}, "damodaran_fcff": {"銷售/資本": 3.044, "g1": 0.0429, "永續g": 0.03, "目標營業利益率": 0.0217, "WACC": 0.0627, "終值WACC": 0.0995, "有效稅率": 0.2628, "終值佔比": 0.746}, "ri_pb": {"常態ROE": 0.0651, "股權成本r": 0.0995, "留存成長g": 0.0434, "合理PB": 0.387}, "ddm": {"DPS": 1.1376, "g": 0.0895, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 2.0, "BVPS": 25.3079}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 3.4455, "NNWC/股": -35.366, "net-net買點": 2.2982}, "epv": {"常態營業利益率": 0.0217, "常態NOPAT": 9489066287.0, "WACC": 0.0609, "淨現金": -107039386000.0}, "damodaran_fcff": {"銷售/資本": 3.044, "g1": 0.0429, "永續g": 0.03, "目標營業利益率": 0.0217, "WACC": 0.0609, "終值WACC": 0.0995, "有效稅率": 0.2628, "終值佔比": 0.746}, "ri_pb": {"常態ROE": 0.0651, "股權成本r": 0.0995, "留存成長g": 0.0434, "合理PB": 0.387}, "ddm": {"DPS": 1.1376, "g": 0.0895, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -10128,10 +10128,10 @@
         </is>
       </c>
       <c r="C10" s="34" t="n">
-        <v>4.915</v>
+        <v>4.795</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>9.1204</v>
+        <v>9.1286</v>
       </c>
       <c r="E10" s="34" t="n">
         <v>9.2554</v>
@@ -10144,10 +10144,10 @@
         <v>24.345</v>
       </c>
       <c r="I10" s="34" t="n">
-        <v>5.5753</v>
+        <v>5.6134</v>
       </c>
       <c r="J10" s="34" t="n">
-        <v>1.2575</v>
+        <v>1.2592</v>
       </c>
       <c r="K10" s="34" t="n">
         <v>5.6021</v>
@@ -10156,7 +10156,7 @@
         <v>3.1723</v>
       </c>
       <c r="M10" s="34" t="n">
-        <v>6.9</v>
+        <v>6.87</v>
       </c>
       <c r="N10" s="34" t="n">
         <v>9.949999999999999</v>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="Q10" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 0.404, "BVPS": 6.9539}, "graham_formula": {"g(上限10%)": -0.0059, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -6.8094, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 161475000000.0, "g1": -0.0073, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 180806500000.0}, "epv": {"常態營業利益率": 0.0234, "常態NOPAT": 52553004985.0, "WACC": 0.069, "淨現金": -363061000000.0}, "damodaran_fcff": {"銷售/資本": 2.289, "g1": -0.05, "永續g": 0.03, "目標營業利益率": 0.0234, "WACC": 0.069, "終值WACC": 0.0995, "有效稅率": 0.1864, "終值佔比": 0.429}, "ri_pb": {"常態ROE": 0.0716, "股權成本r": 0.0995, "留存成長g": 0.0089, "合理PB": 0.692}, "ddm": {"DPS": 0.2556, "g": 0.0052, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 0.404, "BVPS": 6.9539}, "graham_formula": {"g(上限10%)": -0.0059, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -6.8094, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 161475000000.0, "g1": -0.0073, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 180806500000.0}, "epv": {"常態營業利益率": 0.0234, "常態NOPAT": 52553004985.0, "WACC": 0.0687, "淨現金": -363061000000.0}, "damodaran_fcff": {"銷售/資本": 2.289, "g1": -0.05, "永續g": 0.03, "目標營業利益率": 0.0234, "WACC": 0.0687, "終值WACC": 0.0995, "有效稅率": 0.1864, "終值佔比": 0.429}, "ri_pb": {"常態ROE": 0.0716, "股權成本r": 0.0995, "留存成長g": 0.0089, "合理PB": 0.692}, "ddm": {"DPS": 0.2556, "g": 0.0052, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -10187,7 +10187,7 @@
         </is>
       </c>
       <c r="C11" s="34" t="n">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="D11" s="34" t="n">
         <v>156.7211</v>
@@ -10240,13 +10240,13 @@
         </is>
       </c>
       <c r="C12" s="34" t="n">
-        <v>435.4</v>
+        <v>429.4</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>659.8262999999999</v>
+        <v>659.8955</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>282.242</v>
+        <v>282.2419</v>
       </c>
       <c r="F12" s="34" t="n">
         <v>469.194</v>
@@ -10256,19 +10256,19 @@
         <v>684.9799</v>
       </c>
       <c r="I12" s="34" t="n">
-        <v>369.0737</v>
+        <v>369.3796</v>
       </c>
       <c r="J12" s="34" t="n">
-        <v>459.3317</v>
+        <v>459.3594</v>
       </c>
       <c r="K12" s="34" t="n">
-        <v>3850.9865</v>
+        <v>3850.9861</v>
       </c>
       <c r="L12" s="34" t="n">
-        <v>609.7472</v>
+        <v>609.7471</v>
       </c>
       <c r="M12" s="34" t="n">
-        <v>9.16</v>
+        <v>9.15</v>
       </c>
       <c r="N12" s="34" t="n">
         <v>9.949999999999999</v>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="Q12" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 20.938, "BVPS": 124.7757}, "graham_formula": {"g(上限10%)": 0.08, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -47.8878, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 202308000000.0, "g1": 0.1058, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 642665100000.0}, "epv": {"常態營業利益率": 0.3189, "常態NOPAT": 206641814252.0, "WACC": 0.0916, "淨現金": -12924000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.1076, "永續g": 0.03, "目標營業利益率": 0.3189, "WACC": 0.0916, "終值WACC": 0.0995, "有效稅率": 0.1678, "終值佔比": 0.565}, "ri_pb": {"常態ROE": 0.2271, "股權成本r": 0.0995, "留存成長g": 0.0945, "合理PB": 26.512}, "ddm": {"DPS": 4.8076, "g": 0.0895, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 20.938, "BVPS": 124.7757}, "graham_formula": {"g(上限10%)": 0.08, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -47.8878, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 202308000000.0, "g1": 0.1058, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 642665100000.0}, "epv": {"常態營業利益率": 0.3189, "常態NOPAT": 206641814252.0, "WACC": 0.0915, "淨現金": -12924000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.1076, "永續g": 0.03, "目標營業利益率": 0.3189, "WACC": 0.0915, "終值WACC": 0.0995, "有效稅率": 0.1678, "終值佔比": 0.565}, "ri_pb": {"常態ROE": 0.2271, "股權成本r": 0.0995, "留存成長g": 0.0945, "合理PB": 26.512}, "ddm": {"DPS": 4.8076, "g": 0.0895, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -10299,10 +10299,10 @@
         </is>
       </c>
       <c r="C13" s="34" t="n">
-        <v>5.735</v>
+        <v>5.815</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>11.4648</v>
+        <v>11.4619</v>
       </c>
       <c r="E13" s="34" t="n">
         <v>15.7849</v>
@@ -10315,10 +10315,10 @@
         <v>12.385</v>
       </c>
       <c r="I13" s="34" t="n">
-        <v>11.5052</v>
+        <v>11.4912</v>
       </c>
       <c r="J13" s="34" t="n">
-        <v>8.379</v>
+        <v>8.3786</v>
       </c>
       <c r="K13" s="34" t="n">
         <v>6.1123</v>
@@ -10327,7 +10327,7 @@
         <v>6.4098</v>
       </c>
       <c r="M13" s="34" t="n">
-        <v>7.48</v>
+        <v>7.5</v>
       </c>
       <c r="N13" s="34" t="n">
         <v>8.67</v>
@@ -10342,7 +10342,7 @@
       </c>
       <c r="Q13" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 0.67, "BVPS": 12.1964}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -5.2925, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 22534000000.0, "g1": -0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 52849300000.0}, "epv": {"常態營業利益率": 0.0496, "常態NOPAT": 16364617627.0, "WACC": 0.0748, "淨現金": 30851000000.0}, "damodaran_fcff": {"銷售/資本": 1.149, "g1": 0.0339, "永續g": 0.03, "目標營業利益率": 0.0496, "WACC": 0.0748, "終值WACC": 0.0995, "有效稅率": 0.1621, "終值佔比": 0.692}, "ri_pb": {"常態ROE": 0.0407, "股權成本r": 0.0867, "留存成長g": 0.006, "合理PB": 0.431}, "ddm": {"DPS": 0.4403, "g": 0.0062, "r": 0.0867}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 0.67, "BVPS": 12.1964}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -5.2925, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 22534000000.0, "g1": -0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 52849300000.0}, "epv": {"常態營業利益率": 0.0496, "常態NOPAT": 16364617627.0, "WACC": 0.075, "淨現金": 30851000000.0}, "damodaran_fcff": {"銷售/資本": 1.149, "g1": 0.0339, "永續g": 0.03, "目標營業利益率": 0.0496, "WACC": 0.075, "終值WACC": 0.0995, "有效稅率": 0.1621, "終值佔比": 0.692}, "ri_pb": {"常態ROE": 0.0407, "股權成本r": 0.0867, "留存成長g": 0.006, "合理PB": 0.431}, "ddm": {"DPS": 0.4403, "g": 0.0062, "r": 0.0867}}</t>
         </is>
       </c>
     </row>
@@ -10358,10 +10358,10 @@
         </is>
       </c>
       <c r="C14" s="34" t="n">
-        <v>9.145</v>
+        <v>8.994999999999999</v>
       </c>
       <c r="D14" s="34" t="n">
-        <v>11.1603</v>
+        <v>11.1691</v>
       </c>
       <c r="E14" s="34" t="n">
         <v>14.7897</v>
@@ -10374,10 +10374,10 @@
         <v>24.6392</v>
       </c>
       <c r="I14" s="34" t="n">
-        <v>4.4903</v>
+        <v>4.5312</v>
       </c>
       <c r="J14" s="34" t="n">
-        <v>2.0876</v>
+        <v>2.0895</v>
       </c>
       <c r="K14" s="34" t="n">
         <v>3.5176</v>
@@ -10386,7 +10386,7 @@
         <v>7.3948</v>
       </c>
       <c r="M14" s="34" t="n">
-        <v>7.12</v>
+        <v>7.1</v>
       </c>
       <c r="N14" s="34" t="n">
         <v>9.949999999999999</v>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="Q14" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 0.6138, "BVPS": 11.6873}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -3.1735, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 19679000000.0, "g1": 0.0554, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 0.0}, "epv": {"常態營業利益率": 0.1543, "常態NOPAT": 11583868633.0, "WACC": 0.0712, "淨現金": -94737000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.029, "永續g": 0.03, "目標營業利益率": 0.1543, "WACC": 0.0712, "終值WACC": 0.0995, "有效稅率": 0.2453, "終值佔比": 0.527}, "ri_pb": {"常態ROE": 0.0366, "股權成本r": 0.0995, "留存成長g": 0.0147, "合理PB": 0.259}, "ddm": {"DPS": 0.4548, "g": 0.026, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 0.6138, "BVPS": 11.6873}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -3.1735, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 19679000000.0, "g1": 0.0554, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 0.0}, "epv": {"常態營業利益率": 0.1543, "常態NOPAT": 11583868633.0, "WACC": 0.071, "淨現金": -94737000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.029, "永續g": 0.03, "目標營業利益率": 0.1543, "WACC": 0.071, "終值WACC": 0.0995, "有效稅率": 0.2453, "終值佔比": 0.527}, "ri_pb": {"常態ROE": 0.0366, "股權成本r": 0.0995, "留存成長g": 0.0147, "合理PB": 0.259}, "ddm": {"DPS": 0.4548, "g": 0.026, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="C15" s="34" t="n">
-        <v>18.9</v>
+        <v>18.68</v>
       </c>
       <c r="D15" s="34" t="n">
         <v>53.4079</v>
@@ -10474,10 +10474,10 @@
         </is>
       </c>
       <c r="C16" s="34" t="n">
-        <v>10.35</v>
+        <v>10.07</v>
       </c>
       <c r="D16" s="34" t="n">
-        <v>22.5194</v>
+        <v>22.5292</v>
       </c>
       <c r="E16" s="34" t="n">
         <v>15.4965</v>
@@ -10490,10 +10490,10 @@
         <v>51.231</v>
       </c>
       <c r="I16" s="34" t="n">
-        <v>13.4986</v>
+        <v>13.5427</v>
       </c>
       <c r="J16" s="34" t="n">
-        <v>9.877700000000001</v>
+        <v>9.880800000000001</v>
       </c>
       <c r="K16" s="34" t="n">
         <v>4.5609</v>
@@ -10502,7 +10502,7 @@
         <v>12.6307</v>
       </c>
       <c r="M16" s="34" t="n">
-        <v>8.619999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="N16" s="34" t="n">
         <v>9.949999999999999</v>
@@ -10517,7 +10517,7 @@
       </c>
       <c r="Q16" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 0.88, "BVPS": 8.9497}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -3.903, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 412042000000.0, "g1": 0.0563, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 223097000000.0}, "epv": {"常態營業利益率": 0.0765, "常態NOPAT": 173543902291.0, "WACC": 0.0862, "淨現金": -114814000000.0}, "damodaran_fcff": {"銷售/資本": 1.678, "g1": -0.0401, "永續g": 0.03, "目標營業利益率": 0.0765, "WACC": 0.0862, "終值WACC": 0.0995, "有效稅率": 0.2293, "終值佔比": 0.427}, "ri_pb": {"常態ROE": 0.0583, "股權成本r": 0.0995, "留存成長g": 0.0263, "合理PB": 0.438}, "ddm": {"DPS": 0.5289, "g": 0.0484, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 0.88, "BVPS": 8.9497}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -3.903, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 412042000000.0, "g1": 0.0563, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 223097000000.0}, "epv": {"常態營業利益率": 0.0765, "常態NOPAT": 173543902291.0, "WACC": 0.0859, "淨現金": -114814000000.0}, "damodaran_fcff": {"銷售/資本": 1.678, "g1": -0.0401, "永續g": 0.03, "目標營業利益率": 0.0765, "WACC": 0.0859, "終值WACC": 0.0995, "有效稅率": 0.2293, "終值佔比": 0.427}, "ri_pb": {"常態ROE": 0.0583, "股權成本r": 0.0995, "留存成長g": 0.0263, "合理PB": 0.438}, "ddm": {"DPS": 0.5289, "g": 0.0484, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -10533,10 +10533,10 @@
         </is>
       </c>
       <c r="C17" s="34" t="n">
-        <v>25.86</v>
+        <v>24.88</v>
       </c>
       <c r="D17" s="34" t="n">
-        <v>71.7223</v>
+        <v>71.7325</v>
       </c>
       <c r="E17" s="34" t="n">
         <v>37.787</v>
@@ -10551,10 +10551,10 @@
         <v>143.8576</v>
       </c>
       <c r="I17" s="34" t="n">
-        <v>41.6658</v>
+        <v>41.7224</v>
       </c>
       <c r="J17" s="34" t="n">
-        <v>41.3289</v>
+        <v>41.3341</v>
       </c>
       <c r="K17" s="34" t="n">
         <v>64.7799</v>
@@ -10563,7 +10563,7 @@
         <v>161.2592</v>
       </c>
       <c r="M17" s="34" t="n">
-        <v>9.529999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="N17" s="34" t="n">
         <v>9.949999999999999</v>
@@ -10578,7 +10578,7 @@
       </c>
       <c r="Q17" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 2.6, "BVPS": 18.0108}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 1.0491, "NNWC/股": 0.1424, "net-net買點": 0.6998}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 209743000000.0, "g1": 0.15, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 31624600000.0}, "epv": {"常態營業利益率": 0.4356, "常態NOPAT": 135656996983.0, "WACC": 0.0953, "淨現金": 246290000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": -0.0198, "永續g": 0.03, "目標營業利益率": 0.4356, "WACC": 0.0953, "終值WACC": 0.0995, "有效稅率": 0.2656, "終值佔比": 0.434}, "ri_pb": {"常態ROE": 0.1412, "股權成本r": 0.0995, "留存成長g": 0.0795, "合理PB": 3.09}, "ddm": {"DPS": 1.2715, "g": 0.0895, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 2.6, "BVPS": 18.0108}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 1.0491, "NNWC/股": 0.1424, "net-net買點": 0.6998}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 209743000000.0, "g1": 0.15, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 31624600000.0}, "epv": {"常態營業利益率": 0.4356, "常態NOPAT": 135656996983.0, "WACC": 0.0952, "淨現金": 246290000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": -0.0198, "永續g": 0.03, "目標營業利益率": 0.4356, "WACC": 0.0952, "終值WACC": 0.0995, "有效稅率": 0.2656, "終值佔比": 0.434}, "ri_pb": {"常態ROE": 0.1412, "股權成本r": 0.0995, "留存成長g": 0.0795, "合理PB": 3.09}, "ddm": {"DPS": 1.2715, "g": 0.0895, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -10594,7 +10594,7 @@
         </is>
       </c>
       <c r="C18" s="34" t="n">
-        <v>9.56</v>
+        <v>9.734999999999999</v>
       </c>
       <c r="D18" s="34" t="n">
         <v>130.7854</v>
@@ -10649,10 +10649,10 @@
         </is>
       </c>
       <c r="C19" s="34" t="n">
-        <v>78.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="D19" s="34" t="n">
-        <v>89.6108</v>
+        <v>89.6123</v>
       </c>
       <c r="E19" s="34" t="n">
         <v>114.0363</v>
@@ -10665,10 +10665,10 @@
         <v>92.48090000000001</v>
       </c>
       <c r="I19" s="34" t="n">
-        <v>87.0635</v>
+        <v>87.0705</v>
       </c>
       <c r="J19" s="34" t="n">
-        <v>77.8382</v>
+        <v>77.8387</v>
       </c>
       <c r="K19" s="34" t="n">
         <v>91.19410000000001</v>
@@ -10708,7 +10708,7 @@
         </is>
       </c>
       <c r="C20" s="34" t="n">
-        <v>6.225</v>
+        <v>5.815</v>
       </c>
       <c r="D20" s="34" t="n">
         <v>158.04</v>
@@ -10765,13 +10765,13 @@
         </is>
       </c>
       <c r="C21" s="34" t="n">
-        <v>65.34999999999999</v>
+        <v>62.35</v>
       </c>
       <c r="D21" s="34" t="n">
-        <v>6.9209</v>
+        <v>6.9166</v>
       </c>
       <c r="E21" s="34" t="n">
-        <v>19.1212</v>
+        <v>19.1211</v>
       </c>
       <c r="F21" s="34" t="n">
         <v>4.7126</v>
@@ -10779,17 +10779,17 @@
       <c r="G21" s="34" t="inlineStr"/>
       <c r="H21" s="34" t="inlineStr"/>
       <c r="I21" s="34" t="n">
-        <v>10.4285</v>
+        <v>10.4145</v>
       </c>
       <c r="J21" s="34" t="n">
-        <v>0.4898</v>
+        <v>0.489</v>
       </c>
       <c r="K21" s="34" t="n">
-        <v>3.7762</v>
+        <v>3.7761</v>
       </c>
       <c r="L21" s="34" t="inlineStr"/>
       <c r="M21" s="34" t="n">
-        <v>11.34</v>
+        <v>11.36</v>
       </c>
       <c r="N21" s="34" t="n">
         <v>10.91</v>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="Q21" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 0.09, "BVPS": 2.9373}, "graham_formula": {"g(上限10%)": -0.0393, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -0.378, "net-net買點": 0.0}, "epv": {"常態營業利益率": 0.119, "常態NOPAT": 1124716922.0, "WACC": 0.1134, "淨現金": -1228240000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.0864, "永續g": 0.03, "目標營業利益率": 0.119, "WACC": 0.1134, "終值WACC": 0.0995, "有效稅率": 0.0896, "終值佔比": 0.722}, "ri_pb": {"常態ROE": 0.0431, "股權成本r": 0.1091, "留存成長g": 0.0302, "合理PB": 0.164}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 0.09, "BVPS": 2.9372}, "graham_formula": {"g(上限10%)": -0.0393, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -0.378, "net-net買點": 0.0}, "epv": {"常態營業利益率": 0.119, "常態NOPAT": 1124716922.0, "WACC": 0.1136, "淨現金": -1228240000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.0864, "永續g": 0.03, "目標營業利益率": 0.119, "WACC": 0.1136, "終值WACC": 0.0995, "有效稅率": 0.0896, "終值佔比": 0.722}, "ri_pb": {"常態ROE": 0.0431, "股權成本r": 0.1091, "留存成長g": 0.0302, "合理PB": 0.164}}</t>
         </is>
       </c>
     </row>
@@ -10820,10 +10820,10 @@
         </is>
       </c>
       <c r="C22" s="34" t="n">
-        <v>30.36</v>
+        <v>31.22</v>
       </c>
       <c r="D22" s="34" t="n">
-        <v>31.629</v>
+        <v>31.6295</v>
       </c>
       <c r="E22" s="34" t="n">
         <v>9.529299999999999</v>
@@ -10836,10 +10836,10 @@
         <v>74.4699</v>
       </c>
       <c r="I22" s="34" t="n">
-        <v>16.8704</v>
+        <v>16.8725</v>
       </c>
       <c r="J22" s="34" t="n">
-        <v>19.3513</v>
+        <v>19.3515</v>
       </c>
       <c r="K22" s="34" t="n">
         <v>11.4649</v>
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="C23" s="34" t="n">
-        <v>7.51</v>
+        <v>7.565</v>
       </c>
       <c r="D23" s="34" t="n">
         <v>98.4873</v>
@@ -10934,10 +10934,10 @@
         </is>
       </c>
       <c r="C24" s="34" t="n">
-        <v>26.92</v>
+        <v>26</v>
       </c>
       <c r="D24" s="34" t="n">
-        <v>28.7622</v>
+        <v>28.7651</v>
       </c>
       <c r="E24" s="34" t="n">
         <v>17.415</v>
@@ -10946,25 +10946,25 @@
         <v>24.7646</v>
       </c>
       <c r="G24" s="34" t="n">
-        <v>1.426</v>
+        <v>1.4259</v>
       </c>
       <c r="H24" s="34" t="n">
-        <v>32.0309</v>
+        <v>32.0308</v>
       </c>
       <c r="I24" s="34" t="n">
-        <v>21.3365</v>
+        <v>21.3543</v>
       </c>
       <c r="J24" s="34" t="n">
-        <v>26.4504</v>
+        <v>26.4515</v>
       </c>
       <c r="K24" s="34" t="n">
-        <v>94.2075</v>
+        <v>94.2072</v>
       </c>
       <c r="L24" s="34" t="n">
         <v>18.8996</v>
       </c>
       <c r="M24" s="34" t="n">
-        <v>9.550000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="N24" s="34" t="n">
         <v>9.949999999999999</v>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="Q24" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 0.95, "BVPS": 10.47}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 1.2249, "NNWC/股": -2.6098, "net-net買點": 0.817}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 32977230000.0, "g1": 0.0471, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 105737650200.0}, "epv": {"常態營業利益率": 0.0738, "常態NOPAT": 27114237928.0, "WACC": 0.0955, "淨現金": 82446791000.0}, "damodaran_fcff": {"銷售/資本": 2.34, "g1": 0.15, "永續g": 0.03, "目標營業利益率": 0.0738, "WACC": 0.0955, "終值WACC": 0.0995, "有效稅率": 0.1618, "終值佔比": 0.69}, "ri_pb": {"常態ROE": 0.1331, "股權成本r": 0.0995, "留存成長g": 0.0945, "合理PB": 7.729}, "ddm": {"DPS": 0.149, "g": 0.0895, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 0.95, "BVPS": 10.47}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 1.2249, "NNWC/股": -2.6098, "net-net買點": 0.817}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 32977230000.0, "g1": 0.0471, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 105737650200.0}, "epv": {"常態營業利益率": 0.0738, "常態NOPAT": 27114237928.0, "WACC": 0.0954, "淨現金": 82446791000.0}, "damodaran_fcff": {"銷售/資本": 2.34, "g1": 0.15, "永續g": 0.03, "目標營業利益率": 0.0738, "WACC": 0.0954, "終值WACC": 0.0995, "有效稅率": 0.1618, "終值佔比": 0.69}, "ri_pb": {"常態ROE": 0.1331, "股權成本r": 0.0995, "留存成長g": 0.0945, "合理PB": 7.729}, "ddm": {"DPS": 0.149, "g": 0.0895, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -10995,7 +10995,7 @@
         </is>
       </c>
       <c r="C25" s="34" t="n">
-        <v>3.09</v>
+        <v>3.055</v>
       </c>
       <c r="D25" s="34" t="n">
         <v>2.3155</v>
@@ -11052,7 +11052,7 @@
         </is>
       </c>
       <c r="C26" s="34" t="n">
-        <v>0.2</v>
+        <v>0.173</v>
       </c>
       <c r="D26" s="34" t="inlineStr"/>
       <c r="E26" s="34" t="inlineStr"/>
@@ -11095,7 +11095,7 @@
         </is>
       </c>
       <c r="C27" s="34" t="n">
-        <v>55.25</v>
+        <v>53.5</v>
       </c>
       <c r="D27" s="34" t="n">
         <v>699.6943</v>
@@ -11152,34 +11152,34 @@
         </is>
       </c>
       <c r="C28" s="34" t="n">
-        <v>195.4</v>
+        <v>188.9</v>
       </c>
       <c r="D28" s="34" t="n">
-        <v>103.4117</v>
+        <v>103.3052</v>
       </c>
       <c r="E28" s="34" t="n">
-        <v>55.5002</v>
+        <v>55.4673</v>
       </c>
       <c r="F28" s="34" t="n">
         <v>94.8874</v>
       </c>
       <c r="G28" s="34" t="n">
-        <v>15.8057</v>
+        <v>15.7869</v>
       </c>
       <c r="H28" s="34" t="n">
-        <v>112.279</v>
+        <v>112.1457</v>
       </c>
       <c r="I28" s="34" t="n">
-        <v>66.6538</v>
+        <v>66.59269999999999</v>
       </c>
       <c r="J28" s="34" t="n">
-        <v>79.3899</v>
+        <v>79.2976</v>
       </c>
       <c r="K28" s="34" t="n">
-        <v>470.3341</v>
+        <v>469.7759</v>
       </c>
       <c r="L28" s="34" t="n">
-        <v>242.7361</v>
+        <v>242.448</v>
       </c>
       <c r="M28" s="34" t="n">
         <v>9.84</v>
@@ -11197,7 +11197,7 @@
       </c>
       <c r="Q28" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 3.64, "BVPS": 27.753}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 13.5774, "NNWC/股": 9.3723, "net-net買點": 9.0561}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 10129371000.0, "g1": 0.15, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 7476415100.0}, "epv": {"常態營業利益率": 0.2922, "常態NOPAT": 12432745411.0, "WACC": 0.0984, "淨現金": 38088875000.0}, "damodaran_fcff": {"銷售/資本": 1.184, "g1": 0.0492, "永續g": 0.03, "目標營業利益率": 0.2922, "WACC": 0.0984, "終值WACC": 0.0995, "有效稅率": 0.2054, "終值佔比": 0.493}, "ri_pb": {"常態ROE": 0.1673, "股權成本r": 0.0995, "留存成長g": 0.0945, "合理PB": 14.558}, "ddm": {"DPS": 1.9139, "g": 0.0895, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 3.64, "BVPS": 27.7201}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 13.5612, "NNWC/股": 9.3612, "net-net買點": 9.0454}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 10129371000.0, "g1": 0.15, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 7476415100.0}, "epv": {"常態營業利益率": 0.2922, "常態NOPAT": 12432745411.0, "WACC": 0.0984, "淨現金": 38088875000.0}, "damodaran_fcff": {"銷售/資本": 1.184, "g1": 0.0492, "永續g": 0.03, "目標營業利益率": 0.2922, "WACC": 0.0984, "終值WACC": 0.0995, "有效稅率": 0.2054, "終值佔比": 0.493}, "ri_pb": {"常態ROE": 0.1673, "股權成本r": 0.0995, "留存成長g": 0.0945, "合理PB": 14.558}, "ddm": {"DPS": 1.9116, "g": 0.0895, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -11213,10 +11213,10 @@
         </is>
       </c>
       <c r="C29" s="34" t="n">
-        <v>3.545</v>
+        <v>3.33</v>
       </c>
       <c r="D29" s="34" t="n">
-        <v>13.2423</v>
+        <v>13.2428</v>
       </c>
       <c r="E29" s="34" t="n">
         <v>4.9089</v>
@@ -11231,10 +11231,10 @@
         <v>6.861</v>
       </c>
       <c r="I29" s="34" t="n">
-        <v>7.7516</v>
+        <v>7.754</v>
       </c>
       <c r="J29" s="34" t="n">
-        <v>11.2315</v>
+        <v>11.2318</v>
       </c>
       <c r="K29" s="34" t="n">
         <v>102.7244</v>
@@ -11258,7 +11258,7 @@
       </c>
       <c r="Q29" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 0.4162, "BVPS": 1.8988}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 1.6803, "NNWC/股": 0.5293, "net-net買點": 1.1208}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 1234014000.0, "g1": 0.0104, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 13782300.0}, "epv": {"常態營業利益率": 0.1382, "常態NOPAT": 1602996272.0, "WACC": 0.0989, "淨現金": 5637209000.0}, "damodaran_fcff": {"銷售/資本": 4.0, "g1": 0.1113, "永續g": 0.03, "目標營業利益率": 0.1382, "WACC": 0.0989, "終值WACC": 0.0995, "有效稅率": 0.241, "終值佔比": 0.521}, "ri_pb": {"常態ROE": 0.3269, "股權成本r": 0.0995, "留存成長g": 0.0945, "合理PB": 46.472}, "ddm": {"DPS": 0.1805, "g": 0.0895, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 0.4162, "BVPS": 1.8988}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 1.6803, "NNWC/股": 0.5293, "net-net買點": 1.1208}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 1234014000.0, "g1": 0.0104, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 13782300.0}, "epv": {"常態營業利益率": 0.1382, "常態NOPAT": 1602996272.0, "WACC": 0.0988, "淨現金": 5637209000.0}, "damodaran_fcff": {"銷售/資本": 4.0, "g1": 0.1113, "永續g": 0.03, "目標營業利益率": 0.1382, "WACC": 0.0988, "終值WACC": 0.0995, "有效稅率": 0.241, "終值佔比": 0.521}, "ri_pb": {"常態ROE": 0.3269, "股權成本r": 0.0995, "留存成長g": 0.0945, "合理PB": 46.472}, "ddm": {"DPS": 0.1805, "g": 0.0895, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -11274,10 +11274,10 @@
         </is>
       </c>
       <c r="C30" s="34" t="n">
-        <v>51.4</v>
+        <v>50.05</v>
       </c>
       <c r="D30" s="34" t="n">
-        <v>84.0279</v>
+        <v>84.1289</v>
       </c>
       <c r="E30" s="34" t="n">
         <v>83.2593</v>
@@ -11290,10 +11290,10 @@
         <v>55.5251</v>
       </c>
       <c r="I30" s="34" t="n">
-        <v>113.4582</v>
+        <v>113.9229</v>
       </c>
       <c r="J30" s="34" t="n">
-        <v>84.36109999999999</v>
+        <v>84.38639999999999</v>
       </c>
       <c r="K30" s="34" t="n">
         <v>165.9242</v>
@@ -11302,7 +11302,7 @@
         <v>106.0289</v>
       </c>
       <c r="M30" s="34" t="n">
-        <v>7.15</v>
+        <v>7.12</v>
       </c>
       <c r="N30" s="34" t="n">
         <v>8.67</v>
@@ -11317,7 +11317,7 @@
       </c>
       <c r="Q30" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 5.35, "BVPS": 42.4945}, "graham_formula": {"g(上限10%)": -0.0102, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -31.3139, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 3560000000.0, "g1": -0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 10906000000.0}, "epv": {"常態營業利益率": 0.0881, "常態NOPAT": 7889920905.0, "WACC": 0.0715, "淨現金": -10879000000.0}, "damodaran_fcff": {"銷售/資本": 1.92, "g1": 0.0056, "永續g": 0.03, "目標營業利益率": 0.0881, "WACC": 0.0715, "終值WACC": 0.0995, "有效稅率": 0.2095, "終值佔比": 0.458}, "ri_pb": {"常態ROE": 0.155, "股權成本r": 0.0867, "留存成長g": 0.0577, "合理PB": 3.354}, "ddm": {"DPS": 3.4077, "g": 0.0475, "r": 0.0867}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 5.35, "BVPS": 42.4945}, "graham_formula": {"g(上限10%)": -0.0102, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -31.3139, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 3560000000.0, "g1": -0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 10906000000.0}, "epv": {"常態營業利益率": 0.0881, "常態NOPAT": 7889920905.0, "WACC": 0.0712, "淨現金": -10879000000.0}, "damodaran_fcff": {"銷售/資本": 1.92, "g1": 0.0056, "永續g": 0.03, "目標營業利益率": 0.0881, "WACC": 0.0712, "終值WACC": 0.0995, "有效稅率": 0.2095, "終值佔比": 0.458}, "ri_pb": {"常態ROE": 0.155, "股權成本r": 0.0867, "留存成長g": 0.0577, "合理PB": 3.354}, "ddm": {"DPS": 3.4077, "g": 0.0475, "r": 0.0867}}</t>
         </is>
       </c>
     </row>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="C31" s="34" t="n">
-        <v>80.59999999999999</v>
+        <v>73.95</v>
       </c>
       <c r="D31" s="34" t="n">
         <v>13.9617</v>
@@ -11357,7 +11357,7 @@
       </c>
       <c r="L31" s="34" t="inlineStr"/>
       <c r="M31" s="34" t="n">
-        <v>12.06</v>
+        <v>12.14</v>
       </c>
       <c r="N31" s="34" t="n">
         <v>10.91</v>
@@ -11388,10 +11388,10 @@
         </is>
       </c>
       <c r="C32" s="34" t="n">
-        <v>562</v>
+        <v>543.5</v>
       </c>
       <c r="D32" s="34" t="n">
-        <v>382.5143</v>
+        <v>382.6004</v>
       </c>
       <c r="E32" s="34" t="n">
         <v>170.1479</v>
@@ -11406,10 +11406,10 @@
         <v>309.2153</v>
       </c>
       <c r="I32" s="34" t="n">
-        <v>213.7926</v>
+        <v>214.1768</v>
       </c>
       <c r="J32" s="34" t="n">
-        <v>266.5266</v>
+        <v>266.5649</v>
       </c>
       <c r="K32" s="34" t="n">
         <v>2201.7896</v>
@@ -11418,7 +11418,7 @@
         <v>1178.8895</v>
       </c>
       <c r="M32" s="34" t="n">
-        <v>9.300000000000001</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="N32" s="34" t="n">
         <v>9.949999999999999</v>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="Q32" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 11.58, "BVPS": 81.991}, "graham_formula": {"g(上限10%)": 0.03, "Y公司債": 0.056}, "ncav": {"NCAV/股": 7.3386, "NNWC/股": -39.3809, "net-net買點": 4.8948}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 65810402000.0, "g1": 0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 10748265500.0}, "epv": {"常態營業利益率": 0.1491, "常態NOPAT": 66831915950.0, "WACC": 0.093, "淨現金": 120569062000.0}, "damodaran_fcff": {"銷售/資本": 2.016, "g1": 0.0884, "永續g": 0.03, "目標營業利益率": 0.1491, "WACC": 0.093, "終值WACC": 0.0995, "有效稅率": 0.1411, "終值佔比": 0.53}, "ri_pb": {"常態ROE": 0.2098, "股權成本r": 0.0995, "留存成長g": 0.0945, "合理PB": 23.068}, "ddm": {"DPS": 9.295, "g": 0.0895, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 11.58, "BVPS": 81.991}, "graham_formula": {"g(上限10%)": 0.03, "Y公司債": 0.056}, "ncav": {"NCAV/股": 7.3386, "NNWC/股": -39.3809, "net-net買點": 4.8948}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 65810402000.0, "g1": 0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 10748265500.0}, "epv": {"常態營業利益率": 0.1491, "常態NOPAT": 66831915950.0, "WACC": 0.0928, "淨現金": 120569062000.0}, "damodaran_fcff": {"銷售/資本": 2.016, "g1": 0.0884, "永續g": 0.03, "目標營業利益率": 0.1491, "WACC": 0.0928, "終值WACC": 0.0995, "有效稅率": 0.1411, "終值佔比": 0.53}, "ri_pb": {"常態ROE": 0.2098, "股權成本r": 0.0995, "留存成長g": 0.0945, "合理PB": 23.068}, "ddm": {"DPS": 9.295, "g": 0.0895, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -11449,7 +11449,7 @@
         </is>
       </c>
       <c r="C33" s="34" t="n">
-        <v>51.9</v>
+        <v>51.65</v>
       </c>
       <c r="D33" s="34" t="n">
         <v>588.5381</v>
@@ -11504,10 +11504,10 @@
         </is>
       </c>
       <c r="C34" s="34" t="n">
-        <v>4.48</v>
+        <v>4.35</v>
       </c>
       <c r="D34" s="34" t="n">
-        <v>8.302</v>
+        <v>8.3026</v>
       </c>
       <c r="E34" s="34" t="n">
         <v>3.8731</v>
@@ -11522,10 +11522,10 @@
         <v>14.7347</v>
       </c>
       <c r="I34" s="34" t="n">
-        <v>4.4147</v>
+        <v>4.4176</v>
       </c>
       <c r="J34" s="34" t="n">
-        <v>7.0629</v>
+        <v>7.0633</v>
       </c>
       <c r="K34" s="34" t="n">
         <v>3.6595</v>
@@ -11534,7 +11534,7 @@
         <v>6.6701</v>
       </c>
       <c r="M34" s="34" t="n">
-        <v>9.699999999999999</v>
+        <v>9.69</v>
       </c>
       <c r="N34" s="34" t="n">
         <v>9.949999999999999</v>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="Q34" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 0.3158, "BVPS": 1.5579}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.9296, "NNWC/股": -0.1501, "net-net買點": 0.6201}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 5349009000.0, "g1": 0.1468, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 1308295800.0}, "epv": {"常態營業利益率": 0.1894, "常態NOPAT": 3722217966.0, "WACC": 0.097, "淨現金": 4788314000.0}, "damodaran_fcff": {"銷售/資本": 2.029, "g1": 0.15, "永續g": 0.03, "目標營業利益率": 0.1894, "WACC": 0.097, "終值WACC": 0.0995, "有效稅率": 0.2816, "終值佔比": 0.577}, "ri_pb": {"常態ROE": 0.1618, "股權成本r": 0.0995, "留存成長g": 0.0383, "合理PB": 2.018}, "ddm": {"DPS": 0.26, "g": 0.0518, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 0.3158, "BVPS": 1.5579}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.9296, "NNWC/股": -0.1501, "net-net買點": 0.6201}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 5349009000.0, "g1": 0.1468, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 1308295800.0}, "epv": {"常態營業利益率": 0.1894, "常態NOPAT": 3722217966.0, "WACC": 0.0969, "淨現金": 4788314000.0}, "damodaran_fcff": {"銷售/資本": 2.029, "g1": 0.15, "永續g": 0.03, "目標營業利益率": 0.1894, "WACC": 0.0969, "終值WACC": 0.0995, "有效稅率": 0.2816, "終值佔比": 0.577}, "ri_pb": {"常態ROE": 0.1618, "股權成本r": 0.0995, "留存成長g": 0.0383, "合理PB": 2.018}, "ddm": {"DPS": 0.26, "g": 0.0518, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -11565,10 +11565,10 @@
         </is>
       </c>
       <c r="C35" s="34" t="n">
-        <v>23.2</v>
+        <v>22.86</v>
       </c>
       <c r="D35" s="34" t="n">
-        <v>12.433</v>
+        <v>12.4346</v>
       </c>
       <c r="E35" s="34" t="n">
         <v>14.9173</v>
@@ -11581,10 +11581,10 @@
         <v>23.633</v>
       </c>
       <c r="I35" s="34" t="n">
-        <v>8.801</v>
+        <v>8.8095</v>
       </c>
       <c r="J35" s="34" t="n">
-        <v>6.5917</v>
+        <v>6.5914</v>
       </c>
       <c r="K35" s="34" t="n">
         <v>7.2799</v>
@@ -11593,7 +11593,7 @@
         <v>6.9258</v>
       </c>
       <c r="M35" s="34" t="n">
-        <v>9.32</v>
+        <v>9.31</v>
       </c>
       <c r="N35" s="34" t="n">
         <v>9.949999999999999</v>
@@ -11608,7 +11608,7 @@
       </c>
       <c r="Q35" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 0.73, "BVPS": 9.9973}, "graham_formula": {"g(上限10%)": 0.03, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -2.5412, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 5736271000.0, "g1": 0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 980000000.0}, "epv": {"常態營業利益率": 0.0675, "常態NOPAT": 3992648994.0, "WACC": 0.0932, "淨現金": -3912000000.0}, "damodaran_fcff": {"銷售/資本": 1.24, "g1": 0.15, "永續g": 0.03, "目標營業利益率": 0.0675, "WACC": 0.0932, "終值WACC": 0.0995, "有效稅率": 0.1589, "終值佔比": 1.229}, "ri_pb": {"常態ROE": 0.0691, "股權成本r": 0.0995, "留存成長g": 0.0183, "合理PB": 0.626}, "ddm": {"DPS": 0.4803, "g": 0.0174, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 0.73, "BVPS": 9.9973}, "graham_formula": {"g(上限10%)": 0.03, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -2.5412, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 5736271000.0, "g1": 0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 980000000.0}, "epv": {"常態營業利益率": 0.0675, "常態NOPAT": 3992648994.0, "WACC": 0.0931, "淨現金": -3912000000.0}, "damodaran_fcff": {"銷售/資本": 1.24, "g1": 0.15, "永續g": 0.03, "目標營業利益率": 0.0675, "WACC": 0.0931, "終值WACC": 0.0995, "有效稅率": 0.1589, "終值佔比": 1.229}, "ri_pb": {"常態ROE": 0.0691, "股權成本r": 0.0995, "留存成長g": 0.0183, "合理PB": 0.626}, "ddm": {"DPS": 0.4803, "g": 0.0174, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -11624,10 +11624,10 @@
         </is>
       </c>
       <c r="C36" s="34" t="n">
-        <v>108.6</v>
+        <v>105</v>
       </c>
       <c r="D36" s="34" t="n">
-        <v>136.2006</v>
+        <v>136.1701</v>
       </c>
       <c r="E36" s="34" t="n">
         <v>135.02</v>
@@ -11640,10 +11640,10 @@
         <v>245.8763</v>
       </c>
       <c r="I36" s="34" t="n">
-        <v>129.3837</v>
+        <v>129.2387</v>
       </c>
       <c r="J36" s="34" t="n">
-        <v>98.45950000000001</v>
+        <v>98.4558</v>
       </c>
       <c r="K36" s="34" t="n">
         <v>54.4545</v>
@@ -11652,7 +11652,7 @@
         <v>55.116</v>
       </c>
       <c r="M36" s="34" t="n">
-        <v>10.74</v>
+        <v>10.76</v>
       </c>
       <c r="N36" s="34" t="n">
         <v>9.949999999999999</v>
@@ -11667,7 +11667,7 @@
       </c>
       <c r="Q36" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 7.69, "BVPS": 77.7484}, "graham_formula": {"g(上限10%)": -0.1587, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -50.5795, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 49191000000.0, "g1": -0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 0.0}, "epv": {"常態營業利益率": 0.0189, "常態NOPAT": 21147865283.0, "WACC": 0.1074, "淨現金": 116354000000.0}, "damodaran_fcff": {"銷售/資本": 4.0, "g1": 0.0776, "永續g": 0.03, "目標營業利益率": 0.0189, "WACC": 0.1074, "終值WACC": 0.0995, "有效稅率": 0.1459, "終值佔比": 0.828}, "ri_pb": {"常態ROE": 0.0679, "股權成本r": 0.0995, "留存成長g": 0.0203, "合理PB": 0.602}, "ddm": {"DPS": 3.6827, "g": 0.0201, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 7.69, "BVPS": 77.7484}, "graham_formula": {"g(上限10%)": -0.1587, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -50.5795, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 49191000000.0, "g1": -0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 0.0}, "epv": {"常態營業利益率": 0.0189, "常態NOPAT": 21147865283.0, "WACC": 0.1076, "淨現金": 116354000000.0}, "damodaran_fcff": {"銷售/資本": 4.0, "g1": 0.0776, "永續g": 0.03, "目標營業利益率": 0.0189, "WACC": 0.1076, "終值WACC": 0.0995, "有效稅率": 0.1459, "終值佔比": 0.828}, "ri_pb": {"常態ROE": 0.0679, "股權成本r": 0.0995, "留存成長g": 0.0203, "合理PB": 0.602}, "ddm": {"DPS": 3.6827, "g": 0.0201, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -11683,10 +11683,10 @@
         </is>
       </c>
       <c r="C37" s="34" t="n">
-        <v>324.2</v>
+        <v>304.8</v>
       </c>
       <c r="D37" s="34" t="n">
-        <v>430.6472</v>
+        <v>430.9274</v>
       </c>
       <c r="E37" s="34" t="n">
         <v>428.4491</v>
@@ -11701,10 +11701,10 @@
         <v>572.925</v>
       </c>
       <c r="I37" s="34" t="n">
-        <v>321.1306</v>
+        <v>322.4101</v>
       </c>
       <c r="J37" s="34" t="n">
-        <v>427.2753</v>
+        <v>427.3765</v>
       </c>
       <c r="K37" s="34" t="n">
         <v>40.2781</v>
@@ -11713,7 +11713,7 @@
         <v>252.0972</v>
       </c>
       <c r="M37" s="34" t="n">
-        <v>9.07</v>
+        <v>9.02</v>
       </c>
       <c r="N37" s="34" t="n">
         <v>9.949999999999999</v>
@@ -11728,7 +11728,7 @@
       </c>
       <c r="Q37" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 26.1, "BVPS": 230.6641}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 37.4485, "NNWC/股": -4.5445, "net-net買點": 24.9782}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 19034000000.0, "g1": 0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 0.0}, "epv": {"常態營業利益率": 0.2756, "常態NOPAT": 13408699793.0, "WACC": 0.0907, "淨現金": 49645000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.15, "永續g": 0.03, "目標營業利益率": 0.2756, "WACC": 0.0907, "終值WACC": 0.0995, "有效稅率": 0.1611, "終值佔比": 0.632}, "ri_pb": {"常態ROE": 0.0403, "股權成本r": 0.0995, "留存成長g": 0.0385, "合理PB": 0.15}, "ddm": {"DPS": 1.9877, "g": 0.0895, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 26.1, "BVPS": 230.6641}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 37.4485, "NNWC/股": -4.5445, "net-net買點": 24.9782}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 19034000000.0, "g1": 0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 0.0}, "epv": {"常態營業利益率": 0.2756, "常態NOPAT": 13408699793.0, "WACC": 0.0902, "淨現金": 49645000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.15, "永續g": 0.03, "目標營業利益率": 0.2756, "WACC": 0.0902, "終值WACC": 0.0995, "有效稅率": 0.1611, "終值佔比": 0.631}, "ri_pb": {"常態ROE": 0.0403, "股權成本r": 0.0995, "留存成長g": 0.0385, "合理PB": 0.15}, "ddm": {"DPS": 1.9877, "g": 0.0895, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -11744,10 +11744,10 @@
         </is>
       </c>
       <c r="C38" s="34" t="n">
-        <v>109.5</v>
+        <v>105.8</v>
       </c>
       <c r="D38" s="34" t="n">
-        <v>68.1579</v>
+        <v>68.1835</v>
       </c>
       <c r="E38" s="34" t="n">
         <v>96.09999999999999</v>
@@ -11760,10 +11760,10 @@
         <v>85.75449999999999</v>
       </c>
       <c r="I38" s="34" t="n">
-        <v>63.9002</v>
+        <v>64.01649999999999</v>
       </c>
       <c r="J38" s="34" t="n">
-        <v>61.5663</v>
+        <v>61.5737</v>
       </c>
       <c r="K38" s="34" t="n">
         <v>58.5967</v>
@@ -11772,7 +11772,7 @@
         <v>33.7265</v>
       </c>
       <c r="M38" s="34" t="n">
-        <v>9.300000000000001</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="N38" s="34" t="n">
         <v>9.949999999999999</v>
@@ -11787,7 +11787,7 @@
       </c>
       <c r="Q38" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 5.7, "BVPS": 53.1367}, "graham_formula": {"g(上限10%)": -0.0389, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -23.2597, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 121050000000.0, "g1": -0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 0.0}, "epv": {"常態營業利益率": 0.1155, "常態NOPAT": 84500768832.0, "WACC": 0.093, "淨現金": 183360000000.0}, "damodaran_fcff": {"銷售/資本": 1.197, "g1": 0.0562, "永續g": 0.03, "目標營業利益率": 0.1155, "WACC": 0.093, "終值WACC": 0.0995, "有效稅率": 0.3, "終值佔比": 0.598}, "ri_pb": {"常態ROE": 0.0969, "股權成本r": 0.0995, "留存成長g": 0.0507, "合理PB": 0.947}, "ddm": {"DPS": 1.7626, "g": 0.0364, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 5.7, "BVPS": 53.1367}, "graham_formula": {"g(上限10%)": -0.0389, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -23.2597, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 121050000000.0, "g1": -0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 0.0}, "epv": {"常態營業利益率": 0.1155, "常態NOPAT": 84500768832.0, "WACC": 0.0928, "淨現金": 183360000000.0}, "damodaran_fcff": {"銷售/資本": 1.197, "g1": 0.0562, "永續g": 0.03, "目標營業利益率": 0.1155, "WACC": 0.0928, "終值WACC": 0.0995, "有效稅率": 0.3, "終值佔比": 0.598}, "ri_pb": {"常態ROE": 0.0969, "股權成本r": 0.0995, "留存成長g": 0.0507, "合理PB": 0.947}, "ddm": {"DPS": 1.7626, "g": 0.0364, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -11803,10 +11803,10 @@
         </is>
       </c>
       <c r="C39" s="34" t="n">
-        <v>188.2</v>
+        <v>182</v>
       </c>
       <c r="D39" s="34" t="n">
-        <v>300.133</v>
+        <v>300.1444</v>
       </c>
       <c r="E39" s="34" t="n">
         <v>121.3865</v>
@@ -11821,10 +11821,10 @@
         <v>378.6999</v>
       </c>
       <c r="I39" s="34" t="n">
-        <v>153.3541</v>
+        <v>153.404</v>
       </c>
       <c r="J39" s="34" t="n">
-        <v>184.6516</v>
+        <v>184.6576</v>
       </c>
       <c r="K39" s="34" t="n">
         <v>1407.6936</v>
@@ -11864,10 +11864,10 @@
         </is>
       </c>
       <c r="C40" s="34" t="n">
-        <v>87.84999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D40" s="34" t="n">
-        <v>126.3602</v>
+        <v>126.3713</v>
       </c>
       <c r="E40" s="34" t="n">
         <v>53.8044</v>
@@ -11882,10 +11882,10 @@
         <v>147.8206</v>
       </c>
       <c r="I40" s="34" t="n">
-        <v>67.4669</v>
+        <v>67.5265</v>
       </c>
       <c r="J40" s="34" t="n">
-        <v>108.1055</v>
+        <v>108.112</v>
       </c>
       <c r="K40" s="34" t="n">
         <v>403.9189</v>
@@ -11894,7 +11894,7 @@
         <v>183.7729</v>
       </c>
       <c r="M40" s="34" t="n">
-        <v>8.619999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="N40" s="34" t="n">
         <v>8.9</v>
@@ -11909,7 +11909,7 @@
       </c>
       <c r="Q40" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 5.32, "BVPS": 24.1847}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.04}, "ncav": {"NCAV/股": 13.8461, "NNWC/股": -5.13, "net-net買點": 9.2354}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 11304326739.0, "g1": 0.15, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 538428743.0}, "epv": {"常態營業利益率": 0.1587, "常態NOPAT": 9974027116.0, "WACC": 0.0862, "淨現金": 23674144031.0}, "damodaran_fcff": {"銷售/資本": 2.893, "g1": 0.15, "永續g": 0.021, "目標營業利益率": 0.1587, "WACC": 0.0862, "終值WACC": 0.089, "有效稅率": 0.1792, "終值佔比": 0.573}, "ri_pb": {"常態ROE": 0.1675, "股權成本r": 0.089, "留存成長g": 0.084, "合理PB": 16.701}, "ddm": {"DPS": 1.7032, "g": 0.079, "r": 0.089}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 5.32, "BVPS": 24.1847}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.04}, "ncav": {"NCAV/股": 13.8461, "NNWC/股": -5.13, "net-net買點": 9.2354}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 11304326739.0, "g1": 0.15, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 538428743.0}, "epv": {"常態營業利益率": 0.1587, "常態NOPAT": 9974027116.0, "WACC": 0.0861, "淨現金": 23674144031.0}, "damodaran_fcff": {"銷售/資本": 2.893, "g1": 0.15, "永續g": 0.021, "目標營業利益率": 0.1587, "WACC": 0.0861, "終值WACC": 0.089, "有效稅率": 0.1792, "終值佔比": 0.573}, "ri_pb": {"常態ROE": 0.1675, "股權成本r": 0.089, "留存成長g": 0.084, "合理PB": 16.701}, "ddm": {"DPS": 1.7032, "g": 0.079, "r": 0.089}}</t>
         </is>
       </c>
     </row>
@@ -11925,10 +11925,10 @@
         </is>
       </c>
       <c r="C41" s="34" t="n">
-        <v>169.95</v>
+        <v>163.23</v>
       </c>
       <c r="D41" s="34" t="n">
-        <v>200.2999</v>
+        <v>200.3009</v>
       </c>
       <c r="E41" s="34" t="n">
         <v>84.8402</v>
@@ -11943,10 +11943,10 @@
         <v>124.1863</v>
       </c>
       <c r="I41" s="34" t="n">
-        <v>116.6235</v>
+        <v>116.6281</v>
       </c>
       <c r="J41" s="34" t="n">
-        <v>134.5581</v>
+        <v>134.5585</v>
       </c>
       <c r="K41" s="34" t="n">
         <v>1437.3751</v>
@@ -11986,7 +11986,7 @@
         </is>
       </c>
       <c r="C42" s="34" t="n">
-        <v>45.71</v>
+        <v>42.19</v>
       </c>
       <c r="D42" s="34" t="n">
         <v>28.4781</v>
@@ -12004,10 +12004,10 @@
         <v>28.1691</v>
       </c>
       <c r="I42" s="34" t="n">
-        <v>16.1529</v>
+        <v>16.1531</v>
       </c>
       <c r="J42" s="34" t="n">
-        <v>22.6237</v>
+        <v>22.6238</v>
       </c>
       <c r="K42" s="34" t="n">
         <v>171.9871</v>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="C43" s="34" t="n">
-        <v>123.34</v>
+        <v>117.62</v>
       </c>
       <c r="D43" s="34" t="n">
-        <v>50.5477</v>
+        <v>50.5525</v>
       </c>
       <c r="E43" s="34" t="n">
         <v>50.2832</v>
@@ -12065,10 +12065,10 @@
         <v>38.8126</v>
       </c>
       <c r="I43" s="34" t="n">
-        <v>46.6002</v>
+        <v>46.6218</v>
       </c>
       <c r="J43" s="34" t="n">
-        <v>50.2357</v>
+        <v>50.2376</v>
       </c>
       <c r="K43" s="34" t="n">
         <v>57.5582</v>
@@ -12077,7 +12077,7 @@
         <v>39.5892</v>
       </c>
       <c r="M43" s="34" t="n">
-        <v>8.81</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N43" s="34" t="n">
         <v>8.9</v>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="Q43" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 4.64, "BVPS": 24.2184}, "graham_formula": {"g(上限10%)": 0.0526, "Y公司債": 0.04}, "ncav": {"NCAV/股": 12.9157, "NNWC/股": 4.1254, "net-net買點": 8.6148}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 1248793852.0, "g1": 0.0526, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 680214571.0}, "epv": {"常態營業利益率": 0.3374, "常態NOPAT": 2321531655.0, "WACC": 0.0881, "淨現金": 1080366024.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.0117, "永續g": 0.021, "目標營業利益率": 0.3374, "WACC": 0.0881, "終值WACC": 0.089, "有效稅率": 0.1604, "終值佔比": 0.485}, "ri_pb": {"常態ROE": 0.2115, "股權成本r": 0.089, "留存成長g": 0.0, "合理PB": 2.377}, "ddm": {"DPS": 3.2624, "g": 0.0061, "r": 0.089}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 4.64, "BVPS": 24.2184}, "graham_formula": {"g(上限10%)": 0.0526, "Y公司債": 0.04}, "ncav": {"NCAV/股": 12.9157, "NNWC/股": 4.1254, "net-net買點": 8.6148}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 1248793852.0, "g1": 0.0526, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 680214571.0}, "epv": {"常態營業利益率": 0.3374, "常態NOPAT": 2321531655.0, "WACC": 0.088, "淨現金": 1080366024.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.0117, "永續g": 0.021, "目標營業利益率": 0.3374, "WACC": 0.088, "終值WACC": 0.089, "有效稅率": 0.1604, "終值佔比": 0.485}, "ri_pb": {"常態ROE": 0.2115, "股權成本r": 0.089, "留存成長g": 0.0, "合理PB": 2.377}, "ddm": {"DPS": 3.2624, "g": 0.0061, "r": 0.089}}</t>
         </is>
       </c>
     </row>
@@ -12108,10 +12108,10 @@
         </is>
       </c>
       <c r="C44" s="34" t="n">
-        <v>1309.3</v>
+        <v>1268.64</v>
       </c>
       <c r="D44" s="34" t="n">
-        <v>1186.834</v>
+        <v>1186.8347</v>
       </c>
       <c r="E44" s="34" t="n">
         <v>544.9149</v>
@@ -12126,10 +12126,10 @@
         <v>869.8927</v>
       </c>
       <c r="I44" s="34" t="n">
-        <v>838.7822</v>
+        <v>838.7851000000001</v>
       </c>
       <c r="J44" s="34" t="n">
-        <v>1283.6279</v>
+        <v>1283.6283</v>
       </c>
       <c r="K44" s="34" t="n">
         <v>2189.9672</v>
@@ -12169,10 +12169,10 @@
         </is>
       </c>
       <c r="C45" s="34" t="n">
-        <v>27.87</v>
+        <v>28.31</v>
       </c>
       <c r="D45" s="34" t="n">
-        <v>20.5832</v>
+        <v>20.5703</v>
       </c>
       <c r="E45" s="34" t="n">
         <v>16.2467</v>
@@ -12185,10 +12185,10 @@
         <v>31.8328</v>
       </c>
       <c r="I45" s="34" t="n">
-        <v>15.6734</v>
+        <v>15.6134</v>
       </c>
       <c r="J45" s="34" t="n">
-        <v>12.7773</v>
+        <v>12.7748</v>
       </c>
       <c r="K45" s="34" t="n">
         <v>22.7622</v>
@@ -12197,7 +12197,7 @@
         <v>25.8636</v>
       </c>
       <c r="M45" s="34" t="n">
-        <v>5.62</v>
+        <v>5.63</v>
       </c>
       <c r="N45" s="34" t="n">
         <v>6.86</v>
@@ -12212,7 +12212,7 @@
       </c>
       <c r="Q45" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 1.3281, "BVPS": 8.8331}, "graham_formula": {"g(上限10%)": 0.0353, "Y公司債": 0.04}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -12.9023, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 45014393233.0, "g1": 0.0238, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 52328014359.0}, "epv": {"常態營業利益率": 0.4692, "常態NOPAT": 34008540377.0, "WACC": 0.0562, "淨現金": -273993253986.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.0779, "永續g": 0.021, "目標營業利益率": 0.4692, "WACC": 0.0562, "終值WACC": 0.089, "有效稅率": 0.1714, "終值佔比": 0.521}, "ri_pb": {"常態ROE": 0.1553, "股權成本r": 0.0686, "留存成長g": 0.0136, "合理PB": 2.577}, "ddm": {"DPS": 1.3682, "g": 0.0149, "r": 0.0686}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 1.3281, "BVPS": 8.8331}, "graham_formula": {"g(上限10%)": 0.0353, "Y公司債": 0.04}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -12.9023, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 45014393233.0, "g1": 0.0238, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 52328014359.0}, "epv": {"常態營業利益率": 0.4692, "常態NOPAT": 34008540377.0, "WACC": 0.0563, "淨現金": -273993253986.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.0779, "永續g": 0.021, "目標營業利益率": 0.4692, "WACC": 0.0563, "終值WACC": 0.089, "有效稅率": 0.1714, "終值佔比": 0.521}, "ri_pb": {"常態ROE": 0.1553, "股權成本r": 0.0686, "留存成長g": 0.0136, "合理PB": 2.577}, "ddm": {"DPS": 1.3682, "g": 0.0149, "r": 0.0686}}</t>
         </is>
       </c>
     </row>
@@ -12228,10 +12228,10 @@
         </is>
       </c>
       <c r="C46" s="34" t="n">
-        <v>64.75</v>
+        <v>64.2</v>
       </c>
       <c r="D46" s="34" t="n">
-        <v>35.7494</v>
+        <v>35.7515</v>
       </c>
       <c r="E46" s="34" t="n">
         <v>15.2693</v>
@@ -12246,10 +12246,10 @@
         <v>25.7507</v>
       </c>
       <c r="I46" s="34" t="n">
-        <v>25.4896</v>
+        <v>25.502</v>
       </c>
       <c r="J46" s="34" t="n">
-        <v>36.6829</v>
+        <v>36.6837</v>
       </c>
       <c r="K46" s="34" t="n">
         <v>164.8877</v>
@@ -12258,7 +12258,7 @@
         <v>130.8639</v>
       </c>
       <c r="M46" s="34" t="n">
-        <v>8.390000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="N46" s="34" t="n">
         <v>8.9</v>
@@ -12273,7 +12273,7 @@
       </c>
       <c r="Q46" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 1.17, "BVPS": 8.8567}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.04}, "ncav": {"NCAV/股": 6.0294, "NNWC/股": -2.245, "net-net買點": 4.0216}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 18769275000.0, "g1": 0.15, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 3053026900.0}, "epv": {"常態營業利益率": 0.0455, "常態NOPAT": 42806605742.0, "WACC": 0.0839, "淨現金": -7517740000.0}, "damodaran_fcff": {"銷售/資本": 4.0, "g1": 0.15, "永續g": 0.021, "目標營業利益率": 0.0455, "WACC": 0.0839, "終值WACC": 0.089, "有效稅率": 0.144, "終值佔比": 0.681}, "ri_pb": {"常態ROE": 0.1771, "股權成本r": 0.089, "留存成長g": 0.084, "合理PB": 18.617}, "ddm": {"DPS": 1.2128, "g": 0.079, "r": 0.089}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 1.17, "BVPS": 8.8567}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.04}, "ncav": {"NCAV/股": 6.0294, "NNWC/股": -2.245, "net-net買點": 4.0216}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 18769275000.0, "g1": 0.15, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 3053026900.0}, "epv": {"常態營業利益率": 0.0455, "常態NOPAT": 42806605742.0, "WACC": 0.0838, "淨現金": -7517740000.0}, "damodaran_fcff": {"銷售/資本": 4.0, "g1": 0.15, "永續g": 0.021, "目標營業利益率": 0.0455, "WACC": 0.0838, "終值WACC": 0.089, "有效稅率": 0.144, "終值佔比": 0.681}, "ri_pb": {"常態ROE": 0.1771, "股權成本r": 0.089, "留存成長g": 0.084, "合理PB": 18.617}, "ddm": {"DPS": 1.2128, "g": 0.079, "r": 0.089}}</t>
         </is>
       </c>
     </row>
@@ -12289,10 +12289,10 @@
         </is>
       </c>
       <c r="C47" s="34" t="n">
-        <v>61.96</v>
+        <v>57.6</v>
       </c>
       <c r="D47" s="34" t="n">
-        <v>100.9205</v>
+        <v>100.9378</v>
       </c>
       <c r="E47" s="34" t="n">
         <v>38.1089</v>
@@ -12307,10 +12307,10 @@
         <v>94.1225</v>
       </c>
       <c r="I47" s="34" t="n">
-        <v>56.3433</v>
+        <v>56.4344</v>
       </c>
       <c r="J47" s="34" t="n">
-        <v>92.6005</v>
+        <v>92.61150000000001</v>
       </c>
       <c r="K47" s="34" t="n">
         <v>442.9869</v>
@@ -12319,7 +12319,7 @@
         <v>89.2491</v>
       </c>
       <c r="M47" s="34" t="n">
-        <v>8.66</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="N47" s="34" t="n">
         <v>8.9</v>
@@ -12334,7 +12334,7 @@
       </c>
       <c r="Q47" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 3.81, "BVPS": 16.9413}, "graham_formula": {"g(上限10%)": 0.0996, "Y公司債": 0.04}, "ncav": {"NCAV/股": 10.3375, "NNWC/股": 5.9725, "net-net買點": 6.8951}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 1377017313.0, "g1": 0.15, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 4526443.0}, "epv": {"常態營業利益率": 0.1688, "常態NOPAT": 1546919867.0, "WACC": 0.0866, "淨現金": 4443223251.0}, "damodaran_fcff": {"銷售/資本": 4.0, "g1": 0.15, "永續g": 0.021, "目標營業利益率": 0.1688, "WACC": 0.0866, "終值WACC": 0.089, "有效稅率": 0.1361, "終值佔比": 0.551}, "ri_pb": {"常態ROE": 0.2147, "股權成本r": 0.089, "留存成長g": 0.084, "合理PB": 26.148}, "ddm": {"DPS": 0.8271, "g": 0.079, "r": 0.089}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 3.81, "BVPS": 16.9413}, "graham_formula": {"g(上限10%)": 0.0996, "Y公司債": 0.04}, "ncav": {"NCAV/股": 10.3375, "NNWC/股": 5.9725, "net-net買點": 6.8951}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 1377017313.0, "g1": 0.15, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 4526443.0}, "epv": {"常態營業利益率": 0.1688, "常態NOPAT": 1546919867.0, "WACC": 0.0864, "淨現金": 4443223251.0}, "damodaran_fcff": {"銷售/資本": 4.0, "g1": 0.15, "永續g": 0.021, "目標營業利益率": 0.1688, "WACC": 0.0864, "終值WACC": 0.089, "有效稅率": 0.1361, "終值佔比": 0.551}, "ri_pb": {"常態ROE": 0.2147, "股權成本r": 0.089, "留存成長g": 0.084, "合理PB": 26.148}, "ddm": {"DPS": 0.8271, "g": 0.079, "r": 0.089}}</t>
         </is>
       </c>
     </row>
@@ -12350,10 +12350,10 @@
         </is>
       </c>
       <c r="C48" s="34" t="n">
-        <v>81.33</v>
+        <v>84.91</v>
       </c>
       <c r="D48" s="34" t="n">
-        <v>113.1392</v>
+        <v>113.1304</v>
       </c>
       <c r="E48" s="34" t="n">
         <v>31.0139</v>
@@ -12368,10 +12368,10 @@
         <v>95.557</v>
       </c>
       <c r="I48" s="34" t="n">
-        <v>61.0883</v>
+        <v>61.0416</v>
       </c>
       <c r="J48" s="34" t="n">
-        <v>108.9394</v>
+        <v>108.9336</v>
       </c>
       <c r="K48" s="34" t="n">
         <v>698.9493</v>
@@ -12380,7 +12380,7 @@
         <v>323.4171</v>
       </c>
       <c r="M48" s="34" t="n">
-        <v>8.720000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="N48" s="34" t="n">
         <v>8.9</v>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="Q48" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 3.36, "BVPS": 12.7231}, "graham_formula": {"g(上限10%)": 0.0326, "Y公司債": 0.04}, "ncav": {"NCAV/股": 6.2142, "NNWC/股": -3.9602, "net-net買點": 4.1449}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 3183106255.0, "g1": 0.15, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 120943438.0}, "epv": {"常態營業利益率": 0.2949, "常態NOPAT": 4450246220.0, "WACC": 0.0872, "淨現金": 4017127052.0}, "damodaran_fcff": {"銷售/資本": 2.32, "g1": 0.15, "永續g": 0.021, "目標營業利益率": 0.2949, "WACC": 0.0872, "終值WACC": 0.089, "有效稅率": 0.1293, "終值佔比": 0.55}, "ri_pb": {"常態ROE": 0.3587, "股權成本r": 0.089, "留存成長g": 0.084, "合理PB": 54.936}, "ddm": {"DPS": 2.9974, "g": 0.079, "r": 0.089}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 3.36, "BVPS": 12.7231}, "graham_formula": {"g(上限10%)": 0.0326, "Y公司債": 0.04}, "ncav": {"NCAV/股": 6.2142, "NNWC/股": -3.9602, "net-net買點": 4.1449}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 3183106255.0, "g1": 0.15, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 120943438.0}, "epv": {"常態營業利益率": 0.2949, "常態NOPAT": 4450246220.0, "WACC": 0.0873, "淨現金": 4017127052.0}, "damodaran_fcff": {"銷售/資本": 2.32, "g1": 0.15, "永續g": 0.021, "目標營業利益率": 0.2949, "WACC": 0.0873, "終值WACC": 0.089, "有效稅率": 0.1293, "終值佔比": 0.55}, "ri_pb": {"常態ROE": 0.3587, "股權成本r": 0.089, "留存成長g": 0.084, "合理PB": 54.936}, "ddm": {"DPS": 2.9974, "g": 0.079, "r": 0.089}}</t>
         </is>
       </c>
     </row>
@@ -12411,10 +12411,10 @@
         </is>
       </c>
       <c r="C49" s="34" t="n">
-        <v>336.01</v>
+        <v>329.87</v>
       </c>
       <c r="D49" s="34" t="n">
-        <v>81.5857</v>
+        <v>81.58629999999999</v>
       </c>
       <c r="E49" s="34" t="n">
         <v>56.7199</v>
@@ -12429,10 +12429,10 @@
         <v>56.4053</v>
       </c>
       <c r="I49" s="34" t="n">
-        <v>81.3643</v>
+        <v>81.3681</v>
       </c>
       <c r="J49" s="34" t="n">
-        <v>120.5055</v>
+        <v>120.5058</v>
       </c>
       <c r="K49" s="34" t="n">
         <v>38.0978</v>
@@ -12472,7 +12472,7 @@
         </is>
       </c>
       <c r="C50" s="34" t="n">
-        <v>292.54</v>
+        <v>277.5</v>
       </c>
       <c r="D50" s="34" t="n">
         <v>10.4095</v>
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="C51" s="34" t="n">
-        <v>523.6799999999999</v>
+        <v>489.03</v>
       </c>
       <c r="D51" s="34" t="n">
         <v>6.6804</v>
@@ -12551,7 +12551,7 @@
         <v>8.4762</v>
       </c>
       <c r="I51" s="34" t="n">
-        <v>5.228</v>
+        <v>5.2281</v>
       </c>
       <c r="J51" s="34" t="n">
         <v>4.587</v>
@@ -13876,7 +13876,7 @@
         </is>
       </c>
       <c r="D2" s="24" t="n">
-        <v>164.9</v>
+        <v>162.4</v>
       </c>
       <c r="E2" s="24" t="n">
         <v>46.269</v>
@@ -13899,7 +13899,7 @@
         </is>
       </c>
       <c r="K2" s="24" t="n">
-        <v>1.782</v>
+        <v>1.755</v>
       </c>
       <c r="L2" s="24" t="n">
         <v>69.40349999999999</v>
@@ -13922,22 +13922,22 @@
         </is>
       </c>
       <c r="D3" s="29" t="n">
-        <v>5.38</v>
+        <v>5.43</v>
       </c>
       <c r="E3" s="29" t="n">
-        <v>1.9641</v>
+        <v>1.957</v>
       </c>
       <c r="F3" s="29" t="n">
-        <v>2.9462</v>
+        <v>2.9355</v>
       </c>
       <c r="G3" s="29" t="n">
-        <v>4.5175</v>
+        <v>4.5011</v>
       </c>
       <c r="H3" s="29" t="n">
-        <v>5.8924</v>
+        <v>5.871</v>
       </c>
       <c r="I3" s="29" t="n">
-        <v>5.8924</v>
+        <v>5.871</v>
       </c>
       <c r="J3" s="31" t="inlineStr">
         <is>
@@ -13945,10 +13945,10 @@
         </is>
       </c>
       <c r="K3" s="29" t="n">
-        <v>1.3696</v>
+        <v>1.3873</v>
       </c>
       <c r="L3" s="29" t="n">
-        <v>2.9462</v>
+        <v>2.9355</v>
       </c>
     </row>
     <row r="4">
@@ -13968,7 +13968,7 @@
         </is>
       </c>
       <c r="D4" s="24" t="n">
-        <v>1.365</v>
+        <v>1.285</v>
       </c>
       <c r="E4" s="24" t="n">
         <v>0.0481</v>
@@ -13991,7 +13991,7 @@
         </is>
       </c>
       <c r="K4" s="24" t="n">
-        <v>14.1797</v>
+        <v>13.3487</v>
       </c>
       <c r="L4" s="24" t="n">
         <v>0.0722</v>
@@ -14014,22 +14014,22 @@
         </is>
       </c>
       <c r="D5" s="14" t="n">
-        <v>85.15000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>53.5987</v>
+        <v>53.5906</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>80.398</v>
+        <v>80.38590000000001</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>123.277</v>
+        <v>123.2584</v>
       </c>
       <c r="H5" s="14" t="n">
-        <v>160.7961</v>
+        <v>160.7718</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>160.7961</v>
+        <v>160.7718</v>
       </c>
       <c r="J5" s="16" t="inlineStr">
         <is>
@@ -14037,10 +14037,10 @@
         </is>
       </c>
       <c r="K5" s="14" t="n">
-        <v>0.7943</v>
+        <v>0.8052</v>
       </c>
       <c r="L5" s="14" t="n">
-        <v>80.398</v>
+        <v>80.38590000000001</v>
       </c>
     </row>
     <row r="6">
@@ -14060,22 +14060,22 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>38.29</v>
+        <v>38.8</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>71.2718</v>
+        <v>71.2572</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>106.9078</v>
+        <v>106.8858</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>163.9252</v>
+        <v>163.8916</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>213.8155</v>
+        <v>213.7717</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>213.8155</v>
+        <v>213.7717</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
@@ -14083,10 +14083,10 @@
         </is>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.2686</v>
+        <v>0.2723</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>106.9078</v>
+        <v>106.8858</v>
       </c>
     </row>
     <row r="7">
@@ -14106,22 +14106,22 @@
         </is>
       </c>
       <c r="D7" s="19" t="n">
-        <v>30.18</v>
+        <v>28.92</v>
       </c>
       <c r="E7" s="19" t="n">
-        <v>11.5275</v>
+        <v>11.5307</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>17.2913</v>
+        <v>17.2961</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>26.5133</v>
+        <v>26.5207</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>34.5826</v>
+        <v>34.5922</v>
       </c>
       <c r="I7" s="19" t="n">
-        <v>34.5826</v>
+        <v>34.5922</v>
       </c>
       <c r="J7" s="21" t="inlineStr">
         <is>
@@ -14129,10 +14129,10 @@
         </is>
       </c>
       <c r="K7" s="19" t="n">
-        <v>1.309</v>
+        <v>1.254</v>
       </c>
       <c r="L7" s="19" t="n">
-        <v>17.2913</v>
+        <v>17.2961</v>
       </c>
     </row>
     <row r="8">
@@ -14152,22 +14152,22 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.395</v>
+        <v>1.315</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.8991</v>
+        <v>1.9004</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.8486</v>
+        <v>2.8506</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.3679</v>
+        <v>4.3709</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.6972</v>
+        <v>5.7011</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5.6972</v>
+        <v>5.7011</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
@@ -14175,10 +14175,10 @@
         </is>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.3673</v>
+        <v>0.346</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>2.8486</v>
+        <v>2.8506</v>
       </c>
     </row>
     <row r="9">
@@ -14198,22 +14198,22 @@
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>38.4</v>
+        <v>34.42</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>20.1309</v>
+        <v>20.424</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>30.1964</v>
+        <v>30.6361</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>46.3012</v>
+        <v>46.9753</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>60.3928</v>
+        <v>61.2721</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>60.3928</v>
+        <v>61.2721</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -14221,10 +14221,10 @@
         </is>
       </c>
       <c r="K9" s="14" t="n">
-        <v>0.9538</v>
+        <v>0.8426</v>
       </c>
       <c r="L9" s="14" t="n">
-        <v>30.1964</v>
+        <v>30.6361</v>
       </c>
     </row>
     <row r="10">
@@ -14244,22 +14244,22 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>4.915</v>
+        <v>4.795</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>4.5602</v>
+        <v>4.5643</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>6.8403</v>
+        <v>6.8465</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>10.4885</v>
+        <v>10.4979</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>13.6806</v>
+        <v>13.6929</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>13.6806</v>
+        <v>13.6929</v>
       </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
@@ -14267,10 +14267,10 @@
         </is>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.5389</v>
+        <v>0.5253</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>6.8403</v>
+        <v>6.8465</v>
       </c>
     </row>
     <row r="11">
@@ -14290,7 +14290,7 @@
         </is>
       </c>
       <c r="D11" s="24" t="n">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="E11" s="24" t="n">
         <v>78.36060000000001</v>
@@ -14313,7 +14313,7 @@
         </is>
       </c>
       <c r="K11" s="24" t="n">
-        <v>2.5651</v>
+        <v>2.4949</v>
       </c>
       <c r="L11" s="24" t="n">
         <v>117.5408</v>
@@ -14336,22 +14336,22 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>435.4</v>
+        <v>429.4</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>329.9132</v>
+        <v>329.9478</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>494.8698</v>
+        <v>494.9216</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>758.8003</v>
+        <v>758.8799</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>989.7395</v>
+        <v>989.8433</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>989.7395</v>
+        <v>989.8433</v>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
@@ -14359,10 +14359,10 @@
         </is>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.6599</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>494.8698</v>
+        <v>494.9216</v>
       </c>
     </row>
     <row r="13">
@@ -14382,22 +14382,22 @@
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>5.735</v>
+        <v>5.815</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>5.7324</v>
+        <v>5.7309</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>8.598599999999999</v>
+        <v>8.596399999999999</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>13.1846</v>
+        <v>13.1812</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>17.1973</v>
+        <v>17.1928</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>17.1973</v>
+        <v>17.1928</v>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
@@ -14405,10 +14405,10 @@
         </is>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.5002</v>
+        <v>0.5073</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>8.598599999999999</v>
+        <v>8.596399999999999</v>
       </c>
     </row>
     <row r="14">
@@ -14428,22 +14428,22 @@
         </is>
       </c>
       <c r="D14" s="14" t="n">
-        <v>9.145</v>
+        <v>8.994999999999999</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>5.5802</v>
+        <v>5.5846</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>8.370200000000001</v>
+        <v>8.376899999999999</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>12.8344</v>
+        <v>12.8445</v>
       </c>
       <c r="H14" s="14" t="n">
-        <v>16.7405</v>
+        <v>16.7537</v>
       </c>
       <c r="I14" s="14" t="n">
-        <v>16.7405</v>
+        <v>16.7537</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -14451,10 +14451,10 @@
         </is>
       </c>
       <c r="K14" s="14" t="n">
-        <v>0.8194</v>
+        <v>0.8053</v>
       </c>
       <c r="L14" s="14" t="n">
-        <v>8.370200000000001</v>
+        <v>8.376899999999999</v>
       </c>
     </row>
     <row r="15">
@@ -14474,7 +14474,7 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>18.9</v>
+        <v>18.68</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>26.704</v>
@@ -14497,7 +14497,7 @@
         </is>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.3539</v>
+        <v>0.3498</v>
       </c>
       <c r="L15" s="4" t="n">
         <v>40.056</v>
@@ -14520,22 +14520,22 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>10.35</v>
+        <v>10.07</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>11.2597</v>
+        <v>11.2646</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>16.8895</v>
+        <v>16.8969</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>25.8973</v>
+        <v>25.9086</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>33.7791</v>
+        <v>33.7938</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>33.7791</v>
+        <v>33.7938</v>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
@@ -14543,10 +14543,10 @@
         </is>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.4596</v>
+        <v>0.447</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>16.8895</v>
+        <v>16.8969</v>
       </c>
     </row>
     <row r="17">
@@ -14566,22 +14566,22 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>25.86</v>
+        <v>24.88</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>35.8612</v>
+        <v>35.8663</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>53.7918</v>
+        <v>53.7994</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>82.4807</v>
+        <v>82.4924</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>107.5835</v>
+        <v>107.5988</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>107.5835</v>
+        <v>107.5988</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
@@ -14589,10 +14589,10 @@
         </is>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.3606</v>
+        <v>0.3468</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>53.7918</v>
+        <v>53.7994</v>
       </c>
     </row>
     <row r="18">
@@ -14612,7 +14612,7 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>9.56</v>
+        <v>9.734999999999999</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>65.3927</v>
@@ -14635,7 +14635,7 @@
         </is>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.0731</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="L18" s="4" t="n">
         <v>98.0891</v>
@@ -14658,22 +14658,22 @@
         </is>
       </c>
       <c r="D19" s="14" t="n">
-        <v>78.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>44.8054</v>
+        <v>44.8062</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>67.2081</v>
+        <v>67.2093</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>103.0524</v>
+        <v>103.0542</v>
       </c>
       <c r="H19" s="14" t="n">
-        <v>134.4162</v>
+        <v>134.4185</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>134.4162</v>
+        <v>134.4185</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -14681,10 +14681,10 @@
         </is>
       </c>
       <c r="K19" s="14" t="n">
-        <v>0.8804999999999999</v>
+        <v>0.8782</v>
       </c>
       <c r="L19" s="14" t="n">
-        <v>67.2081</v>
+        <v>67.2093</v>
       </c>
     </row>
     <row r="20">
@@ -14704,7 +14704,7 @@
         </is>
       </c>
       <c r="D20" s="29" t="n">
-        <v>6.225</v>
+        <v>5.815</v>
       </c>
       <c r="E20" s="29" t="n">
         <v>79.02</v>
@@ -14727,7 +14727,7 @@
         </is>
       </c>
       <c r="K20" s="29" t="n">
-        <v>0.0394</v>
+        <v>0.0368</v>
       </c>
       <c r="L20" s="29" t="n">
         <v>102.726</v>
@@ -14750,22 +14750,22 @@
         </is>
       </c>
       <c r="D21" s="24" t="n">
-        <v>65.34999999999999</v>
+        <v>62.35</v>
       </c>
       <c r="E21" s="24" t="n">
-        <v>3.4605</v>
+        <v>3.4583</v>
       </c>
       <c r="F21" s="24" t="n">
-        <v>5.1907</v>
+        <v>5.1874</v>
       </c>
       <c r="G21" s="24" t="n">
-        <v>7.9591</v>
+        <v>7.9541</v>
       </c>
       <c r="H21" s="24" t="n">
-        <v>10.3814</v>
+        <v>10.3749</v>
       </c>
       <c r="I21" s="24" t="n">
-        <v>10.3814</v>
+        <v>10.3749</v>
       </c>
       <c r="J21" s="26" t="inlineStr">
         <is>
@@ -14773,10 +14773,10 @@
         </is>
       </c>
       <c r="K21" s="24" t="n">
-        <v>9.442399999999999</v>
+        <v>9.0146</v>
       </c>
       <c r="L21" s="24" t="n">
-        <v>5.1907</v>
+        <v>5.1874</v>
       </c>
     </row>
     <row r="22">
@@ -14796,22 +14796,22 @@
         </is>
       </c>
       <c r="D22" s="14" t="n">
-        <v>30.36</v>
+        <v>31.22</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>15.8145</v>
+        <v>15.8147</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>23.7218</v>
+        <v>23.7221</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>36.3734</v>
+        <v>36.3739</v>
       </c>
       <c r="H22" s="14" t="n">
-        <v>47.4435</v>
+        <v>47.4442</v>
       </c>
       <c r="I22" s="14" t="n">
-        <v>47.4435</v>
+        <v>47.4442</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -14819,10 +14819,10 @@
         </is>
       </c>
       <c r="K22" s="14" t="n">
-        <v>0.9599</v>
+        <v>0.9871</v>
       </c>
       <c r="L22" s="14" t="n">
-        <v>23.7218</v>
+        <v>23.7221</v>
       </c>
     </row>
     <row r="23">
@@ -14842,7 +14842,7 @@
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>7.51</v>
+        <v>7.565</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>49.2437</v>
@@ -14865,7 +14865,7 @@
         </is>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="L23" s="4" t="n">
         <v>73.8655</v>
@@ -14888,22 +14888,22 @@
         </is>
       </c>
       <c r="D24" s="14" t="n">
-        <v>26.92</v>
+        <v>26</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>14.3811</v>
+        <v>14.3826</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>21.5716</v>
+        <v>21.5739</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>33.0765</v>
+        <v>33.0799</v>
       </c>
       <c r="H24" s="14" t="n">
-        <v>43.1432</v>
+        <v>43.1477</v>
       </c>
       <c r="I24" s="14" t="n">
-        <v>43.1432</v>
+        <v>43.1477</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -14911,10 +14911,10 @@
         </is>
       </c>
       <c r="K24" s="14" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9039</v>
       </c>
       <c r="L24" s="14" t="n">
-        <v>21.5716</v>
+        <v>21.5739</v>
       </c>
     </row>
     <row r="25">
@@ -14934,7 +14934,7 @@
         </is>
       </c>
       <c r="D25" s="19" t="n">
-        <v>3.09</v>
+        <v>3.055</v>
       </c>
       <c r="E25" s="19" t="n">
         <v>1.1577</v>
@@ -14957,7 +14957,7 @@
         </is>
       </c>
       <c r="K25" s="19" t="n">
-        <v>1.3345</v>
+        <v>1.3194</v>
       </c>
       <c r="L25" s="19" t="n">
         <v>1.7366</v>
@@ -14980,7 +14980,7 @@
         </is>
       </c>
       <c r="D26" s="29" t="n">
-        <v>0.2</v>
+        <v>0.173</v>
       </c>
       <c r="E26" s="29" t="inlineStr"/>
       <c r="F26" s="29" t="inlineStr"/>
@@ -15012,7 +15012,7 @@
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>55.25</v>
+        <v>53.5</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>349.8471</v>
@@ -15035,7 +15035,7 @@
         </is>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.079</v>
+        <v>0.0765</v>
       </c>
       <c r="L27" s="4" t="n">
         <v>524.7707</v>
@@ -15058,22 +15058,22 @@
         </is>
       </c>
       <c r="D28" s="24" t="n">
-        <v>195.4</v>
+        <v>188.9</v>
       </c>
       <c r="E28" s="24" t="n">
-        <v>51.7059</v>
+        <v>51.6526</v>
       </c>
       <c r="F28" s="24" t="n">
-        <v>77.55880000000001</v>
+        <v>77.4789</v>
       </c>
       <c r="G28" s="24" t="n">
-        <v>118.9235</v>
+        <v>118.801</v>
       </c>
       <c r="H28" s="24" t="n">
-        <v>155.1176</v>
+        <v>154.9578</v>
       </c>
       <c r="I28" s="24" t="n">
-        <v>155.1176</v>
+        <v>154.9578</v>
       </c>
       <c r="J28" s="26" t="inlineStr">
         <is>
@@ -15081,10 +15081,10 @@
         </is>
       </c>
       <c r="K28" s="24" t="n">
-        <v>1.8895</v>
+        <v>1.8286</v>
       </c>
       <c r="L28" s="24" t="n">
-        <v>77.55880000000001</v>
+        <v>77.4789</v>
       </c>
     </row>
     <row r="29">
@@ -15104,22 +15104,22 @@
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.545</v>
+        <v>3.33</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>6.6211</v>
+        <v>6.6214</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>9.931699999999999</v>
+        <v>9.9321</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>15.2286</v>
+        <v>15.2292</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>19.8634</v>
+        <v>19.8641</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>19.8634</v>
+        <v>19.8641</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
@@ -15127,10 +15127,10 @@
         </is>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.2677</v>
+        <v>0.2515</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>9.931699999999999</v>
+        <v>9.9321</v>
       </c>
     </row>
     <row r="30">
@@ -15150,22 +15150,22 @@
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>51.4</v>
+        <v>50.05</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>42.014</v>
+        <v>42.0645</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>63.0209</v>
+        <v>63.0967</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>96.63209999999999</v>
+        <v>96.7483</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>126.0419</v>
+        <v>126.1934</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>126.0419</v>
+        <v>126.1934</v>
       </c>
       <c r="J30" s="11" t="inlineStr">
         <is>
@@ -15173,10 +15173,10 @@
         </is>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.6117</v>
+        <v>0.5949</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>63.0209</v>
+        <v>63.0967</v>
       </c>
     </row>
     <row r="31">
@@ -15196,7 +15196,7 @@
         </is>
       </c>
       <c r="D31" s="24" t="n">
-        <v>80.59999999999999</v>
+        <v>73.95</v>
       </c>
       <c r="E31" s="24" t="n">
         <v>6.9808</v>
@@ -15219,7 +15219,7 @@
         </is>
       </c>
       <c r="K31" s="24" t="n">
-        <v>5.7729</v>
+        <v>5.2966</v>
       </c>
       <c r="L31" s="24" t="n">
         <v>10.4713</v>
@@ -15242,22 +15242,22 @@
         </is>
       </c>
       <c r="D32" s="19" t="n">
-        <v>562</v>
+        <v>543.5</v>
       </c>
       <c r="E32" s="19" t="n">
-        <v>191.2572</v>
+        <v>191.3002</v>
       </c>
       <c r="F32" s="19" t="n">
-        <v>286.8858</v>
+        <v>286.9503</v>
       </c>
       <c r="G32" s="19" t="n">
-        <v>439.8915</v>
+        <v>439.9904</v>
       </c>
       <c r="H32" s="19" t="n">
-        <v>573.7714999999999</v>
+        <v>573.9005</v>
       </c>
       <c r="I32" s="19" t="n">
-        <v>573.7714999999999</v>
+        <v>573.9005</v>
       </c>
       <c r="J32" s="21" t="inlineStr">
         <is>
@@ -15265,10 +15265,10 @@
         </is>
       </c>
       <c r="K32" s="19" t="n">
-        <v>1.4692</v>
+        <v>1.4205</v>
       </c>
       <c r="L32" s="19" t="n">
-        <v>286.8858</v>
+        <v>286.9503</v>
       </c>
     </row>
     <row r="33">
@@ -15288,7 +15288,7 @@
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>51.9</v>
+        <v>51.65</v>
       </c>
       <c r="E33" s="4" t="n">
         <v>294.269</v>
@@ -15311,7 +15311,7 @@
         </is>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.0882</v>
+        <v>0.0878</v>
       </c>
       <c r="L33" s="4" t="n">
         <v>441.4036</v>
@@ -15334,22 +15334,22 @@
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>4.48</v>
+        <v>4.35</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>4.151</v>
+        <v>4.1513</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>6.2265</v>
+        <v>6.2269</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>9.5473</v>
+        <v>9.5479</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>12.453</v>
+        <v>12.4538</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>12.453</v>
+        <v>12.4538</v>
       </c>
       <c r="J34" s="11" t="inlineStr">
         <is>
@@ -15357,10 +15357,10 @@
         </is>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.5396</v>
+        <v>0.5239</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>6.2265</v>
+        <v>6.2269</v>
       </c>
     </row>
     <row r="35">
@@ -15380,22 +15380,22 @@
         </is>
       </c>
       <c r="D35" s="24" t="n">
-        <v>23.2</v>
+        <v>22.86</v>
       </c>
       <c r="E35" s="24" t="n">
-        <v>6.2165</v>
+        <v>6.2173</v>
       </c>
       <c r="F35" s="24" t="n">
-        <v>9.3247</v>
+        <v>9.326000000000001</v>
       </c>
       <c r="G35" s="24" t="n">
-        <v>14.2979</v>
+        <v>14.2998</v>
       </c>
       <c r="H35" s="24" t="n">
-        <v>18.6495</v>
+        <v>18.6519</v>
       </c>
       <c r="I35" s="24" t="n">
-        <v>18.6495</v>
+        <v>18.6519</v>
       </c>
       <c r="J35" s="26" t="inlineStr">
         <is>
@@ -15403,10 +15403,10 @@
         </is>
       </c>
       <c r="K35" s="24" t="n">
-        <v>1.866</v>
+        <v>1.8384</v>
       </c>
       <c r="L35" s="24" t="n">
-        <v>9.3247</v>
+        <v>9.326000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -15426,22 +15426,22 @@
         </is>
       </c>
       <c r="D36" s="14" t="n">
-        <v>108.6</v>
+        <v>105</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>68.1003</v>
+        <v>68.08499999999999</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>102.1504</v>
+        <v>102.1276</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>156.6307</v>
+        <v>156.5956</v>
       </c>
       <c r="H36" s="14" t="n">
-        <v>204.3008</v>
+        <v>204.2551</v>
       </c>
       <c r="I36" s="14" t="n">
-        <v>204.3008</v>
+        <v>204.2551</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -15449,56 +15449,56 @@
         </is>
       </c>
       <c r="K36" s="14" t="n">
-        <v>0.7974</v>
+        <v>0.7711</v>
       </c>
       <c r="L36" s="14" t="n">
-        <v>102.1504</v>
+        <v>102.1276</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>09961</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>携程集团-S</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>HKD</t>
         </is>
       </c>
-      <c r="D37" s="14" t="n">
-        <v>324.2</v>
-      </c>
-      <c r="E37" s="14" t="n">
-        <v>215.3236</v>
-      </c>
-      <c r="F37" s="14" t="n">
-        <v>322.9854</v>
-      </c>
-      <c r="G37" s="14" t="n">
-        <v>495.2443</v>
-      </c>
-      <c r="H37" s="14" t="n">
-        <v>645.9708000000001</v>
-      </c>
-      <c r="I37" s="14" t="n">
-        <v>645.9708000000001</v>
-      </c>
-      <c r="J37" s="16" t="inlineStr">
-        <is>
-          <t>合理</t>
-        </is>
-      </c>
-      <c r="K37" s="14" t="n">
-        <v>0.7528</v>
-      </c>
-      <c r="L37" s="14" t="n">
-        <v>322.9854</v>
+      <c r="D37" s="9" t="n">
+        <v>304.8</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>215.4637</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>323.1955</v>
+      </c>
+      <c r="G37" s="9" t="n">
+        <v>495.5665</v>
+      </c>
+      <c r="H37" s="9" t="n">
+        <v>646.391</v>
+      </c>
+      <c r="I37" s="9" t="n">
+        <v>646.391</v>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>便宜</t>
+        </is>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>0.7073</v>
+      </c>
+      <c r="L37" s="9" t="n">
+        <v>323.1955</v>
       </c>
     </row>
     <row r="38">
@@ -15518,22 +15518,22 @@
         </is>
       </c>
       <c r="D38" s="24" t="n">
-        <v>109.5</v>
+        <v>105.8</v>
       </c>
       <c r="E38" s="24" t="n">
-        <v>34.079</v>
+        <v>34.0917</v>
       </c>
       <c r="F38" s="24" t="n">
-        <v>51.1184</v>
+        <v>51.1376</v>
       </c>
       <c r="G38" s="24" t="n">
-        <v>78.38160000000001</v>
+        <v>78.411</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>102.2369</v>
+        <v>102.2752</v>
       </c>
       <c r="I38" s="24" t="n">
-        <v>102.2369</v>
+        <v>102.2752</v>
       </c>
       <c r="J38" s="26" t="inlineStr">
         <is>
@@ -15541,10 +15541,10 @@
         </is>
       </c>
       <c r="K38" s="24" t="n">
-        <v>1.6066</v>
+        <v>1.5517</v>
       </c>
       <c r="L38" s="24" t="n">
-        <v>51.1184</v>
+        <v>51.1376</v>
       </c>
     </row>
     <row r="39">
@@ -15564,22 +15564,22 @@
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>188.2</v>
+        <v>182</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>150.0665</v>
+        <v>150.0722</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>225.0998</v>
+        <v>225.1083</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>345.153</v>
+        <v>345.1661</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>450.1995</v>
+        <v>450.2166</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>450.1995</v>
+        <v>450.2166</v>
       </c>
       <c r="J39" s="11" t="inlineStr">
         <is>
@@ -15587,10 +15587,10 @@
         </is>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.6271</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>225.0998</v>
+        <v>225.1083</v>
       </c>
     </row>
     <row r="40">
@@ -15610,22 +15610,22 @@
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>87.84999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>63.1801</v>
+        <v>63.1856</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>94.7702</v>
+        <v>94.77849999999999</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>145.3143</v>
+        <v>145.327</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>189.5404</v>
+        <v>189.5569</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>189.5404</v>
+        <v>189.5569</v>
       </c>
       <c r="J40" s="11" t="inlineStr">
         <is>
@@ -15633,10 +15633,10 @@
         </is>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.6952</v>
+        <v>0.6718</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>94.7702</v>
+        <v>94.77849999999999</v>
       </c>
     </row>
     <row r="41">
@@ -15656,22 +15656,22 @@
         </is>
       </c>
       <c r="D41" s="14" t="n">
-        <v>169.95</v>
+        <v>163.23</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>100.1499</v>
+        <v>100.1504</v>
       </c>
       <c r="F41" s="14" t="n">
-        <v>150.2249</v>
+        <v>150.2257</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>230.3448</v>
+        <v>230.346</v>
       </c>
       <c r="H41" s="14" t="n">
-        <v>300.4498</v>
+        <v>300.4513</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>300.4498</v>
+        <v>300.4513</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -15679,55 +15679,55 @@
         </is>
       </c>
       <c r="K41" s="14" t="n">
-        <v>0.8485</v>
+        <v>0.8149</v>
       </c>
       <c r="L41" s="14" t="n">
-        <v>150.2249</v>
+        <v>150.2257</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="22" t="inlineStr">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>600276</t>
         </is>
       </c>
-      <c r="B42" s="23" t="inlineStr">
+      <c r="B42" s="18" t="inlineStr">
         <is>
           <t>恒瑞医药</t>
         </is>
       </c>
-      <c r="C42" s="22" t="inlineStr">
+      <c r="C42" s="17" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="D42" s="24" t="n">
-        <v>45.71</v>
-      </c>
-      <c r="E42" s="24" t="n">
-        <v>14.239</v>
-      </c>
-      <c r="F42" s="24" t="n">
+      <c r="D42" s="19" t="n">
+        <v>42.19</v>
+      </c>
+      <c r="E42" s="19" t="n">
+        <v>14.2391</v>
+      </c>
+      <c r="F42" s="19" t="n">
         <v>21.3586</v>
       </c>
-      <c r="G42" s="24" t="n">
+      <c r="G42" s="19" t="n">
         <v>32.7498</v>
       </c>
-      <c r="H42" s="24" t="n">
-        <v>42.7171</v>
-      </c>
-      <c r="I42" s="24" t="n">
-        <v>42.7171</v>
-      </c>
-      <c r="J42" s="26" t="inlineStr">
-        <is>
-          <t>非常昂貴</t>
-        </is>
-      </c>
-      <c r="K42" s="24" t="n">
-        <v>1.6051</v>
-      </c>
-      <c r="L42" s="24" t="n">
+      <c r="H42" s="19" t="n">
+        <v>42.7172</v>
+      </c>
+      <c r="I42" s="19" t="n">
+        <v>42.7172</v>
+      </c>
+      <c r="J42" s="21" t="inlineStr">
+        <is>
+          <t>昂貴</t>
+        </is>
+      </c>
+      <c r="K42" s="19" t="n">
+        <v>1.4815</v>
+      </c>
+      <c r="L42" s="19" t="n">
         <v>21.3586</v>
       </c>
     </row>
@@ -15748,22 +15748,22 @@
         </is>
       </c>
       <c r="D43" s="24" t="n">
-        <v>123.34</v>
+        <v>117.62</v>
       </c>
       <c r="E43" s="24" t="n">
-        <v>25.2739</v>
+        <v>25.2763</v>
       </c>
       <c r="F43" s="24" t="n">
-        <v>37.9108</v>
+        <v>37.9144</v>
       </c>
       <c r="G43" s="24" t="n">
-        <v>58.1299</v>
+        <v>58.1354</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>75.8216</v>
+        <v>75.8288</v>
       </c>
       <c r="I43" s="24" t="n">
-        <v>75.8216</v>
+        <v>75.8288</v>
       </c>
       <c r="J43" s="26" t="inlineStr">
         <is>
@@ -15771,10 +15771,10 @@
         </is>
       </c>
       <c r="K43" s="24" t="n">
-        <v>2.4401</v>
+        <v>2.3267</v>
       </c>
       <c r="L43" s="24" t="n">
-        <v>37.9108</v>
+        <v>37.9144</v>
       </c>
     </row>
     <row r="44">
@@ -15794,22 +15794,22 @@
         </is>
       </c>
       <c r="D44" s="14" t="n">
-        <v>1309.3</v>
+        <v>1268.64</v>
       </c>
       <c r="E44" s="14" t="n">
-        <v>593.417</v>
+        <v>593.4174</v>
       </c>
       <c r="F44" s="14" t="n">
-        <v>890.1255</v>
+        <v>890.126</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>1364.8591</v>
+        <v>1364.8599</v>
       </c>
       <c r="H44" s="14" t="n">
-        <v>1780.2511</v>
+        <v>1780.2521</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>1780.2511</v>
+        <v>1780.2521</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -15817,10 +15817,10 @@
         </is>
       </c>
       <c r="K44" s="14" t="n">
-        <v>1.1032</v>
+        <v>1.0689</v>
       </c>
       <c r="L44" s="14" t="n">
-        <v>890.1255</v>
+        <v>890.126</v>
       </c>
     </row>
     <row r="45">
@@ -15840,22 +15840,22 @@
         </is>
       </c>
       <c r="D45" s="19" t="n">
-        <v>27.87</v>
+        <v>28.31</v>
       </c>
       <c r="E45" s="19" t="n">
-        <v>10.2916</v>
+        <v>10.2852</v>
       </c>
       <c r="F45" s="19" t="n">
-        <v>15.4374</v>
+        <v>15.4277</v>
       </c>
       <c r="G45" s="19" t="n">
-        <v>23.6707</v>
+        <v>23.6558</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>30.8748</v>
+        <v>30.8555</v>
       </c>
       <c r="I45" s="19" t="n">
-        <v>30.8748</v>
+        <v>30.8555</v>
       </c>
       <c r="J45" s="21" t="inlineStr">
         <is>
@@ -15863,10 +15863,10 @@
         </is>
       </c>
       <c r="K45" s="19" t="n">
-        <v>1.354</v>
+        <v>1.3763</v>
       </c>
       <c r="L45" s="19" t="n">
-        <v>15.4374</v>
+        <v>15.4277</v>
       </c>
     </row>
     <row r="46">
@@ -15886,22 +15886,22 @@
         </is>
       </c>
       <c r="D46" s="24" t="n">
-        <v>64.75</v>
+        <v>64.2</v>
       </c>
       <c r="E46" s="24" t="n">
-        <v>17.8747</v>
+        <v>17.8758</v>
       </c>
       <c r="F46" s="24" t="n">
-        <v>26.8121</v>
+        <v>26.8137</v>
       </c>
       <c r="G46" s="24" t="n">
-        <v>41.1119</v>
+        <v>41.1143</v>
       </c>
       <c r="H46" s="24" t="n">
-        <v>53.6242</v>
+        <v>53.6273</v>
       </c>
       <c r="I46" s="24" t="n">
-        <v>53.6242</v>
+        <v>53.6273</v>
       </c>
       <c r="J46" s="26" t="inlineStr">
         <is>
@@ -15909,10 +15909,10 @@
         </is>
       </c>
       <c r="K46" s="24" t="n">
-        <v>1.8112</v>
+        <v>1.7957</v>
       </c>
       <c r="L46" s="24" t="n">
-        <v>26.8121</v>
+        <v>26.8137</v>
       </c>
     </row>
     <row r="47">
@@ -15932,22 +15932,22 @@
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>61.96</v>
+        <v>57.6</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>50.4603</v>
+        <v>50.4689</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>75.6904</v>
+        <v>75.7033</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>116.0586</v>
+        <v>116.0784</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>151.3808</v>
+        <v>151.4066</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>151.3808</v>
+        <v>151.4066</v>
       </c>
       <c r="J47" s="11" t="inlineStr">
         <is>
@@ -15955,56 +15955,56 @@
         </is>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.6139</v>
+        <v>0.5706</v>
       </c>
       <c r="L47" s="9" t="n">
-        <v>75.6904</v>
+        <v>75.7033</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t>605117</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="13" t="inlineStr">
         <is>
           <t>德业股份</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C48" s="12" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="D48" s="9" t="n">
-        <v>81.33</v>
-      </c>
-      <c r="E48" s="9" t="n">
-        <v>56.5696</v>
-      </c>
-      <c r="F48" s="9" t="n">
-        <v>84.8544</v>
-      </c>
-      <c r="G48" s="9" t="n">
-        <v>130.1101</v>
-      </c>
-      <c r="H48" s="9" t="n">
-        <v>169.7088</v>
-      </c>
-      <c r="I48" s="9" t="n">
-        <v>169.7088</v>
-      </c>
-      <c r="J48" s="11" t="inlineStr">
-        <is>
-          <t>便宜</t>
-        </is>
-      </c>
-      <c r="K48" s="9" t="n">
-        <v>0.7188</v>
-      </c>
-      <c r="L48" s="9" t="n">
-        <v>84.8544</v>
+      <c r="D48" s="14" t="n">
+        <v>84.91</v>
+      </c>
+      <c r="E48" s="14" t="n">
+        <v>56.5652</v>
+      </c>
+      <c r="F48" s="14" t="n">
+        <v>84.84780000000001</v>
+      </c>
+      <c r="G48" s="14" t="n">
+        <v>130.0999</v>
+      </c>
+      <c r="H48" s="14" t="n">
+        <v>169.6955</v>
+      </c>
+      <c r="I48" s="14" t="n">
+        <v>169.6955</v>
+      </c>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>合理</t>
+        </is>
+      </c>
+      <c r="K48" s="14" t="n">
+        <v>0.7506</v>
+      </c>
+      <c r="L48" s="14" t="n">
+        <v>84.84780000000001</v>
       </c>
     </row>
     <row r="49">
@@ -16024,22 +16024,22 @@
         </is>
       </c>
       <c r="D49" s="24" t="n">
-        <v>336.01</v>
+        <v>329.87</v>
       </c>
       <c r="E49" s="24" t="n">
-        <v>40.7928</v>
+        <v>40.7932</v>
       </c>
       <c r="F49" s="24" t="n">
-        <v>61.1893</v>
+        <v>61.1898</v>
       </c>
       <c r="G49" s="24" t="n">
-        <v>93.8235</v>
+        <v>93.82429999999999</v>
       </c>
       <c r="H49" s="24" t="n">
-        <v>122.3785</v>
+        <v>122.3795</v>
       </c>
       <c r="I49" s="24" t="n">
-        <v>122.3785</v>
+        <v>122.3795</v>
       </c>
       <c r="J49" s="26" t="inlineStr">
         <is>
@@ -16047,10 +16047,10 @@
         </is>
       </c>
       <c r="K49" s="24" t="n">
-        <v>4.1185</v>
+        <v>4.0432</v>
       </c>
       <c r="L49" s="24" t="n">
-        <v>61.1893</v>
+        <v>61.1898</v>
       </c>
     </row>
     <row r="50">
@@ -16070,7 +16070,7 @@
         </is>
       </c>
       <c r="D50" s="24" t="n">
-        <v>292.54</v>
+        <v>277.5</v>
       </c>
       <c r="E50" s="24" t="n">
         <v>5.2047</v>
@@ -16093,7 +16093,7 @@
         </is>
       </c>
       <c r="K50" s="24" t="n">
-        <v>28.1032</v>
+        <v>26.6583</v>
       </c>
       <c r="L50" s="24" t="n">
         <v>7.8071</v>
@@ -16116,7 +16116,7 @@
         </is>
       </c>
       <c r="D51" s="24" t="n">
-        <v>523.6799999999999</v>
+        <v>489.03</v>
       </c>
       <c r="E51" s="24" t="n">
         <v>3.3402</v>
@@ -16139,7 +16139,7 @@
         </is>
       </c>
       <c r="K51" s="24" t="n">
-        <v>78.39</v>
+        <v>73.2032</v>
       </c>
       <c r="L51" s="24" t="n">
         <v>5.0103</v>
@@ -24283,7 +24283,7 @@
         </is>
       </c>
       <c r="G9" s="12" t="n">
-        <v>81.8</v>
+        <v>82</v>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>93.09999999999999</v>
+        <v>93</v>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         </is>
       </c>
       <c r="G14" s="12" t="n">
-        <v>83.40000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
@@ -25878,58 +25878,58 @@
       </c>
     </row>
     <row r="37" ht="118" customHeight="1">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>09961</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>携程集团-S</t>
         </is>
       </c>
-      <c r="C37" s="12" t="n">
+      <c r="C37" s="7" t="n">
         <v>7.5</v>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>★★★★☆</t>
         </is>
       </c>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>便宜</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>合理</t>
         </is>
       </c>
-      <c r="F37" s="12" t="inlineStr">
-        <is>
-          <t>合理</t>
-        </is>
-      </c>
-      <c r="G37" s="12" t="n">
+      <c r="G37" s="7" t="n">
         <v>89.2</v>
       </c>
-      <c r="H37" s="13" t="inlineStr">
+      <c r="H37" s="8" t="inlineStr">
         <is>
           <t>毛利率89.71%、淨現金496億，ROIC 11.73% ROE不穩</t>
         </is>
       </c>
-      <c r="I37" s="13" t="inlineStr">
+      <c r="I37" s="8" t="inlineStr">
         <is>
           <t>獲利品質優異，TTM淨利率54.33%、自由現金流率23.41%，業主盈餘19034百萬CNY支撐再投資能力；資產負債穩健，負債權益比0.19、利息保障倍數23.83倍，淨現金49645百萬CNY降低財務風險。成長動能強勁，營收CAGR_3年47.37%，但ROE穩定度0顯示波動大，ROE(10年中位)僅4.03%反映獲利不穩。估值模型加權內在價值430.65 HKD，現價324.2 HKD對應價格/內在價值0.75，未達安全邊際MOS 0.25（安全買點322.99 HKD）。結論：財務體質強但成長可持續性待驗證，建議密切觀察營業利益率27.85%及ROIC 11.73%能否維持，若營收CAGR_3年回落至20%以下需重新評估。</t>
         </is>
       </c>
-      <c r="J37" s="13" t="inlineStr">
+      <c r="J37" s="8" t="inlineStr">
         <is>
           <t>ROE波動大(10年中位4.03%) / 成長放緩風險 / 匯率轉換影響</t>
         </is>
       </c>
-      <c r="K37" s="12" t="inlineStr">
+      <c r="K37" s="7" t="inlineStr">
         <is>
           <t>qwen-plus</t>
         </is>
       </c>
-      <c r="L37" s="12" t="inlineStr">
+      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
@@ -26168,58 +26168,58 @@
       </c>
     </row>
     <row r="42" ht="118" customHeight="1">
-      <c r="A42" s="22" t="inlineStr">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>600276</t>
         </is>
       </c>
-      <c r="B42" s="23" t="inlineStr">
+      <c r="B42" s="18" t="inlineStr">
         <is>
           <t>恒瑞医药</t>
         </is>
       </c>
-      <c r="C42" s="22" t="n">
+      <c r="C42" s="17" t="n">
         <v>4.2</v>
       </c>
-      <c r="D42" s="22" t="inlineStr">
+      <c r="D42" s="17" t="inlineStr">
         <is>
           <t>★★☆☆☆</t>
         </is>
       </c>
-      <c r="E42" s="26" t="inlineStr">
+      <c r="E42" s="21" t="inlineStr">
+        <is>
+          <t>昂貴</t>
+        </is>
+      </c>
+      <c r="F42" s="17" t="inlineStr">
         <is>
           <t>非常昂貴</t>
         </is>
       </c>
-      <c r="F42" s="22" t="inlineStr">
-        <is>
-          <t>非常昂貴</t>
-        </is>
-      </c>
-      <c r="G42" s="22" t="n">
+      <c r="G42" s="17" t="n">
         <v>95.90000000000001</v>
       </c>
-      <c r="H42" s="23" t="inlineStr">
+      <c r="H42" s="18" t="inlineStr">
         <is>
           <t>高毛利率86%、淨現金386億，ROIC 31%但ROE下滑至12%。</t>
         </is>
       </c>
-      <c r="I42" s="23" t="inlineStr">
+      <c r="I42" s="18" t="inlineStr">
         <is>
           <t>獲利品質優異，TTM毛利率86.08%、自由現金流率18.04%，經營現金流強勁支撐營運。資產負債極穩健，負債佔資產僅8.17%，流動比率11.68，淨現金386.66億，無償債風險。成長動能放緩，營收3年CAGR 14.13%但5年CAGR僅2.66%，ROE(TTM)11.99%低於10年中位17.25%，再投資報酬趨緩。估值模型顯示價格/內在價值1.6051倍，安全買點21.36元，現價45.71元嚴重高估。結論：財務體質佳但價格昂貴，建議等待安全邊際達25%以上，密切觀察營收CAGR_3年與ROE恢復情況。</t>
         </is>
       </c>
-      <c r="J42" s="23" t="inlineStr">
+      <c r="J42" s="18" t="inlineStr">
         <is>
           <t>ROE下滑至12%，低於歷史中位17.25% / 營收5年CAGR僅2.66%，增長放緩 / 估值昂貴，價格/內在價值1.61倍</t>
         </is>
       </c>
-      <c r="K42" s="22" t="inlineStr">
+      <c r="K42" s="17" t="inlineStr">
         <is>
           <t>qwen-plus</t>
         </is>
       </c>
-      <c r="L42" s="22" t="inlineStr">
+      <c r="L42" s="17" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
@@ -26516,58 +26516,58 @@
       </c>
     </row>
     <row r="48" ht="118" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t>605117</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="13" t="inlineStr">
         <is>
           <t>德业股份</t>
         </is>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="12" t="n">
         <v>8.9</v>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D48" s="12" t="inlineStr">
         <is>
           <t>★★★★☆</t>
         </is>
       </c>
-      <c r="E48" s="11" t="inlineStr">
+      <c r="E48" s="16" t="inlineStr">
+        <is>
+          <t>合理</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="inlineStr">
         <is>
           <t>便宜</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>便宜</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="n">
+      <c r="G48" s="12" t="n">
         <v>91.5</v>
       </c>
-      <c r="H48" s="8" t="inlineStr">
+      <c r="H48" s="13" t="inlineStr">
         <is>
           <t>ROE中位35.87%、毛利率38.04%、負債權益比0.175924（規則式）</t>
         </is>
       </c>
-      <c r="I48" s="8" t="inlineStr">
+      <c r="I48" s="13" t="inlineStr">
         <is>
           <t>【規則式後備結論，未經 AI】依現有財報：獲利連續性 10/10，ROE 十年中位 35.87%，毛利率 38.04%，負債權益比 0.175924，流動比率 1.470908，利息保障 103.059121。多模型加權內在價值 113.1392，區間 55.5052~108.9394，現價/內在價值 0.7188，判定為「便宜」，估值信心 91.5/100，格雷厄姆檢查通過 3/7 項。請以此為基礎自行覆核假設，特別是成長率、營業利益率與折現率三個敏感變數。</t>
         </is>
       </c>
-      <c r="J48" s="8" t="inlineStr">
+      <c r="J48" s="13" t="inlineStr">
         <is>
           <t>未經 AI 覆核 / 模型假設敏感 / 資料完整度</t>
         </is>
       </c>
-      <c r="K48" s="7" t="inlineStr">
+      <c r="K48" s="12" t="inlineStr">
         <is>
           <t>qwen-plus</t>
         </is>
       </c>
-      <c r="L48" s="7" t="inlineStr">
+      <c r="L48" s="12" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>

--- a/docs/reports/內在價值報告_20260911.xlsx
+++ b/docs/reports/內在價值報告_20260911.xlsx
@@ -829,25 +829,25 @@
       </c>
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="4" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>13.2428</v>
+        <v>13.2429</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>6.861</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>11.2318</v>
+        <v>11.2319</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>-74.90000000000001</v>
+        <v>-75.3</v>
       </c>
       <c r="M2" s="5" t="n">
         <v>25</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>9.9321</v>
+        <v>9.9322</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
       </c>
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="4" t="n">
-        <v>38.8</v>
+        <v>38.74</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>142.5145</v>
+        <v>142.5179</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>55.8024</v>
@@ -1091,7 +1091,7 @@
         <v>25</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>106.8858</v>
+        <v>106.8884</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -1191,25 +1191,25 @@
       </c>
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="4" t="n">
-        <v>1.315</v>
+        <v>1.305</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>3.8007</v>
+        <v>3.8011</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>2.2071</v>
+        <v>2.2072</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>2.9007</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>-65.40000000000001</v>
+        <v>-65.7</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>25</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>2.8506</v>
+        <v>2.8508</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="4" t="n">
-        <v>18.68</v>
+        <v>18.78</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>53.4079</v>
@@ -1325,7 +1325,7 @@
         <v>62.7</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>-65</v>
+        <v>-64.8</v>
       </c>
       <c r="M6" s="5" t="n">
         <v>25</v>
@@ -1431,10 +1431,10 @@
       </c>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="4" t="n">
-        <v>10.07</v>
+        <v>9.98</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>22.5292</v>
+        <v>22.5324</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>12.6307</v>
@@ -1443,13 +1443,13 @@
         <v>15.4965</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>-55.3</v>
+        <v>-55.7</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>25</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>16.8969</v>
+        <v>16.8993</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -1553,25 +1553,25 @@
       </c>
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="4" t="n">
-        <v>24.88</v>
+        <v>24.38</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>71.7325</v>
+        <v>71.738</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>41.3341</v>
+        <v>41.337</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>67.77670000000001</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>-65.3</v>
+        <v>-66</v>
       </c>
       <c r="M8" s="5" t="n">
         <v>25</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>53.7994</v>
+        <v>53.8035</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="4" t="n">
-        <v>51.65</v>
+        <v>51.95</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>588.5381</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="4" t="n">
-        <v>9.734999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>130.7854</v>
@@ -1807,7 +1807,7 @@
         <v>20.1692</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>-92.59999999999999</v>
+        <v>-92.5</v>
       </c>
       <c r="M10" s="5" t="n">
         <v>25</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="4" t="n">
-        <v>7.565</v>
+        <v>7.61</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>98.4873</v>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="4" t="n">
-        <v>53.5</v>
+        <v>54</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>699.6943</v>
@@ -2291,7 +2291,7 @@
         <v>136.5623</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>-92.40000000000001</v>
+        <v>-92.3</v>
       </c>
       <c r="M14" s="5" t="n">
         <v>25</v>
@@ -2399,25 +2399,25 @@
       </c>
       <c r="G15" s="8" t="inlineStr"/>
       <c r="H15" s="9" t="n">
-        <v>57.6</v>
+        <v>57.21</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>100.9378</v>
+        <v>100.9394</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>56.4344</v>
+        <v>56.4432</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>94.1225</v>
       </c>
       <c r="L15" s="10" t="n">
-        <v>-42.9</v>
+        <v>-43.3</v>
       </c>
       <c r="M15" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>75.7033</v>
+        <v>75.7046</v>
       </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
@@ -2491,17 +2491,17 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>03998</t>
+          <t>605117</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>波司登</t>
+          <t>德业股份</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr"/>
@@ -2512,34 +2512,34 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>HKD</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr"/>
       <c r="H16" s="9" t="n">
-        <v>4.35</v>
+        <v>85.5</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>8.3026</v>
+        <v>113.129</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>3.8731</v>
+        <v>55.5052</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>7.0633</v>
+        <v>108.9327</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>-47.6</v>
+        <v>-24.4</v>
       </c>
       <c r="M16" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>6.2269</v>
+        <v>84.8467</v>
       </c>
       <c r="O16" s="7" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P16" s="11" t="inlineStr">
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="R16" s="7" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
@@ -2561,42 +2561,42 @@
         </is>
       </c>
       <c r="T16" s="7" t="n">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="U16" s="7" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="V16" s="7" t="n">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="W16" s="7" t="n">
-        <v>93.09999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="X16" s="8" t="inlineStr">
         <is>
-          <t>高毛利57.22%、ROIC 28.22%穩定成長，現金流強勁，資產負債健康。</t>
+          <t>ROE中位35.87%、毛利率38.04%、負債權益比0.175924（規則式）</t>
         </is>
       </c>
       <c r="Y16" s="10" t="n">
-        <v>21.9</v>
+        <v>38</v>
       </c>
       <c r="Z16" s="10" t="n">
-        <v>28.2</v>
+        <v>58.5</v>
       </c>
       <c r="AA16" s="10" t="n">
-        <v>57.2</v>
+        <v>38</v>
       </c>
       <c r="AB16" s="10" t="n">
-        <v>37.5</v>
+        <v>53.9</v>
       </c>
       <c r="AC16" s="7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="AD16" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AE16" s="7" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AF16" s="8" t="inlineStr">
         <is>
-          <t>報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
+          <t>行情總股本(1,273,282,072)與財報EPS反推(902,750,991)差異&gt;25%，已改用反推值</t>
         </is>
       </c>
     </row>
@@ -2618,18 +2618,18 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>00700</t>
+          <t>03998</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>腾讯控股</t>
+          <t>波司登</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr"/>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>mature</t>
+          <t>growth</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -2639,25 +2639,25 @@
       </c>
       <c r="G17" s="8" t="inlineStr"/>
       <c r="H17" s="9" t="n">
-        <v>429.4</v>
+        <v>4.365</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>659.8955</v>
+        <v>8.3025</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>459.3594</v>
+        <v>3.8731</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>609.7471</v>
+        <v>7.0632</v>
       </c>
       <c r="L17" s="10" t="n">
-        <v>-34.9</v>
+        <v>-47.4</v>
       </c>
       <c r="M17" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>494.9216</v>
+        <v>6.2269</v>
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="R17" s="7" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="T17" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U17" s="7" t="n">
         <v>9</v>
@@ -2692,33 +2692,33 @@
         <v>8.5</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>95.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="X17" s="8" t="inlineStr">
         <is>
-          <t>ROE中位22.71%穩，ROIC 18.73%，自由現金流率24.83%，負債比0.415</t>
+          <t>高毛利57.22%、ROIC 28.22%穩定成長，現金流強勁，資產負債健康。</t>
         </is>
       </c>
       <c r="Y17" s="10" t="n">
-        <v>20.7</v>
+        <v>21.9</v>
       </c>
       <c r="Z17" s="10" t="n">
-        <v>18.7</v>
+        <v>28.2</v>
       </c>
       <c r="AA17" s="10" t="n">
-        <v>57.4</v>
+        <v>57.2</v>
       </c>
       <c r="AB17" s="10" t="n">
-        <v>43.4</v>
+        <v>37.5</v>
       </c>
       <c r="AC17" s="7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AD17" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AE17" s="7" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>02688</t>
+          <t>00700</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>新奥能源</t>
+          <t>腾讯控股</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr"/>
@@ -2761,25 +2761,25 @@
       </c>
       <c r="G18" s="8" t="inlineStr"/>
       <c r="H18" s="9" t="n">
-        <v>50.05</v>
+        <v>428.4</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>84.1289</v>
+        <v>659.9072</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>83.2593</v>
+        <v>459.3641</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>106.0289</v>
+        <v>609.7471</v>
       </c>
       <c r="L18" s="10" t="n">
-        <v>-40.5</v>
+        <v>-35.1</v>
       </c>
       <c r="M18" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>63.0967</v>
+        <v>494.9304</v>
       </c>
       <c r="O18" s="7" t="inlineStr">
         <is>
@@ -2808,30 +2808,30 @@
         <v>7</v>
       </c>
       <c r="U18" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V18" s="7" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W18" s="7" t="n">
-        <v>93</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="X18" s="8" t="inlineStr">
         <is>
-          <t>ROE穩定10年獲利，自由現金流健康，但流動比率偏低。</t>
+          <t>ROE中位22.71%穩，ROIC 18.73%，自由現金流率24.83%，負債比0.415</t>
         </is>
       </c>
       <c r="Y18" s="10" t="n">
-        <v>12.8</v>
+        <v>20.7</v>
       </c>
       <c r="Z18" s="10" t="n">
-        <v>11.4</v>
+        <v>18.7</v>
       </c>
       <c r="AA18" s="10" t="n">
-        <v>11.9</v>
+        <v>57.4</v>
       </c>
       <c r="AB18" s="10" t="n">
-        <v>48.6</v>
+        <v>43.4</v>
       </c>
       <c r="AC18" s="7" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="AF18" s="8" t="inlineStr">
         <is>
-          <t>缺關鍵科目：d_and_a / 報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
+          <t>報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
         </is>
       </c>
     </row>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>09999</t>
+          <t>02688</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>网易</t>
+          <t>新奥能源</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr"/>
@@ -2883,25 +2883,25 @@
       </c>
       <c r="G19" s="8" t="inlineStr"/>
       <c r="H19" s="9" t="n">
-        <v>182</v>
+        <v>48.14</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>300.1444</v>
+        <v>84.2801</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>153.404</v>
+        <v>83.2593</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>378.6999</v>
+        <v>106.0289</v>
       </c>
       <c r="L19" s="10" t="n">
-        <v>-39.4</v>
+        <v>-42.9</v>
       </c>
       <c r="M19" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>225.1083</v>
+        <v>63.2101</v>
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
@@ -2927,33 +2927,33 @@
         </is>
       </c>
       <c r="T19" s="7" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="U19" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="V19" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="V19" s="7" t="n">
-        <v>8.5</v>
-      </c>
       <c r="W19" s="7" t="n">
-        <v>84.8</v>
+        <v>93</v>
       </c>
       <c r="X19" s="8" t="inlineStr">
         <is>
-          <t>高毛利率67.15%、ROE中位21.06%、淨現金162788.7百萬，財務極穩健。</t>
+          <t>ROE穩定10年獲利，自由現金流健康，但流動比率偏低。</t>
         </is>
       </c>
       <c r="Y19" s="10" t="n">
-        <v>19.5</v>
+        <v>12.8</v>
       </c>
       <c r="Z19" s="10" t="n">
-        <v>777.9</v>
+        <v>11.4</v>
       </c>
       <c r="AA19" s="10" t="n">
-        <v>67.2</v>
+        <v>11.9</v>
       </c>
       <c r="AB19" s="10" t="n">
-        <v>26.1</v>
+        <v>48.6</v>
       </c>
       <c r="AC19" s="7" t="inlineStr">
         <is>
@@ -2972,58 +2972,58 @@
       </c>
       <c r="AF19" s="8" t="inlineStr">
         <is>
-          <t>報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
+          <t>缺關鍵科目：d_and_a / 報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>09999</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>网易</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr"/>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>growth</t>
+          <t>mature</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>HKD</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr"/>
       <c r="H20" s="9" t="n">
-        <v>84.90000000000001</v>
+        <v>182.1</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>126.3713</v>
+        <v>300.1442</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>67.5265</v>
+        <v>153.4032</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>166.782</v>
+        <v>378.6999</v>
       </c>
       <c r="L20" s="10" t="n">
-        <v>-32.8</v>
+        <v>-39.3</v>
       </c>
       <c r="M20" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>94.77849999999999</v>
+        <v>225.1082</v>
       </c>
       <c r="O20" s="7" t="inlineStr">
         <is>
@@ -3049,33 +3049,33 @@
         </is>
       </c>
       <c r="T20" s="7" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="U20" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="V20" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="V20" s="7" t="n">
-        <v>8</v>
-      </c>
       <c r="W20" s="7" t="n">
-        <v>85.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="X20" s="8" t="inlineStr">
         <is>
-          <t>ROIC達41.11%，經營現金流強勁，淨現金23674.1百萬，但流動比率1.64偏低。</t>
+          <t>高毛利率67.15%、ROE中位21.06%、淨現金162788.7百萬，財務極穩健。</t>
         </is>
       </c>
       <c r="Y20" s="10" t="n">
-        <v>21.7</v>
+        <v>19.5</v>
       </c>
       <c r="Z20" s="10" t="n">
-        <v>41.1</v>
+        <v>777.9</v>
       </c>
       <c r="AA20" s="10" t="n">
-        <v>32</v>
+        <v>67.2</v>
       </c>
       <c r="AB20" s="10" t="n">
-        <v>58.2</v>
+        <v>26.1</v>
       </c>
       <c r="AC20" s="7" t="inlineStr">
         <is>
@@ -3092,56 +3092,60 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AF20" s="8" t="inlineStr"/>
+      <c r="AF20" s="8" t="inlineStr">
+        <is>
+          <t>報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>00762</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>中国联通</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr"/>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>mature</t>
+          <t>growth</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>HKD</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr"/>
       <c r="H21" s="9" t="n">
-        <v>5.815</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>11.4619</v>
+        <v>126.3732</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>8.3786</v>
+        <v>67.53700000000001</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>12.385</v>
+        <v>166.782</v>
       </c>
       <c r="L21" s="10" t="n">
-        <v>-49.3</v>
+        <v>-33.2</v>
       </c>
       <c r="M21" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>8.596399999999999</v>
+        <v>94.7799</v>
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
@@ -3159,7 +3163,7 @@
         </is>
       </c>
       <c r="R21" s="7" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
@@ -3170,30 +3174,30 @@
         <v>7</v>
       </c>
       <c r="U21" s="7" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="V21" s="7" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W21" s="7" t="n">
-        <v>93.7</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="X21" s="8" t="inlineStr">
         <is>
-          <t>獲利穩定十年，ROE僅4.23%，流動比率0.70偏低，自由現金流率5.73%健康</t>
+          <t>ROIC達41.11%，經營現金流強勁，淨現金23674.1百萬，但流動比率1.64偏低。</t>
         </is>
       </c>
       <c r="Y21" s="10" t="n">
-        <v>4.2</v>
+        <v>21.7</v>
       </c>
       <c r="Z21" s="10" t="n">
-        <v>3.4</v>
+        <v>41.1</v>
       </c>
       <c r="AA21" s="10" t="n">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="AB21" s="10" t="n">
-        <v>44.4</v>
+        <v>58.2</v>
       </c>
       <c r="AC21" s="7" t="inlineStr">
         <is>
@@ -3210,11 +3214,7 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AF21" s="8" t="inlineStr">
-        <is>
-          <t>報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
-        </is>
-      </c>
+      <c r="AF21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -3224,12 +3224,12 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>09961</t>
+          <t>00762</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>携程集团-S</t>
+          <t>中国联通</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr"/>
@@ -3245,25 +3245,25 @@
       </c>
       <c r="G22" s="8" t="inlineStr"/>
       <c r="H22" s="9" t="n">
-        <v>304.8</v>
+        <v>5.825</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>430.9274</v>
+        <v>11.4615</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>252.0972</v>
+        <v>8.3786</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>428.4491</v>
+        <v>12.385</v>
       </c>
       <c r="L22" s="10" t="n">
-        <v>-29.3</v>
+        <v>-49.2</v>
       </c>
       <c r="M22" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>323.1955</v>
+        <v>8.5961</v>
       </c>
       <c r="O22" s="7" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="Q22" s="7" t="inlineStr">
         <is>
-          <t>合理</t>
+          <t>便宜</t>
         </is>
       </c>
       <c r="R22" s="7" t="n">
@@ -3289,33 +3289,33 @@
         </is>
       </c>
       <c r="T22" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U22" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V22" s="7" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W22" s="7" t="n">
-        <v>89.2</v>
+        <v>93.7</v>
       </c>
       <c r="X22" s="8" t="inlineStr">
         <is>
-          <t>毛利率89.71%、淨現金496億，ROIC 11.73% ROE不穩</t>
+          <t>獲利穩定十年，ROE僅4.23%，流動比率0.70偏低，自由現金流率5.73%健康</t>
         </is>
       </c>
       <c r="Y22" s="10" t="n">
-        <v>19.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z22" s="10" t="n">
-        <v>11.7</v>
+        <v>3.4</v>
       </c>
       <c r="AA22" s="10" t="n">
-        <v>89.7</v>
+        <v>69</v>
       </c>
       <c r="AB22" s="10" t="n">
-        <v>36.7</v>
+        <v>44.4</v>
       </c>
       <c r="AC22" s="7" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="AD22" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AE22" s="7" t="inlineStr">
@@ -3346,12 +3346,12 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>00386</t>
+          <t>09961</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>中国石油化工股份</t>
+          <t>携程集团-S</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr"/>
@@ -3367,25 +3367,25 @@
       </c>
       <c r="G23" s="8" t="inlineStr"/>
       <c r="H23" s="9" t="n">
-        <v>4.795</v>
+        <v>305.8</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>9.1286</v>
+        <v>430.9121</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>3.1723</v>
+        <v>252.0972</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>5.6134</v>
+        <v>428.4491</v>
       </c>
       <c r="L23" s="10" t="n">
-        <v>-47.5</v>
+        <v>-29</v>
       </c>
       <c r="M23" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>6.8465</v>
+        <v>323.1841</v>
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
@@ -3399,45 +3399,45 @@
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>便宜</t>
+          <t>合理</t>
         </is>
       </c>
       <c r="R23" s="7" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T23" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U23" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="V23" s="7" t="n">
         <v>7.5</v>
       </c>
-      <c r="U23" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="V23" s="7" t="n">
-        <v>5</v>
-      </c>
       <c r="W23" s="7" t="n">
-        <v>93</v>
+        <v>89.2</v>
       </c>
       <c r="X23" s="8" t="inlineStr">
         <is>
-          <t>營業利益率僅1.9%但近十年穩定獲利，負債權益比0.674穩健，經營現金流強勁。</t>
+          <t>毛利率89.71%、淨現金496億，ROIC 11.73% ROE不穩</t>
         </is>
       </c>
       <c r="Y23" s="10" t="n">
-        <v>4.2</v>
+        <v>19.1</v>
       </c>
       <c r="Z23" s="10" t="n">
-        <v>3.5</v>
+        <v>11.7</v>
       </c>
       <c r="AA23" s="10" t="n">
-        <v>23.5</v>
+        <v>89.7</v>
       </c>
       <c r="AB23" s="10" t="n">
-        <v>54.4</v>
+        <v>36.7</v>
       </c>
       <c r="AC23" s="7" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="AD23" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AE23" s="7" t="inlineStr">
@@ -3456,24 +3456,24 @@
       </c>
       <c r="AF23" s="8" t="inlineStr">
         <is>
-          <t>缺關鍵科目：capex / 報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
+          <t>報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>00386</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>强生</t>
+          <t>中国石油化工股份</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr"/>
@@ -3484,30 +3484,30 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>HKD</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr"/>
       <c r="H24" s="9" t="n">
-        <v>266.35</v>
+        <v>4.775</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>480.8077</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>9.3416</v>
+        <v>3.1723</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>17.7689</v>
+        <v>5.6199</v>
       </c>
       <c r="L24" s="10" t="n">
-        <v>-44.6</v>
+        <v>-47.7</v>
       </c>
       <c r="M24" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>360.6058</v>
+        <v>6.8475</v>
       </c>
       <c r="O24" s="7" t="inlineStr">
         <is>
@@ -3533,174 +3533,174 @@
         </is>
       </c>
       <c r="T24" s="7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="U24" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="V24" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="U24" s="7" t="n">
+      <c r="W24" s="7" t="n">
+        <v>93</v>
+      </c>
+      <c r="X24" s="8" t="inlineStr">
+        <is>
+          <t>營業利益率僅1.9%但近十年穩定獲利，負債權益比0.674穩健，經營現金流強勁。</t>
+        </is>
+      </c>
+      <c r="Y24" s="10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Z24" s="10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA24" s="10" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AB24" s="10" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="AC24" s="7" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="AD24" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AE24" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AF24" s="8" t="inlineStr">
+        <is>
+          <t>缺關鍵科目：capex / 報表幣別 CNY → 交易幣別 HKD，匯率 1.1641</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>JNJ</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>强生</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>mature</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr"/>
+      <c r="H25" s="9" t="n">
+        <v>266.35</v>
+      </c>
+      <c r="I25" s="9" t="n">
+        <v>480.8077</v>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>9.3416</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>17.7689</v>
+      </c>
+      <c r="L25" s="10" t="n">
+        <v>-44.6</v>
+      </c>
+      <c r="M25" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="N25" s="9" t="n">
+        <v>360.6058</v>
+      </c>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P25" s="11" t="inlineStr">
+        <is>
+          <t>便宜</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>便宜</t>
+        </is>
+      </c>
+      <c r="R25" s="7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T25" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U25" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="V24" s="7" t="n">
+      <c r="V25" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="W24" s="7" t="n">
+      <c r="W25" s="7" t="n">
         <v>93.2</v>
       </c>
-      <c r="X24" s="8" t="inlineStr">
+      <c r="X25" s="8" t="inlineStr">
         <is>
           <t>獲利穩定但ROIC偏低，淨現金為負，高毛利率支撐護城河</t>
         </is>
       </c>
-      <c r="Y24" s="10" t="n">
+      <c r="Y25" s="10" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="Z24" s="10" t="n">
+      <c r="Z25" s="10" t="n">
         <v>6.1</v>
       </c>
-      <c r="AA24" s="10" t="n">
+      <c r="AA25" s="10" t="n">
         <v>70.09999999999999</v>
       </c>
-      <c r="AB24" s="10" t="n">
+      <c r="AB25" s="10" t="n">
         <v>57.7</v>
       </c>
-      <c r="AC24" s="7" t="inlineStr">
+      <c r="AC25" s="7" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="AD24" s="7" t="inlineStr">
+      <c r="AD25" s="7" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="AE24" s="7" t="inlineStr">
+      <c r="AE25" s="7" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AF24" s="8" t="inlineStr">
+      <c r="AF25" s="8" t="inlineStr">
         <is>
           <t>缺關鍵科目：cfo,capex,d_and_a</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>605117</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>德业股份</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="inlineStr"/>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>growth</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="G25" s="13" t="inlineStr"/>
-      <c r="H25" s="14" t="n">
-        <v>84.91</v>
-      </c>
-      <c r="I25" s="14" t="n">
-        <v>113.1304</v>
-      </c>
-      <c r="J25" s="14" t="n">
-        <v>55.5052</v>
-      </c>
-      <c r="K25" s="14" t="n">
-        <v>108.9336</v>
-      </c>
-      <c r="L25" s="15" t="n">
-        <v>-24.9</v>
-      </c>
-      <c r="M25" s="15" t="n">
-        <v>25</v>
-      </c>
-      <c r="N25" s="14" t="n">
-        <v>84.84780000000001</v>
-      </c>
-      <c r="O25" s="12" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P25" s="16" t="inlineStr">
-        <is>
-          <t>合理</t>
-        </is>
-      </c>
-      <c r="Q25" s="12" t="inlineStr">
-        <is>
-          <t>便宜</t>
-        </is>
-      </c>
-      <c r="R25" s="12" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="S25" s="12" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="T25" s="12" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="U25" s="12" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="V25" s="12" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W25" s="12" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="X25" s="13" t="inlineStr">
-        <is>
-          <t>ROE中位35.87%、毛利率38.04%、負債權益比0.175924（規則式）</t>
-        </is>
-      </c>
-      <c r="Y25" s="15" t="n">
-        <v>38</v>
-      </c>
-      <c r="Z25" s="15" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="AA25" s="15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB25" s="15" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="AC25" s="12" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="AD25" s="12" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AE25" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AF25" s="13" t="inlineStr">
-        <is>
-          <t>行情總股本(1,273,282,072)與財報EPS反推(902,750,991)差異&gt;25%，已改用反推值</t>
         </is>
       </c>
     </row>
@@ -3733,19 +3733,19 @@
       </c>
       <c r="G26" s="13" t="inlineStr"/>
       <c r="H26" s="14" t="n">
-        <v>163.23</v>
+        <v>162.73</v>
       </c>
       <c r="I26" s="14" t="n">
-        <v>200.3009</v>
+        <v>200.301</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>116.6281</v>
+        <v>116.6284</v>
       </c>
       <c r="K26" s="14" t="n">
         <v>176.872</v>
       </c>
       <c r="L26" s="15" t="n">
-        <v>-18.5</v>
+        <v>-18.8</v>
       </c>
       <c r="M26" s="15" t="n">
         <v>25</v>
@@ -3851,25 +3851,25 @@
       </c>
       <c r="G27" s="13" t="inlineStr"/>
       <c r="H27" s="14" t="n">
-        <v>1268.64</v>
+        <v>1275.16</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>1186.8347</v>
+        <v>1186.8346</v>
       </c>
       <c r="J27" s="14" t="n">
-        <v>838.7851000000001</v>
+        <v>838.7846</v>
       </c>
       <c r="K27" s="14" t="n">
         <v>2058.441</v>
       </c>
       <c r="L27" s="15" t="n">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="M27" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>890.126</v>
+        <v>890.1259</v>
       </c>
       <c r="O27" s="12" t="inlineStr">
         <is>
@@ -3969,25 +3969,25 @@
       </c>
       <c r="G28" s="13" t="inlineStr"/>
       <c r="H28" s="14" t="n">
-        <v>78.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I28" s="14" t="n">
-        <v>89.6123</v>
+        <v>89.6108</v>
       </c>
       <c r="J28" s="14" t="n">
-        <v>87.0705</v>
+        <v>87.0635</v>
       </c>
       <c r="K28" s="14" t="n">
         <v>92.48090000000001</v>
       </c>
       <c r="L28" s="15" t="n">
-        <v>-12.2</v>
+        <v>-12</v>
       </c>
       <c r="M28" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>67.2093</v>
+        <v>67.2081</v>
       </c>
       <c r="O28" s="12" t="inlineStr">
         <is>
@@ -4091,13 +4091,13 @@
       </c>
       <c r="G29" s="13" t="inlineStr"/>
       <c r="H29" s="14" t="n">
-        <v>86.3</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>107.1812</v>
+        <v>107.1817</v>
       </c>
       <c r="J29" s="14" t="n">
-        <v>69.08240000000001</v>
+        <v>69.0847</v>
       </c>
       <c r="K29" s="14" t="n">
         <v>136.1669</v>
@@ -4109,7 +4109,7 @@
         <v>25</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>80.38590000000001</v>
+        <v>80.38630000000001</v>
       </c>
       <c r="O29" s="12" t="inlineStr">
         <is>
@@ -4209,19 +4209,19 @@
       </c>
       <c r="G30" s="13" t="inlineStr"/>
       <c r="H30" s="14" t="n">
-        <v>31.22</v>
+        <v>31.3</v>
       </c>
       <c r="I30" s="14" t="n">
         <v>31.6295</v>
       </c>
       <c r="J30" s="14" t="n">
-        <v>16.8725</v>
+        <v>16.8727</v>
       </c>
       <c r="K30" s="14" t="n">
         <v>19.839</v>
       </c>
       <c r="L30" s="15" t="n">
-        <v>-1.3</v>
+        <v>-1</v>
       </c>
       <c r="M30" s="15" t="n">
         <v>25</v>
@@ -4331,25 +4331,25 @@
       </c>
       <c r="G31" s="13" t="inlineStr"/>
       <c r="H31" s="14" t="n">
-        <v>8.994999999999999</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>11.1691</v>
+        <v>11.1671</v>
       </c>
       <c r="J31" s="14" t="n">
-        <v>4.5312</v>
+        <v>4.5216</v>
       </c>
       <c r="K31" s="14" t="n">
         <v>14.7897</v>
       </c>
       <c r="L31" s="15" t="n">
-        <v>-19.5</v>
+        <v>-19.1</v>
       </c>
       <c r="M31" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>8.376899999999999</v>
+        <v>8.375299999999999</v>
       </c>
       <c r="O31" s="12" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>5.5</v>
       </c>
       <c r="W31" s="12" t="n">
-        <v>83.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="X31" s="13" t="inlineStr">
         <is>
@@ -4453,25 +4453,25 @@
       </c>
       <c r="G32" s="13" t="inlineStr"/>
       <c r="H32" s="14" t="n">
-        <v>105</v>
+        <v>106.2</v>
       </c>
       <c r="I32" s="14" t="n">
-        <v>136.1701</v>
+        <v>136.1804</v>
       </c>
       <c r="J32" s="14" t="n">
         <v>59.7871</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>129.2387</v>
+        <v>129.2877</v>
       </c>
       <c r="L32" s="15" t="n">
-        <v>-22.9</v>
+        <v>-22</v>
       </c>
       <c r="M32" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N32" s="14" t="n">
-        <v>102.1276</v>
+        <v>102.1353</v>
       </c>
       <c r="O32" s="12" t="inlineStr">
         <is>
@@ -4575,25 +4575,25 @@
       </c>
       <c r="G33" s="13" t="inlineStr"/>
       <c r="H33" s="14" t="n">
-        <v>26</v>
+        <v>26.36</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>28.7651</v>
+        <v>28.7639</v>
       </c>
       <c r="J33" s="14" t="n">
         <v>18.8996</v>
       </c>
       <c r="K33" s="14" t="n">
-        <v>26.4515</v>
+        <v>26.451</v>
       </c>
       <c r="L33" s="15" t="n">
-        <v>-9.6</v>
+        <v>-8.4</v>
       </c>
       <c r="M33" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>21.5739</v>
+        <v>21.5729</v>
       </c>
       <c r="O33" s="12" t="inlineStr">
         <is>
@@ -4697,10 +4697,10 @@
       </c>
       <c r="G34" s="13" t="inlineStr"/>
       <c r="H34" s="14" t="n">
-        <v>34.42</v>
+        <v>34.96</v>
       </c>
       <c r="I34" s="14" t="n">
-        <v>40.8481</v>
+        <v>40.763</v>
       </c>
       <c r="J34" s="14" t="n">
         <v>11.3883</v>
@@ -4709,13 +4709,13 @@
         <v>52.1359</v>
       </c>
       <c r="L34" s="15" t="n">
-        <v>-15.7</v>
+        <v>-14.2</v>
       </c>
       <c r="M34" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>30.6361</v>
+        <v>30.5723</v>
       </c>
       <c r="O34" s="12" t="inlineStr">
         <is>
@@ -4941,10 +4941,10 @@
       </c>
       <c r="G36" s="18" t="inlineStr"/>
       <c r="H36" s="19" t="n">
-        <v>28.31</v>
+        <v>28.45</v>
       </c>
       <c r="I36" s="19" t="n">
-        <v>20.5703</v>
+        <v>20.5663</v>
       </c>
       <c r="J36" s="19" t="n">
         <v>16.2467</v>
@@ -4953,13 +4953,13 @@
         <v>22.7622</v>
       </c>
       <c r="L36" s="20" t="n">
-        <v>37.6</v>
+        <v>38.3</v>
       </c>
       <c r="M36" s="20" t="n">
         <v>25</v>
       </c>
       <c r="N36" s="19" t="n">
-        <v>15.4277</v>
+        <v>15.4247</v>
       </c>
       <c r="O36" s="17" t="inlineStr">
         <is>
@@ -5063,10 +5063,10 @@
         </is>
       </c>
       <c r="H37" s="19" t="n">
-        <v>543.5</v>
+        <v>547.5</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>382.6004</v>
+        <v>382.5813</v>
       </c>
       <c r="J37" s="19" t="n">
         <v>170.1479</v>
@@ -5075,13 +5075,13 @@
         <v>309.2153</v>
       </c>
       <c r="L37" s="20" t="n">
-        <v>42.1</v>
+        <v>43.1</v>
       </c>
       <c r="M37" s="20" t="n">
         <v>25</v>
       </c>
       <c r="N37" s="19" t="n">
-        <v>286.9503</v>
+        <v>286.936</v>
       </c>
       <c r="O37" s="17" t="inlineStr">
         <is>
@@ -5185,10 +5185,10 @@
       </c>
       <c r="G38" s="18" t="inlineStr"/>
       <c r="H38" s="19" t="n">
-        <v>28.92</v>
+        <v>28.97</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>23.0615</v>
+        <v>23.0612</v>
       </c>
       <c r="J38" s="19" t="n">
         <v>8.570600000000001</v>
@@ -5197,13 +5197,13 @@
         <v>15.399</v>
       </c>
       <c r="L38" s="20" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="M38" s="20" t="n">
         <v>25</v>
       </c>
       <c r="N38" s="19" t="n">
-        <v>17.2961</v>
+        <v>17.2959</v>
       </c>
       <c r="O38" s="17" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="G39" s="18" t="inlineStr"/>
       <c r="H39" s="19" t="n">
-        <v>3.055</v>
+        <v>3.065</v>
       </c>
       <c r="I39" s="19" t="n">
         <v>2.3155</v>
@@ -5319,7 +5319,7 @@
         <v>3.9797</v>
       </c>
       <c r="L39" s="20" t="n">
-        <v>31.9</v>
+        <v>32.4</v>
       </c>
       <c r="M39" s="20" t="n">
         <v>25</v>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="G40" s="18" t="inlineStr"/>
       <c r="H40" s="19" t="n">
-        <v>42.19</v>
+        <v>42.67</v>
       </c>
       <c r="I40" s="19" t="n">
         <v>28.4781</v>
@@ -5441,7 +5441,7 @@
         <v>22.6238</v>
       </c>
       <c r="L40" s="20" t="n">
-        <v>48.1</v>
+        <v>49.8</v>
       </c>
       <c r="M40" s="20" t="n">
         <v>25</v>
@@ -5791,7 +5791,7 @@
       </c>
       <c r="G43" s="23" t="inlineStr"/>
       <c r="H43" s="24" t="n">
-        <v>162.4</v>
+        <v>163.3</v>
       </c>
       <c r="I43" s="24" t="n">
         <v>92.538</v>
@@ -5803,7 +5803,7 @@
         <v>147.259</v>
       </c>
       <c r="L43" s="25" t="n">
-        <v>75.5</v>
+        <v>76.5</v>
       </c>
       <c r="M43" s="25" t="n">
         <v>25</v>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="AF43" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">行情總股本(17,160,052,183)與財報EPS反推(163,822,314,050)差異&gt;25%，已改用反推值 / 缺關鍵科目：revenue,cash,total_debt,current_assets,current_liab </t>
+          <t xml:space="preserve">行情總股本(17,160,042,183)與財報EPS反推(163,822,314,050)差異&gt;25%，已改用反推值 / 缺關鍵科目：revenue,cash,total_debt,current_assets,current_liab </t>
         </is>
       </c>
     </row>
@@ -5911,7 +5911,7 @@
       </c>
       <c r="G44" s="23" t="inlineStr"/>
       <c r="H44" s="24" t="n">
-        <v>391</v>
+        <v>392.6</v>
       </c>
       <c r="I44" s="24" t="n">
         <v>156.7211</v>
@@ -5923,7 +5923,7 @@
         <v>215.7121</v>
       </c>
       <c r="L44" s="25" t="n">
-        <v>149.5</v>
+        <v>150.5</v>
       </c>
       <c r="M44" s="25" t="n">
         <v>25</v>
@@ -6029,19 +6029,19 @@
       </c>
       <c r="G45" s="23" t="inlineStr"/>
       <c r="H45" s="24" t="n">
-        <v>188.9</v>
+        <v>188.8</v>
       </c>
       <c r="I45" s="24" t="n">
         <v>103.3052</v>
       </c>
       <c r="J45" s="24" t="n">
-        <v>66.59269999999999</v>
+        <v>66.593</v>
       </c>
       <c r="K45" s="24" t="n">
         <v>112.1457</v>
       </c>
       <c r="L45" s="25" t="n">
-        <v>82.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="M45" s="25" t="n">
         <v>25</v>
@@ -6151,10 +6151,10 @@
       </c>
       <c r="G46" s="23" t="inlineStr"/>
       <c r="H46" s="24" t="n">
-        <v>22.86</v>
+        <v>22.4</v>
       </c>
       <c r="I46" s="24" t="n">
-        <v>12.4346</v>
+        <v>12.437</v>
       </c>
       <c r="J46" s="24" t="n">
         <v>7.2799</v>
@@ -6163,13 +6163,13 @@
         <v>9.681699999999999</v>
       </c>
       <c r="L46" s="25" t="n">
-        <v>83.8</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="M46" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N46" s="24" t="n">
-        <v>9.326000000000001</v>
+        <v>9.3277</v>
       </c>
       <c r="O46" s="22" t="inlineStr">
         <is>
@@ -6273,25 +6273,25 @@
       </c>
       <c r="G47" s="23" t="inlineStr"/>
       <c r="H47" s="24" t="n">
-        <v>105.8</v>
+        <v>107.5</v>
       </c>
       <c r="I47" s="24" t="n">
-        <v>68.1835</v>
+        <v>68.17149999999999</v>
       </c>
       <c r="J47" s="24" t="n">
         <v>58.5967</v>
       </c>
       <c r="K47" s="24" t="n">
-        <v>64.01649999999999</v>
+        <v>63.9621</v>
       </c>
       <c r="L47" s="25" t="n">
-        <v>55.2</v>
+        <v>57.7</v>
       </c>
       <c r="M47" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N47" s="24" t="n">
-        <v>51.1376</v>
+        <v>51.1286</v>
       </c>
       <c r="O47" s="22" t="inlineStr">
         <is>
@@ -6395,10 +6395,10 @@
       </c>
       <c r="G48" s="23" t="inlineStr"/>
       <c r="H48" s="24" t="n">
-        <v>117.62</v>
+        <v>119.73</v>
       </c>
       <c r="I48" s="24" t="n">
-        <v>50.5525</v>
+        <v>50.5507</v>
       </c>
       <c r="J48" s="24" t="n">
         <v>39.5892</v>
@@ -6407,13 +6407,13 @@
         <v>50.2832</v>
       </c>
       <c r="L48" s="25" t="n">
-        <v>132.7</v>
+        <v>136.9</v>
       </c>
       <c r="M48" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N48" s="24" t="n">
-        <v>37.9144</v>
+        <v>37.913</v>
       </c>
       <c r="O48" s="22" t="inlineStr">
         <is>
@@ -6513,25 +6513,25 @@
       </c>
       <c r="G49" s="23" t="inlineStr"/>
       <c r="H49" s="24" t="n">
-        <v>64.2</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="I49" s="24" t="n">
-        <v>35.7515</v>
+        <v>35.7521</v>
       </c>
       <c r="J49" s="24" t="n">
-        <v>25.502</v>
+        <v>25.5049</v>
       </c>
       <c r="K49" s="24" t="n">
-        <v>36.6837</v>
+        <v>36.6839</v>
       </c>
       <c r="L49" s="25" t="n">
-        <v>79.59999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="M49" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N49" s="24" t="n">
-        <v>26.8137</v>
+        <v>26.814</v>
       </c>
       <c r="O49" s="22" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
       </c>
       <c r="G55" s="23" t="inlineStr"/>
       <c r="H55" s="24" t="n">
-        <v>73.95</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I55" s="24" t="n">
         <v>13.9617</v>
@@ -7257,7 +7257,7 @@
         <v>58.1316</v>
       </c>
       <c r="L55" s="25" t="n">
-        <v>429.7</v>
+        <v>437.9</v>
       </c>
       <c r="M55" s="25" t="n">
         <v>25</v>
@@ -7367,25 +7367,25 @@
       </c>
       <c r="G56" s="23" t="inlineStr"/>
       <c r="H56" s="24" t="n">
-        <v>329.87</v>
+        <v>333.59</v>
       </c>
       <c r="I56" s="24" t="n">
-        <v>81.58629999999999</v>
+        <v>81.5859</v>
       </c>
       <c r="J56" s="24" t="n">
         <v>56.4053</v>
       </c>
       <c r="K56" s="24" t="n">
-        <v>81.3681</v>
+        <v>81.36579999999999</v>
       </c>
       <c r="L56" s="25" t="n">
-        <v>304.3</v>
+        <v>308.9</v>
       </c>
       <c r="M56" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N56" s="24" t="n">
-        <v>61.1898</v>
+        <v>61.1895</v>
       </c>
       <c r="O56" s="22" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="G57" s="23" t="inlineStr"/>
       <c r="H57" s="24" t="n">
-        <v>277.5</v>
+        <v>280.66</v>
       </c>
       <c r="I57" s="24" t="n">
         <v>10.4095</v>
@@ -7501,7 +7501,7 @@
         <v>12.8567</v>
       </c>
       <c r="L57" s="25" t="n">
-        <v>2565.8</v>
+        <v>2596.2</v>
       </c>
       <c r="M57" s="25" t="n">
         <v>25</v>
@@ -8581,7 +8581,7 @@
       </c>
       <c r="G66" s="23" t="inlineStr"/>
       <c r="H66" s="24" t="n">
-        <v>1.285</v>
+        <v>1.31</v>
       </c>
       <c r="I66" s="24" t="n">
         <v>0.0963</v>
@@ -8593,7 +8593,7 @@
         <v>0.1246</v>
       </c>
       <c r="L66" s="25" t="n">
-        <v>1234.4</v>
+        <v>1260.3</v>
       </c>
       <c r="M66" s="25" t="n">
         <v>25</v>
@@ -8703,25 +8703,25 @@
       </c>
       <c r="G67" s="23" t="inlineStr"/>
       <c r="H67" s="24" t="n">
-        <v>62.35</v>
+        <v>63.15</v>
       </c>
       <c r="I67" s="24" t="n">
-        <v>6.9166</v>
+        <v>6.9178</v>
       </c>
       <c r="J67" s="24" t="n">
         <v>3.7761</v>
       </c>
       <c r="K67" s="24" t="n">
-        <v>10.4145</v>
+        <v>10.4183</v>
       </c>
       <c r="L67" s="25" t="n">
-        <v>801.5</v>
+        <v>812.9</v>
       </c>
       <c r="M67" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N67" s="24" t="n">
-        <v>5.1874</v>
+        <v>5.1883</v>
       </c>
       <c r="O67" s="22" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         </is>
       </c>
       <c r="H68" s="24" t="n">
-        <v>489.03</v>
+        <v>477.12</v>
       </c>
       <c r="I68" s="24" t="n">
         <v>6.6804</v>
@@ -8841,7 +8841,7 @@
         <v>8.4762</v>
       </c>
       <c r="L68" s="25" t="n">
-        <v>7220.4</v>
+        <v>7042.1</v>
       </c>
       <c r="M68" s="25" t="n">
         <v>25</v>
@@ -8947,25 +8947,25 @@
       </c>
       <c r="G69" s="28" t="inlineStr"/>
       <c r="H69" s="29" t="n">
-        <v>5.43</v>
+        <v>5.415</v>
       </c>
       <c r="I69" s="29" t="n">
-        <v>3.914</v>
+        <v>3.9183</v>
       </c>
       <c r="J69" s="29" t="n">
-        <v>2.6415</v>
+        <v>2.6472</v>
       </c>
       <c r="K69" s="29" t="n">
         <v>79.6524</v>
       </c>
       <c r="L69" s="30" t="n">
-        <v>38.7</v>
+        <v>38.2</v>
       </c>
       <c r="M69" s="30" t="n">
         <v>25</v>
       </c>
       <c r="N69" s="29" t="n">
-        <v>2.9355</v>
+        <v>2.9387</v>
       </c>
       <c r="O69" s="27" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
       </c>
       <c r="G72" s="28" t="inlineStr"/>
       <c r="H72" s="29" t="n">
-        <v>5.815</v>
+        <v>5.67</v>
       </c>
       <c r="I72" s="29" t="n">
         <v>158.04</v>
@@ -9325,7 +9325,7 @@
         <v>62.1445</v>
       </c>
       <c r="L72" s="30" t="n">
-        <v>-96.3</v>
+        <v>-96.40000000000001</v>
       </c>
       <c r="M72" s="30" t="n">
         <v>35</v>
@@ -9672,7 +9672,7 @@
         </is>
       </c>
       <c r="C2" s="34" t="n">
-        <v>162.4</v>
+        <v>163.3</v>
       </c>
       <c r="D2" s="34" t="n">
         <v>92.538</v>
@@ -9727,10 +9727,10 @@
         </is>
       </c>
       <c r="C3" s="34" t="n">
-        <v>5.43</v>
+        <v>5.415</v>
       </c>
       <c r="D3" s="34" t="n">
-        <v>3.914</v>
+        <v>3.9183</v>
       </c>
       <c r="E3" s="34" t="inlineStr"/>
       <c r="F3" s="34" t="inlineStr"/>
@@ -9739,7 +9739,7 @@
         <v>7.7314</v>
       </c>
       <c r="I3" s="34" t="n">
-        <v>2.6415</v>
+        <v>2.6472</v>
       </c>
       <c r="J3" s="34" t="inlineStr"/>
       <c r="K3" s="34" t="inlineStr"/>
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="C4" s="34" t="n">
-        <v>1.285</v>
+        <v>1.31</v>
       </c>
       <c r="D4" s="34" t="n">
         <v>0.0963</v>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="L4" s="34" t="inlineStr"/>
       <c r="M4" s="34" t="n">
-        <v>10.28</v>
+        <v>10.3</v>
       </c>
       <c r="N4" s="34" t="n">
         <v>11.23</v>
@@ -9827,10 +9827,10 @@
         </is>
       </c>
       <c r="C5" s="34" t="n">
-        <v>86.3</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="D5" s="34" t="n">
-        <v>107.1812</v>
+        <v>107.1817</v>
       </c>
       <c r="E5" s="34" t="n">
         <v>58.4383</v>
@@ -9845,10 +9845,10 @@
         <v>163.0562</v>
       </c>
       <c r="I5" s="34" t="n">
-        <v>69.08240000000001</v>
+        <v>69.0847</v>
       </c>
       <c r="J5" s="34" t="n">
-        <v>88.2657</v>
+        <v>88.2659</v>
       </c>
       <c r="K5" s="34" t="n">
         <v>136.1669</v>
@@ -9888,10 +9888,10 @@
         </is>
       </c>
       <c r="C6" s="34" t="n">
-        <v>38.8</v>
+        <v>38.74</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>142.5145</v>
+        <v>142.5179</v>
       </c>
       <c r="E6" s="34" t="n">
         <v>55.8024</v>
@@ -9906,10 +9906,10 @@
         <v>216.1553</v>
       </c>
       <c r="I6" s="34" t="n">
-        <v>62.2548</v>
+        <v>62.2708</v>
       </c>
       <c r="J6" s="34" t="n">
-        <v>48.7401</v>
+        <v>48.741</v>
       </c>
       <c r="K6" s="34" t="n">
         <v>808.3745</v>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="C7" s="34" t="n">
-        <v>28.92</v>
+        <v>28.97</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>23.0615</v>
+        <v>23.0612</v>
       </c>
       <c r="E7" s="34" t="n">
         <v>15.399</v>
@@ -9967,7 +9967,7 @@
         <v>57.4509</v>
       </c>
       <c r="I7" s="34" t="n">
-        <v>10.1137</v>
+        <v>10.1123</v>
       </c>
       <c r="J7" s="34" t="n">
         <v>8.278</v>
@@ -9979,7 +9979,7 @@
         <v>13.1089</v>
       </c>
       <c r="M7" s="34" t="n">
-        <v>8.289999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N7" s="34" t="n">
         <v>8.9</v>
@@ -10010,10 +10010,10 @@
         </is>
       </c>
       <c r="C8" s="34" t="n">
-        <v>1.315</v>
+        <v>1.305</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>3.8007</v>
+        <v>3.8011</v>
       </c>
       <c r="E8" s="34" t="n">
         <v>2.8029</v>
@@ -10028,10 +10028,10 @@
         <v>7.9395</v>
       </c>
       <c r="I8" s="34" t="n">
-        <v>2.3764</v>
+        <v>2.378</v>
       </c>
       <c r="J8" s="34" t="n">
-        <v>2.2071</v>
+        <v>2.2072</v>
       </c>
       <c r="K8" s="34" t="n">
         <v>1.2252</v>
@@ -10040,7 +10040,7 @@
         <v>2.9007</v>
       </c>
       <c r="M8" s="34" t="n">
-        <v>8.66</v>
+        <v>8.65</v>
       </c>
       <c r="N8" s="34" t="n">
         <v>9.949999999999999</v>
@@ -10055,7 +10055,7 @@
       </c>
       <c r="Q8" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 0.1511, "BVPS": 1.7052}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.4212, "NNWC/股": -0.3809, "net-net買點": 0.281}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 1650620000.0, "g1": 0.15, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 1933444800.0}, "epv": {"常態營業利益率": 0.0458, "常態NOPAT": 894448196.0, "WACC": 0.0866, "淨現金": 2074648000.0}, "damodaran_fcff": {"銷售/資本": 2.507, "g1": 0.0038, "永續g": 0.03, "目標營業利益率": 0.0458, "WACC": 0.0866, "終值WACC": 0.0995, "有效稅率": 0.2132, "終值佔比": 0.477}, "ri_pb": {"常態ROE": 0.08, "股權成本r": 0.0995, "留存成長g": 0.0485, "合理PB": 0.617}, "ddm": {"DPS": 0.0748, "g": 0.0675, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 0.1511, "BVPS": 1.7052}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.4212, "NNWC/股": -0.3809, "net-net買點": 0.281}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 1650620000.0, "g1": 0.15, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 1933444800.0}, "epv": {"常態營業利益率": 0.0458, "常態NOPAT": 894448196.0, "WACC": 0.0865, "淨現金": 2074648000.0}, "damodaran_fcff": {"銷售/資本": 2.507, "g1": 0.0038, "永續g": 0.03, "目標營業利益率": 0.0458, "WACC": 0.0865, "終值WACC": 0.0995, "有效稅率": 0.2132, "終值佔比": 0.477}, "ri_pb": {"常態ROE": 0.08, "股權成本r": 0.0995, "留存成長g": 0.0485, "合理PB": 0.617}, "ddm": {"DPS": 0.0748, "g": 0.0675, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -10071,10 +10071,10 @@
         </is>
       </c>
       <c r="C9" s="34" t="n">
-        <v>34.42</v>
+        <v>34.96</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>40.8481</v>
+        <v>40.763</v>
       </c>
       <c r="E9" s="34" t="n">
         <v>39.2855</v>
@@ -10087,7 +10087,7 @@
       </c>
       <c r="H9" s="34" t="inlineStr"/>
       <c r="I9" s="34" t="n">
-        <v>21.1765</v>
+        <v>20.9554</v>
       </c>
       <c r="J9" s="34" t="inlineStr"/>
       <c r="K9" s="34" t="n">
@@ -10097,7 +10097,7 @@
         <v>144.2784</v>
       </c>
       <c r="M9" s="34" t="n">
-        <v>6.09</v>
+        <v>6.11</v>
       </c>
       <c r="N9" s="34" t="n">
         <v>9.949999999999999</v>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="Q9" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 2.0, "BVPS": 25.3079}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 3.4455, "NNWC/股": -35.366, "net-net買點": 2.2982}, "epv": {"常態營業利益率": 0.0217, "常態NOPAT": 9489066287.0, "WACC": 0.0609, "淨現金": -107039386000.0}, "damodaran_fcff": {"銷售/資本": 3.044, "g1": 0.0429, "永續g": 0.03, "目標營業利益率": 0.0217, "WACC": 0.0609, "終值WACC": 0.0995, "有效稅率": 0.2628, "終值佔比": 0.746}, "ri_pb": {"常態ROE": 0.0651, "股權成本r": 0.0995, "留存成長g": 0.0434, "合理PB": 0.387}, "ddm": {"DPS": 1.1376, "g": 0.0895, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 2.0, "BVPS": 25.3079}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 3.4455, "NNWC/股": -35.366, "net-net買點": 2.2982}, "epv": {"常態營業利益率": 0.0217, "常態NOPAT": 9489066287.0, "WACC": 0.0611, "淨現金": -107039386000.0}, "damodaran_fcff": {"銷售/資本": 3.044, "g1": 0.0429, "永續g": 0.03, "目標營業利益率": 0.0217, "WACC": 0.0611, "終值WACC": 0.0995, "有效稅率": 0.2628, "終值佔比": 0.746}, "ri_pb": {"常態ROE": 0.0651, "股權成本r": 0.0995, "留存成長g": 0.0434, "合理PB": 0.387}, "ddm": {"DPS": 1.1376, "g": 0.0895, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -10128,10 +10128,10 @@
         </is>
       </c>
       <c r="C10" s="34" t="n">
-        <v>4.795</v>
+        <v>4.775</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>9.1286</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="E10" s="34" t="n">
         <v>9.2554</v>
@@ -10144,10 +10144,10 @@
         <v>24.345</v>
       </c>
       <c r="I10" s="34" t="n">
-        <v>5.6134</v>
+        <v>5.6199</v>
       </c>
       <c r="J10" s="34" t="n">
-        <v>1.2592</v>
+        <v>1.2595</v>
       </c>
       <c r="K10" s="34" t="n">
         <v>5.6021</v>
@@ -10156,7 +10156,7 @@
         <v>3.1723</v>
       </c>
       <c r="M10" s="34" t="n">
-        <v>6.87</v>
+        <v>6.86</v>
       </c>
       <c r="N10" s="34" t="n">
         <v>9.949999999999999</v>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="Q10" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 0.404, "BVPS": 6.9539}, "graham_formula": {"g(上限10%)": -0.0059, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -6.8094, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 161475000000.0, "g1": -0.0073, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 180806500000.0}, "epv": {"常態營業利益率": 0.0234, "常態NOPAT": 52553004985.0, "WACC": 0.0687, "淨現金": -363061000000.0}, "damodaran_fcff": {"銷售/資本": 2.289, "g1": -0.05, "永續g": 0.03, "目標營業利益率": 0.0234, "WACC": 0.0687, "終值WACC": 0.0995, "有效稅率": 0.1864, "終值佔比": 0.429}, "ri_pb": {"常態ROE": 0.0716, "股權成本r": 0.0995, "留存成長g": 0.0089, "合理PB": 0.692}, "ddm": {"DPS": 0.2556, "g": 0.0052, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 0.404, "BVPS": 6.9539}, "graham_formula": {"g(上限10%)": -0.0059, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -6.8094, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 161475000000.0, "g1": -0.0073, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 180806500000.0}, "epv": {"常態營業利益率": 0.0234, "常態NOPAT": 52553004985.0, "WACC": 0.0686, "淨現金": -363061000000.0}, "damodaran_fcff": {"銷售/資本": 2.289, "g1": -0.05, "永續g": 0.03, "目標營業利益率": 0.0234, "WACC": 0.0686, "終值WACC": 0.0995, "有效稅率": 0.1864, "終值佔比": 0.429}, "ri_pb": {"常態ROE": 0.0716, "股權成本r": 0.0995, "留存成長g": 0.0089, "合理PB": 0.692}, "ddm": {"DPS": 0.2556, "g": 0.0052, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -10187,7 +10187,7 @@
         </is>
       </c>
       <c r="C11" s="34" t="n">
-        <v>391</v>
+        <v>392.6</v>
       </c>
       <c r="D11" s="34" t="n">
         <v>156.7211</v>
@@ -10240,10 +10240,10 @@
         </is>
       </c>
       <c r="C12" s="34" t="n">
-        <v>429.4</v>
+        <v>428.4</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>659.8955</v>
+        <v>659.9072</v>
       </c>
       <c r="E12" s="34" t="n">
         <v>282.2419</v>
@@ -10256,10 +10256,10 @@
         <v>684.9799</v>
       </c>
       <c r="I12" s="34" t="n">
-        <v>369.3796</v>
+        <v>369.4314</v>
       </c>
       <c r="J12" s="34" t="n">
-        <v>459.3594</v>
+        <v>459.3641</v>
       </c>
       <c r="K12" s="34" t="n">
         <v>3850.9861</v>
@@ -10299,10 +10299,10 @@
         </is>
       </c>
       <c r="C13" s="34" t="n">
-        <v>5.815</v>
+        <v>5.825</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>11.4619</v>
+        <v>11.4615</v>
       </c>
       <c r="E13" s="34" t="n">
         <v>15.7849</v>
@@ -10315,7 +10315,7 @@
         <v>12.385</v>
       </c>
       <c r="I13" s="34" t="n">
-        <v>11.4912</v>
+        <v>11.4894</v>
       </c>
       <c r="J13" s="34" t="n">
         <v>8.3786</v>
@@ -10358,10 +10358,10 @@
         </is>
       </c>
       <c r="C14" s="34" t="n">
-        <v>8.994999999999999</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="D14" s="34" t="n">
-        <v>11.1691</v>
+        <v>11.1671</v>
       </c>
       <c r="E14" s="34" t="n">
         <v>14.7897</v>
@@ -10374,10 +10374,10 @@
         <v>24.6392</v>
       </c>
       <c r="I14" s="34" t="n">
-        <v>4.5312</v>
+        <v>4.5216</v>
       </c>
       <c r="J14" s="34" t="n">
-        <v>2.0895</v>
+        <v>2.089</v>
       </c>
       <c r="K14" s="34" t="n">
         <v>3.5176</v>
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="C15" s="34" t="n">
-        <v>18.68</v>
+        <v>18.78</v>
       </c>
       <c r="D15" s="34" t="n">
         <v>53.4079</v>
@@ -10474,10 +10474,10 @@
         </is>
       </c>
       <c r="C16" s="34" t="n">
-        <v>10.07</v>
+        <v>9.98</v>
       </c>
       <c r="D16" s="34" t="n">
-        <v>22.5292</v>
+        <v>22.5324</v>
       </c>
       <c r="E16" s="34" t="n">
         <v>15.4965</v>
@@ -10490,10 +10490,10 @@
         <v>51.231</v>
       </c>
       <c r="I16" s="34" t="n">
-        <v>13.5427</v>
+        <v>13.5574</v>
       </c>
       <c r="J16" s="34" t="n">
-        <v>9.880800000000001</v>
+        <v>9.8819</v>
       </c>
       <c r="K16" s="34" t="n">
         <v>4.5609</v>
@@ -10502,7 +10502,7 @@
         <v>12.6307</v>
       </c>
       <c r="M16" s="34" t="n">
-        <v>8.59</v>
+        <v>8.58</v>
       </c>
       <c r="N16" s="34" t="n">
         <v>9.949999999999999</v>
@@ -10517,7 +10517,7 @@
       </c>
       <c r="Q16" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 0.88, "BVPS": 8.9497}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -3.903, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 412042000000.0, "g1": 0.0563, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 223097000000.0}, "epv": {"常態營業利益率": 0.0765, "常態NOPAT": 173543902291.0, "WACC": 0.0859, "淨現金": -114814000000.0}, "damodaran_fcff": {"銷售/資本": 1.678, "g1": -0.0401, "永續g": 0.03, "目標營業利益率": 0.0765, "WACC": 0.0859, "終值WACC": 0.0995, "有效稅率": 0.2293, "終值佔比": 0.427}, "ri_pb": {"常態ROE": 0.0583, "股權成本r": 0.0995, "留存成長g": 0.0263, "合理PB": 0.438}, "ddm": {"DPS": 0.5289, "g": 0.0484, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 0.88, "BVPS": 8.9497}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -3.903, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 412042000000.0, "g1": 0.0563, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 223097000000.0}, "epv": {"常態營業利益率": 0.0765, "常態NOPAT": 173543902291.0, "WACC": 0.0858, "淨現金": -114814000000.0}, "damodaran_fcff": {"銷售/資本": 1.678, "g1": -0.0401, "永續g": 0.03, "目標營業利益率": 0.0765, "WACC": 0.0858, "終值WACC": 0.0995, "有效稅率": 0.2293, "終值佔比": 0.427}, "ri_pb": {"常態ROE": 0.0583, "股權成本r": 0.0995, "留存成長g": 0.0263, "合理PB": 0.438}, "ddm": {"DPS": 0.5289, "g": 0.0484, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -10533,10 +10533,10 @@
         </is>
       </c>
       <c r="C17" s="34" t="n">
-        <v>24.88</v>
+        <v>24.38</v>
       </c>
       <c r="D17" s="34" t="n">
-        <v>71.7325</v>
+        <v>71.738</v>
       </c>
       <c r="E17" s="34" t="n">
         <v>37.787</v>
@@ -10551,10 +10551,10 @@
         <v>143.8576</v>
       </c>
       <c r="I17" s="34" t="n">
-        <v>41.7224</v>
+        <v>41.753</v>
       </c>
       <c r="J17" s="34" t="n">
-        <v>41.3341</v>
+        <v>41.337</v>
       </c>
       <c r="K17" s="34" t="n">
         <v>64.7799</v>
@@ -10563,7 +10563,7 @@
         <v>161.2592</v>
       </c>
       <c r="M17" s="34" t="n">
-        <v>9.52</v>
+        <v>9.51</v>
       </c>
       <c r="N17" s="34" t="n">
         <v>9.949999999999999</v>
@@ -10578,7 +10578,7 @@
       </c>
       <c r="Q17" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 2.6, "BVPS": 18.0108}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 1.0491, "NNWC/股": 0.1424, "net-net買點": 0.6998}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 209743000000.0, "g1": 0.15, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 31624600000.0}, "epv": {"常態營業利益率": 0.4356, "常態NOPAT": 135656996983.0, "WACC": 0.0952, "淨現金": 246290000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": -0.0198, "永續g": 0.03, "目標營業利益率": 0.4356, "WACC": 0.0952, "終值WACC": 0.0995, "有效稅率": 0.2656, "終值佔比": 0.434}, "ri_pb": {"常態ROE": 0.1412, "股權成本r": 0.0995, "留存成長g": 0.0795, "合理PB": 3.09}, "ddm": {"DPS": 1.2715, "g": 0.0895, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 2.6, "BVPS": 18.0108}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.056}, "ncav": {"NCAV/股": 1.0491, "NNWC/股": 0.1424, "net-net買點": 0.6998}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 209743000000.0, "g1": 0.15, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 31624600000.0}, "epv": {"常態營業利益率": 0.4356, "常態NOPAT": 135656996983.0, "WACC": 0.0951, "淨現金": 246290000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": -0.0198, "永續g": 0.03, "目標營業利益率": 0.4356, "WACC": 0.0951, "終值WACC": 0.0995, "有效稅率": 0.2656, "終值佔比": 0.434}, "ri_pb": {"常態ROE": 0.1412, "股權成本r": 0.0995, "留存成長g": 0.0795, "合理PB": 3.09}, "ddm": {"DPS": 1.2715, "g": 0.0895, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -10594,7 +10594,7 @@
         </is>
       </c>
       <c r="C18" s="34" t="n">
-        <v>9.734999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="D18" s="34" t="n">
         <v>130.7854</v>
@@ -10649,10 +10649,10 @@
         </is>
       </c>
       <c r="C19" s="34" t="n">
-        <v>78.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D19" s="34" t="n">
-        <v>89.6123</v>
+        <v>89.6108</v>
       </c>
       <c r="E19" s="34" t="n">
         <v>114.0363</v>
@@ -10665,10 +10665,10 @@
         <v>92.48090000000001</v>
       </c>
       <c r="I19" s="34" t="n">
-        <v>87.0705</v>
+        <v>87.0635</v>
       </c>
       <c r="J19" s="34" t="n">
-        <v>77.8387</v>
+        <v>77.8382</v>
       </c>
       <c r="K19" s="34" t="n">
         <v>91.19410000000001</v>
@@ -10708,7 +10708,7 @@
         </is>
       </c>
       <c r="C20" s="34" t="n">
-        <v>5.815</v>
+        <v>5.67</v>
       </c>
       <c r="D20" s="34" t="n">
         <v>158.04</v>
@@ -10765,10 +10765,10 @@
         </is>
       </c>
       <c r="C21" s="34" t="n">
-        <v>62.35</v>
+        <v>63.15</v>
       </c>
       <c r="D21" s="34" t="n">
-        <v>6.9166</v>
+        <v>6.9178</v>
       </c>
       <c r="E21" s="34" t="n">
         <v>19.1211</v>
@@ -10779,10 +10779,10 @@
       <c r="G21" s="34" t="inlineStr"/>
       <c r="H21" s="34" t="inlineStr"/>
       <c r="I21" s="34" t="n">
-        <v>10.4145</v>
+        <v>10.4183</v>
       </c>
       <c r="J21" s="34" t="n">
-        <v>0.489</v>
+        <v>0.4892</v>
       </c>
       <c r="K21" s="34" t="n">
         <v>3.7761</v>
@@ -10820,7 +10820,7 @@
         </is>
       </c>
       <c r="C22" s="34" t="n">
-        <v>31.22</v>
+        <v>31.3</v>
       </c>
       <c r="D22" s="34" t="n">
         <v>31.6295</v>
@@ -10836,7 +10836,7 @@
         <v>74.4699</v>
       </c>
       <c r="I22" s="34" t="n">
-        <v>16.8725</v>
+        <v>16.8727</v>
       </c>
       <c r="J22" s="34" t="n">
         <v>19.3515</v>
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="C23" s="34" t="n">
-        <v>7.565</v>
+        <v>7.61</v>
       </c>
       <c r="D23" s="34" t="n">
         <v>98.4873</v>
@@ -10934,10 +10934,10 @@
         </is>
       </c>
       <c r="C24" s="34" t="n">
-        <v>26</v>
+        <v>26.36</v>
       </c>
       <c r="D24" s="34" t="n">
-        <v>28.7651</v>
+        <v>28.7639</v>
       </c>
       <c r="E24" s="34" t="n">
         <v>17.415</v>
@@ -10952,10 +10952,10 @@
         <v>32.0308</v>
       </c>
       <c r="I24" s="34" t="n">
-        <v>21.3543</v>
+        <v>21.3472</v>
       </c>
       <c r="J24" s="34" t="n">
-        <v>26.4515</v>
+        <v>26.451</v>
       </c>
       <c r="K24" s="34" t="n">
         <v>94.2072</v>
@@ -10995,7 +10995,7 @@
         </is>
       </c>
       <c r="C25" s="34" t="n">
-        <v>3.055</v>
+        <v>3.065</v>
       </c>
       <c r="D25" s="34" t="n">
         <v>2.3155</v>
@@ -11095,7 +11095,7 @@
         </is>
       </c>
       <c r="C27" s="34" t="n">
-        <v>53.5</v>
+        <v>54</v>
       </c>
       <c r="D27" s="34" t="n">
         <v>699.6943</v>
@@ -11152,7 +11152,7 @@
         </is>
       </c>
       <c r="C28" s="34" t="n">
-        <v>188.9</v>
+        <v>188.8</v>
       </c>
       <c r="D28" s="34" t="n">
         <v>103.3052</v>
@@ -11170,10 +11170,10 @@
         <v>112.1457</v>
       </c>
       <c r="I28" s="34" t="n">
-        <v>66.59269999999999</v>
+        <v>66.593</v>
       </c>
       <c r="J28" s="34" t="n">
-        <v>79.2976</v>
+        <v>79.29770000000001</v>
       </c>
       <c r="K28" s="34" t="n">
         <v>469.7759</v>
@@ -11213,10 +11213,10 @@
         </is>
       </c>
       <c r="C29" s="34" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="D29" s="34" t="n">
-        <v>13.2428</v>
+        <v>13.2429</v>
       </c>
       <c r="E29" s="34" t="n">
         <v>4.9089</v>
@@ -11231,10 +11231,10 @@
         <v>6.861</v>
       </c>
       <c r="I29" s="34" t="n">
-        <v>7.754</v>
+        <v>7.7547</v>
       </c>
       <c r="J29" s="34" t="n">
-        <v>11.2318</v>
+        <v>11.2319</v>
       </c>
       <c r="K29" s="34" t="n">
         <v>102.7244</v>
@@ -11274,10 +11274,10 @@
         </is>
       </c>
       <c r="C30" s="34" t="n">
-        <v>50.05</v>
+        <v>48.14</v>
       </c>
       <c r="D30" s="34" t="n">
-        <v>84.1289</v>
+        <v>84.2801</v>
       </c>
       <c r="E30" s="34" t="n">
         <v>83.2593</v>
@@ -11290,10 +11290,10 @@
         <v>55.5251</v>
       </c>
       <c r="I30" s="34" t="n">
-        <v>113.9229</v>
+        <v>114.6186</v>
       </c>
       <c r="J30" s="34" t="n">
-        <v>84.38639999999999</v>
+        <v>84.4239</v>
       </c>
       <c r="K30" s="34" t="n">
         <v>165.9242</v>
@@ -11302,7 +11302,7 @@
         <v>106.0289</v>
       </c>
       <c r="M30" s="34" t="n">
-        <v>7.12</v>
+        <v>7.08</v>
       </c>
       <c r="N30" s="34" t="n">
         <v>8.67</v>
@@ -11317,7 +11317,7 @@
       </c>
       <c r="Q30" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 5.35, "BVPS": 42.4945}, "graham_formula": {"g(上限10%)": -0.0102, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -31.3139, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 3560000000.0, "g1": -0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 10906000000.0}, "epv": {"常態營業利益率": 0.0881, "常態NOPAT": 7889920905.0, "WACC": 0.0712, "淨現金": -10879000000.0}, "damodaran_fcff": {"銷售/資本": 1.92, "g1": 0.0056, "永續g": 0.03, "目標營業利益率": 0.0881, "WACC": 0.0712, "終值WACC": 0.0995, "有效稅率": 0.2095, "終值佔比": 0.458}, "ri_pb": {"常態ROE": 0.155, "股權成本r": 0.0867, "留存成長g": 0.0577, "合理PB": 3.354}, "ddm": {"DPS": 3.4077, "g": 0.0475, "r": 0.0867}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 5.35, "BVPS": 42.4945}, "graham_formula": {"g(上限10%)": -0.0102, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -31.3139, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 3560000000.0, "g1": -0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 10906000000.0}, "epv": {"常態營業利益率": 0.0881, "常態NOPAT": 7889920905.0, "WACC": 0.0708, "淨現金": -10879000000.0}, "damodaran_fcff": {"銷售/資本": 1.92, "g1": 0.0056, "永續g": 0.03, "目標營業利益率": 0.0881, "WACC": 0.0708, "終值WACC": 0.0995, "有效稅率": 0.2095, "終值佔比": 0.458}, "ri_pb": {"常態ROE": 0.155, "股權成本r": 0.0867, "留存成長g": 0.0577, "合理PB": 3.354}, "ddm": {"DPS": 3.4077, "g": 0.0475, "r": 0.0867}}</t>
         </is>
       </c>
     </row>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="C31" s="34" t="n">
-        <v>73.95</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="D31" s="34" t="n">
         <v>13.9617</v>
@@ -11357,7 +11357,7 @@
       </c>
       <c r="L31" s="34" t="inlineStr"/>
       <c r="M31" s="34" t="n">
-        <v>12.14</v>
+        <v>12.12</v>
       </c>
       <c r="N31" s="34" t="n">
         <v>10.91</v>
@@ -11388,10 +11388,10 @@
         </is>
       </c>
       <c r="C32" s="34" t="n">
-        <v>543.5</v>
+        <v>547.5</v>
       </c>
       <c r="D32" s="34" t="n">
-        <v>382.6004</v>
+        <v>382.5813</v>
       </c>
       <c r="E32" s="34" t="n">
         <v>170.1479</v>
@@ -11406,10 +11406,10 @@
         <v>309.2153</v>
       </c>
       <c r="I32" s="34" t="n">
-        <v>214.1768</v>
+        <v>214.0916</v>
       </c>
       <c r="J32" s="34" t="n">
-        <v>266.5649</v>
+        <v>266.5564</v>
       </c>
       <c r="K32" s="34" t="n">
         <v>2201.7896</v>
@@ -11418,7 +11418,7 @@
         <v>1178.8895</v>
       </c>
       <c r="M32" s="34" t="n">
-        <v>9.279999999999999</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="N32" s="34" t="n">
         <v>9.949999999999999</v>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="Q32" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 11.58, "BVPS": 81.991}, "graham_formula": {"g(上限10%)": 0.03, "Y公司債": 0.056}, "ncav": {"NCAV/股": 7.3386, "NNWC/股": -39.3809, "net-net買點": 4.8948}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 65810402000.0, "g1": 0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 10748265500.0}, "epv": {"常態營業利益率": 0.1491, "常態NOPAT": 66831915950.0, "WACC": 0.0928, "淨現金": 120569062000.0}, "damodaran_fcff": {"銷售/資本": 2.016, "g1": 0.0884, "永續g": 0.03, "目標營業利益率": 0.1491, "WACC": 0.0928, "終值WACC": 0.0995, "有效稅率": 0.1411, "終值佔比": 0.53}, "ri_pb": {"常態ROE": 0.2098, "股權成本r": 0.0995, "留存成長g": 0.0945, "合理PB": 23.068}, "ddm": {"DPS": 9.295, "g": 0.0895, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 11.58, "BVPS": 81.991}, "graham_formula": {"g(上限10%)": 0.03, "Y公司債": 0.056}, "ncav": {"NCAV/股": 7.3386, "NNWC/股": -39.3809, "net-net買點": 4.8948}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 65810402000.0, "g1": 0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 10748265500.0}, "epv": {"常態營業利益率": 0.1491, "常態NOPAT": 66831915950.0, "WACC": 0.0929, "淨現金": 120569062000.0}, "damodaran_fcff": {"銷售/資本": 2.016, "g1": 0.0884, "永續g": 0.03, "目標營業利益率": 0.1491, "WACC": 0.0929, "終值WACC": 0.0995, "有效稅率": 0.1411, "終值佔比": 0.53}, "ri_pb": {"常態ROE": 0.2098, "股權成本r": 0.0995, "留存成長g": 0.0945, "合理PB": 23.068}, "ddm": {"DPS": 9.295, "g": 0.0895, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -11449,7 +11449,7 @@
         </is>
       </c>
       <c r="C33" s="34" t="n">
-        <v>51.65</v>
+        <v>51.95</v>
       </c>
       <c r="D33" s="34" t="n">
         <v>588.5381</v>
@@ -11504,10 +11504,10 @@
         </is>
       </c>
       <c r="C34" s="34" t="n">
-        <v>4.35</v>
+        <v>4.365</v>
       </c>
       <c r="D34" s="34" t="n">
-        <v>8.3026</v>
+        <v>8.3025</v>
       </c>
       <c r="E34" s="34" t="n">
         <v>3.8731</v>
@@ -11522,10 +11522,10 @@
         <v>14.7347</v>
       </c>
       <c r="I34" s="34" t="n">
-        <v>4.4176</v>
+        <v>4.4172</v>
       </c>
       <c r="J34" s="34" t="n">
-        <v>7.0633</v>
+        <v>7.0632</v>
       </c>
       <c r="K34" s="34" t="n">
         <v>3.6595</v>
@@ -11534,7 +11534,7 @@
         <v>6.6701</v>
       </c>
       <c r="M34" s="34" t="n">
-        <v>9.69</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="N34" s="34" t="n">
         <v>9.949999999999999</v>
@@ -11565,10 +11565,10 @@
         </is>
       </c>
       <c r="C35" s="34" t="n">
-        <v>22.86</v>
+        <v>22.4</v>
       </c>
       <c r="D35" s="34" t="n">
-        <v>12.4346</v>
+        <v>12.437</v>
       </c>
       <c r="E35" s="34" t="n">
         <v>14.9173</v>
@@ -11581,10 +11581,10 @@
         <v>23.633</v>
       </c>
       <c r="I35" s="34" t="n">
-        <v>8.8095</v>
+        <v>8.8215</v>
       </c>
       <c r="J35" s="34" t="n">
-        <v>6.5914</v>
+        <v>6.5909</v>
       </c>
       <c r="K35" s="34" t="n">
         <v>7.2799</v>
@@ -11593,7 +11593,7 @@
         <v>6.9258</v>
       </c>
       <c r="M35" s="34" t="n">
-        <v>9.31</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="N35" s="34" t="n">
         <v>9.949999999999999</v>
@@ -11608,7 +11608,7 @@
       </c>
       <c r="Q35" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 0.73, "BVPS": 9.9973}, "graham_formula": {"g(上限10%)": 0.03, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -2.5412, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 5736271000.0, "g1": 0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 980000000.0}, "epv": {"常態營業利益率": 0.0675, "常態NOPAT": 3992648994.0, "WACC": 0.0931, "淨現金": -3912000000.0}, "damodaran_fcff": {"銷售/資本": 1.24, "g1": 0.15, "永續g": 0.03, "目標營業利益率": 0.0675, "WACC": 0.0931, "終值WACC": 0.0995, "有效稅率": 0.1589, "終值佔比": 1.229}, "ri_pb": {"常態ROE": 0.0691, "股權成本r": 0.0995, "留存成長g": 0.0183, "合理PB": 0.626}, "ddm": {"DPS": 0.4803, "g": 0.0174, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 0.73, "BVPS": 9.9973}, "graham_formula": {"g(上限10%)": 0.03, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -2.5412, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 5736271000.0, "g1": 0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 980000000.0}, "epv": {"常態營業利益率": 0.0675, "常態NOPAT": 3992648994.0, "WACC": 0.093, "淨現金": -3912000000.0}, "damodaran_fcff": {"銷售/資本": 1.24, "g1": 0.15, "永續g": 0.03, "目標營業利益率": 0.0675, "WACC": 0.093, "終值WACC": 0.0995, "有效稅率": 0.1589, "終值佔比": 1.229}, "ri_pb": {"常態ROE": 0.0691, "股權成本r": 0.0995, "留存成長g": 0.0183, "合理PB": 0.626}, "ddm": {"DPS": 0.4803, "g": 0.0174, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -11624,10 +11624,10 @@
         </is>
       </c>
       <c r="C36" s="34" t="n">
-        <v>105</v>
+        <v>106.2</v>
       </c>
       <c r="D36" s="34" t="n">
-        <v>136.1701</v>
+        <v>136.1804</v>
       </c>
       <c r="E36" s="34" t="n">
         <v>135.02</v>
@@ -11640,10 +11640,10 @@
         <v>245.8763</v>
       </c>
       <c r="I36" s="34" t="n">
-        <v>129.2387</v>
+        <v>129.2877</v>
       </c>
       <c r="J36" s="34" t="n">
-        <v>98.4558</v>
+        <v>98.4571</v>
       </c>
       <c r="K36" s="34" t="n">
         <v>54.4545</v>
@@ -11652,7 +11652,7 @@
         <v>55.116</v>
       </c>
       <c r="M36" s="34" t="n">
-        <v>10.76</v>
+        <v>10.75</v>
       </c>
       <c r="N36" s="34" t="n">
         <v>9.949999999999999</v>
@@ -11667,7 +11667,7 @@
       </c>
       <c r="Q36" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 7.69, "BVPS": 77.7484}, "graham_formula": {"g(上限10%)": -0.1587, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -50.5795, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 49191000000.0, "g1": -0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 0.0}, "epv": {"常態營業利益率": 0.0189, "常態NOPAT": 21147865283.0, "WACC": 0.1076, "淨現金": 116354000000.0}, "damodaran_fcff": {"銷售/資本": 4.0, "g1": 0.0776, "永續g": 0.03, "目標營業利益率": 0.0189, "WACC": 0.1076, "終值WACC": 0.0995, "有效稅率": 0.1459, "終值佔比": 0.828}, "ri_pb": {"常態ROE": 0.0679, "股權成本r": 0.0995, "留存成長g": 0.0203, "合理PB": 0.602}, "ddm": {"DPS": 3.6827, "g": 0.0201, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 7.69, "BVPS": 77.7484}, "graham_formula": {"g(上限10%)": -0.1587, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -50.5795, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 49191000000.0, "g1": -0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 0.0}, "epv": {"常態營業利益率": 0.0189, "常態NOPAT": 21147865283.0, "WACC": 0.1075, "淨現金": 116354000000.0}, "damodaran_fcff": {"銷售/資本": 4.0, "g1": 0.0776, "永續g": 0.03, "目標營業利益率": 0.0189, "WACC": 0.1075, "終值WACC": 0.0995, "有效稅率": 0.1459, "終值佔比": 0.828}, "ri_pb": {"常態ROE": 0.0679, "股權成本r": 0.0995, "留存成長g": 0.0203, "合理PB": 0.602}, "ddm": {"DPS": 3.6827, "g": 0.0201, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -11683,10 +11683,10 @@
         </is>
       </c>
       <c r="C37" s="34" t="n">
-        <v>304.8</v>
+        <v>305.8</v>
       </c>
       <c r="D37" s="34" t="n">
-        <v>430.9274</v>
+        <v>430.9121</v>
       </c>
       <c r="E37" s="34" t="n">
         <v>428.4491</v>
@@ -11701,10 +11701,10 @@
         <v>572.925</v>
       </c>
       <c r="I37" s="34" t="n">
-        <v>322.4101</v>
+        <v>322.3404</v>
       </c>
       <c r="J37" s="34" t="n">
-        <v>427.3765</v>
+        <v>427.371</v>
       </c>
       <c r="K37" s="34" t="n">
         <v>40.2781</v>
@@ -11744,10 +11744,10 @@
         </is>
       </c>
       <c r="C38" s="34" t="n">
-        <v>105.8</v>
+        <v>107.5</v>
       </c>
       <c r="D38" s="34" t="n">
-        <v>68.1835</v>
+        <v>68.17149999999999</v>
       </c>
       <c r="E38" s="34" t="n">
         <v>96.09999999999999</v>
@@ -11760,10 +11760,10 @@
         <v>85.75449999999999</v>
       </c>
       <c r="I38" s="34" t="n">
-        <v>64.01649999999999</v>
+        <v>63.9621</v>
       </c>
       <c r="J38" s="34" t="n">
-        <v>61.5737</v>
+        <v>61.5702</v>
       </c>
       <c r="K38" s="34" t="n">
         <v>58.5967</v>
@@ -11772,7 +11772,7 @@
         <v>33.7265</v>
       </c>
       <c r="M38" s="34" t="n">
-        <v>9.279999999999999</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="N38" s="34" t="n">
         <v>9.949999999999999</v>
@@ -11787,7 +11787,7 @@
       </c>
       <c r="Q38" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 5.7, "BVPS": 53.1367}, "graham_formula": {"g(上限10%)": -0.0389, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -23.2597, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 121050000000.0, "g1": -0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 0.0}, "epv": {"常態營業利益率": 0.1155, "常態NOPAT": 84500768832.0, "WACC": 0.0928, "淨現金": 183360000000.0}, "damodaran_fcff": {"銷售/資本": 1.197, "g1": 0.0562, "永續g": 0.03, "目標營業利益率": 0.1155, "WACC": 0.0928, "終值WACC": 0.0995, "有效稅率": 0.3, "終值佔比": 0.598}, "ri_pb": {"常態ROE": 0.0969, "股權成本r": 0.0995, "留存成長g": 0.0507, "合理PB": 0.947}, "ddm": {"DPS": 1.7626, "g": 0.0364, "r": 0.0995}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 5.7, "BVPS": 53.1367}, "graham_formula": {"g(上限10%)": -0.0389, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -23.2597, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 121050000000.0, "g1": -0.05, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 0.0}, "epv": {"常態營業利益率": 0.1155, "常態NOPAT": 84500768832.0, "WACC": 0.0929, "淨現金": 183360000000.0}, "damodaran_fcff": {"銷售/資本": 1.197, "g1": 0.0562, "永續g": 0.03, "目標營業利益率": 0.1155, "WACC": 0.0929, "終值WACC": 0.0995, "有效稅率": 0.3, "終值佔比": 0.598}, "ri_pb": {"常態ROE": 0.0969, "股權成本r": 0.0995, "留存成長g": 0.0507, "合理PB": 0.947}, "ddm": {"DPS": 1.7626, "g": 0.0364, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
@@ -11803,10 +11803,10 @@
         </is>
       </c>
       <c r="C39" s="34" t="n">
-        <v>182</v>
+        <v>182.1</v>
       </c>
       <c r="D39" s="34" t="n">
-        <v>300.1444</v>
+        <v>300.1442</v>
       </c>
       <c r="E39" s="34" t="n">
         <v>121.3865</v>
@@ -11821,10 +11821,10 @@
         <v>378.6999</v>
       </c>
       <c r="I39" s="34" t="n">
-        <v>153.404</v>
+        <v>153.4032</v>
       </c>
       <c r="J39" s="34" t="n">
-        <v>184.6576</v>
+        <v>184.6575</v>
       </c>
       <c r="K39" s="34" t="n">
         <v>1407.6936</v>
@@ -11864,10 +11864,10 @@
         </is>
       </c>
       <c r="C40" s="34" t="n">
-        <v>84.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="D40" s="34" t="n">
-        <v>126.3713</v>
+        <v>126.3732</v>
       </c>
       <c r="E40" s="34" t="n">
         <v>53.8044</v>
@@ -11882,10 +11882,10 @@
         <v>147.8206</v>
       </c>
       <c r="I40" s="34" t="n">
-        <v>67.5265</v>
+        <v>67.53700000000001</v>
       </c>
       <c r="J40" s="34" t="n">
-        <v>108.112</v>
+        <v>108.1132</v>
       </c>
       <c r="K40" s="34" t="n">
         <v>403.9189</v>
@@ -11925,10 +11925,10 @@
         </is>
       </c>
       <c r="C41" s="34" t="n">
-        <v>163.23</v>
+        <v>162.73</v>
       </c>
       <c r="D41" s="34" t="n">
-        <v>200.3009</v>
+        <v>200.301</v>
       </c>
       <c r="E41" s="34" t="n">
         <v>84.8402</v>
@@ -11943,10 +11943,10 @@
         <v>124.1863</v>
       </c>
       <c r="I41" s="34" t="n">
-        <v>116.6281</v>
+        <v>116.6284</v>
       </c>
       <c r="J41" s="34" t="n">
-        <v>134.5585</v>
+        <v>134.5586</v>
       </c>
       <c r="K41" s="34" t="n">
         <v>1437.3751</v>
@@ -11986,7 +11986,7 @@
         </is>
       </c>
       <c r="C42" s="34" t="n">
-        <v>42.19</v>
+        <v>42.67</v>
       </c>
       <c r="D42" s="34" t="n">
         <v>28.4781</v>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="C43" s="34" t="n">
-        <v>117.62</v>
+        <v>119.73</v>
       </c>
       <c r="D43" s="34" t="n">
-        <v>50.5525</v>
+        <v>50.5507</v>
       </c>
       <c r="E43" s="34" t="n">
         <v>50.2832</v>
@@ -12065,10 +12065,10 @@
         <v>38.8126</v>
       </c>
       <c r="I43" s="34" t="n">
-        <v>46.6218</v>
+        <v>46.6136</v>
       </c>
       <c r="J43" s="34" t="n">
-        <v>50.2376</v>
+        <v>50.2369</v>
       </c>
       <c r="K43" s="34" t="n">
         <v>57.5582</v>
@@ -12077,7 +12077,7 @@
         <v>39.5892</v>
       </c>
       <c r="M43" s="34" t="n">
-        <v>8.800000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="N43" s="34" t="n">
         <v>8.9</v>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="Q43" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 4.64, "BVPS": 24.2184}, "graham_formula": {"g(上限10%)": 0.0526, "Y公司債": 0.04}, "ncav": {"NCAV/股": 12.9157, "NNWC/股": 4.1254, "net-net買點": 8.6148}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 1248793852.0, "g1": 0.0526, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 680214571.0}, "epv": {"常態營業利益率": 0.3374, "常態NOPAT": 2321531655.0, "WACC": 0.088, "淨現金": 1080366024.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.0117, "永續g": 0.021, "目標營業利益率": 0.3374, "WACC": 0.088, "終值WACC": 0.089, "有效稅率": 0.1604, "終值佔比": 0.485}, "ri_pb": {"常態ROE": 0.2115, "股權成本r": 0.089, "留存成長g": 0.0, "合理PB": 2.377}, "ddm": {"DPS": 3.2624, "g": 0.0061, "r": 0.089}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 4.64, "BVPS": 24.2184}, "graham_formula": {"g(上限10%)": 0.0526, "Y公司債": 0.04}, "ncav": {"NCAV/股": 12.9157, "NNWC/股": 4.1254, "net-net買點": 8.6148}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 1248793852.0, "g1": 0.0526, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 680214571.0}, "epv": {"常態營業利益率": 0.3374, "常態NOPAT": 2321531655.0, "WACC": 0.0881, "淨現金": 1080366024.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.0117, "永續g": 0.021, "目標營業利益率": 0.3374, "WACC": 0.0881, "終值WACC": 0.089, "有效稅率": 0.1604, "終值佔比": 0.485}, "ri_pb": {"常態ROE": 0.2115, "股權成本r": 0.089, "留存成長g": 0.0, "合理PB": 2.377}, "ddm": {"DPS": 3.2624, "g": 0.0061, "r": 0.089}}</t>
         </is>
       </c>
     </row>
@@ -12108,10 +12108,10 @@
         </is>
       </c>
       <c r="C44" s="34" t="n">
-        <v>1268.64</v>
+        <v>1275.16</v>
       </c>
       <c r="D44" s="34" t="n">
-        <v>1186.8347</v>
+        <v>1186.8346</v>
       </c>
       <c r="E44" s="34" t="n">
         <v>544.9149</v>
@@ -12126,10 +12126,10 @@
         <v>869.8927</v>
       </c>
       <c r="I44" s="34" t="n">
-        <v>838.7851000000001</v>
+        <v>838.7846</v>
       </c>
       <c r="J44" s="34" t="n">
-        <v>1283.6283</v>
+        <v>1283.6282</v>
       </c>
       <c r="K44" s="34" t="n">
         <v>2189.9672</v>
@@ -12169,10 +12169,10 @@
         </is>
       </c>
       <c r="C45" s="34" t="n">
-        <v>28.31</v>
+        <v>28.45</v>
       </c>
       <c r="D45" s="34" t="n">
-        <v>20.5703</v>
+        <v>20.5663</v>
       </c>
       <c r="E45" s="34" t="n">
         <v>16.2467</v>
@@ -12185,10 +12185,10 @@
         <v>31.8328</v>
       </c>
       <c r="I45" s="34" t="n">
-        <v>15.6134</v>
+        <v>15.5946</v>
       </c>
       <c r="J45" s="34" t="n">
-        <v>12.7748</v>
+        <v>12.7739</v>
       </c>
       <c r="K45" s="34" t="n">
         <v>22.7622</v>
@@ -12197,7 +12197,7 @@
         <v>25.8636</v>
       </c>
       <c r="M45" s="34" t="n">
-        <v>5.63</v>
+        <v>5.64</v>
       </c>
       <c r="N45" s="34" t="n">
         <v>6.86</v>
@@ -12212,7 +12212,7 @@
       </c>
       <c r="Q45" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 1.3281, "BVPS": 8.8331}, "graham_formula": {"g(上限10%)": 0.0353, "Y公司債": 0.04}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -12.9023, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 45014393233.0, "g1": 0.0238, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 52328014359.0}, "epv": {"常態營業利益率": 0.4692, "常態NOPAT": 34008540377.0, "WACC": 0.0563, "淨現金": -273993253986.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.0779, "永續g": 0.021, "目標營業利益率": 0.4692, "WACC": 0.0563, "終值WACC": 0.089, "有效稅率": 0.1714, "終值佔比": 0.521}, "ri_pb": {"常態ROE": 0.1553, "股權成本r": 0.0686, "留存成長g": 0.0136, "合理PB": 2.577}, "ddm": {"DPS": 1.3682, "g": 0.0149, "r": 0.0686}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 1.3281, "BVPS": 8.8331}, "graham_formula": {"g(上限10%)": 0.0353, "Y公司債": 0.04}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -12.9023, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 45014393233.0, "g1": 0.0238, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 52328014359.0}, "epv": {"常態營業利益率": 0.4692, "常態NOPAT": 34008540377.0, "WACC": 0.0564, "淨現金": -273993253986.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.0779, "永續g": 0.021, "目標營業利益率": 0.4692, "WACC": 0.0564, "終值WACC": 0.089, "有效稅率": 0.1714, "終值佔比": 0.521}, "ri_pb": {"常態ROE": 0.1553, "股權成本r": 0.0686, "留存成長g": 0.0136, "合理PB": 2.577}, "ddm": {"DPS": 1.3682, "g": 0.0149, "r": 0.0686}}</t>
         </is>
       </c>
     </row>
@@ -12228,10 +12228,10 @@
         </is>
       </c>
       <c r="C46" s="34" t="n">
-        <v>64.2</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="D46" s="34" t="n">
-        <v>35.7515</v>
+        <v>35.7521</v>
       </c>
       <c r="E46" s="34" t="n">
         <v>15.2693</v>
@@ -12246,10 +12246,10 @@
         <v>25.7507</v>
       </c>
       <c r="I46" s="34" t="n">
-        <v>25.502</v>
+        <v>25.5049</v>
       </c>
       <c r="J46" s="34" t="n">
-        <v>36.6837</v>
+        <v>36.6839</v>
       </c>
       <c r="K46" s="34" t="n">
         <v>164.8877</v>
@@ -12289,10 +12289,10 @@
         </is>
       </c>
       <c r="C47" s="34" t="n">
-        <v>57.6</v>
+        <v>57.21</v>
       </c>
       <c r="D47" s="34" t="n">
-        <v>100.9378</v>
+        <v>100.9394</v>
       </c>
       <c r="E47" s="34" t="n">
         <v>38.1089</v>
@@ -12307,10 +12307,10 @@
         <v>94.1225</v>
       </c>
       <c r="I47" s="34" t="n">
-        <v>56.4344</v>
+        <v>56.4432</v>
       </c>
       <c r="J47" s="34" t="n">
-        <v>92.61150000000001</v>
+        <v>92.6126</v>
       </c>
       <c r="K47" s="34" t="n">
         <v>442.9869</v>
@@ -12350,10 +12350,10 @@
         </is>
       </c>
       <c r="C48" s="34" t="n">
-        <v>84.91</v>
+        <v>85.5</v>
       </c>
       <c r="D48" s="34" t="n">
-        <v>113.1304</v>
+        <v>113.129</v>
       </c>
       <c r="E48" s="34" t="n">
         <v>31.0139</v>
@@ -12368,10 +12368,10 @@
         <v>95.557</v>
       </c>
       <c r="I48" s="34" t="n">
-        <v>61.0416</v>
+        <v>61.0343</v>
       </c>
       <c r="J48" s="34" t="n">
-        <v>108.9336</v>
+        <v>108.9327</v>
       </c>
       <c r="K48" s="34" t="n">
         <v>698.9493</v>
@@ -12411,10 +12411,10 @@
         </is>
       </c>
       <c r="C49" s="34" t="n">
-        <v>329.87</v>
+        <v>333.59</v>
       </c>
       <c r="D49" s="34" t="n">
-        <v>81.58629999999999</v>
+        <v>81.5859</v>
       </c>
       <c r="E49" s="34" t="n">
         <v>56.7199</v>
@@ -12429,10 +12429,10 @@
         <v>56.4053</v>
       </c>
       <c r="I49" s="34" t="n">
-        <v>81.3681</v>
+        <v>81.36579999999999</v>
       </c>
       <c r="J49" s="34" t="n">
-        <v>120.5058</v>
+        <v>120.5056</v>
       </c>
       <c r="K49" s="34" t="n">
         <v>38.0978</v>
@@ -12472,7 +12472,7 @@
         </is>
       </c>
       <c r="C50" s="34" t="n">
-        <v>277.5</v>
+        <v>280.66</v>
       </c>
       <c r="D50" s="34" t="n">
         <v>10.4095</v>
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="C51" s="34" t="n">
-        <v>489.03</v>
+        <v>477.12</v>
       </c>
       <c r="D51" s="34" t="n">
         <v>6.6804</v>
@@ -13876,7 +13876,7 @@
         </is>
       </c>
       <c r="D2" s="24" t="n">
-        <v>162.4</v>
+        <v>163.3</v>
       </c>
       <c r="E2" s="24" t="n">
         <v>46.269</v>
@@ -13899,7 +13899,7 @@
         </is>
       </c>
       <c r="K2" s="24" t="n">
-        <v>1.755</v>
+        <v>1.7647</v>
       </c>
       <c r="L2" s="24" t="n">
         <v>69.40349999999999</v>
@@ -13922,22 +13922,22 @@
         </is>
       </c>
       <c r="D3" s="29" t="n">
-        <v>5.43</v>
+        <v>5.415</v>
       </c>
       <c r="E3" s="29" t="n">
-        <v>1.957</v>
+        <v>1.9591</v>
       </c>
       <c r="F3" s="29" t="n">
-        <v>2.9355</v>
+        <v>2.9387</v>
       </c>
       <c r="G3" s="29" t="n">
-        <v>4.5011</v>
+        <v>4.506</v>
       </c>
       <c r="H3" s="29" t="n">
-        <v>5.871</v>
+        <v>5.8774</v>
       </c>
       <c r="I3" s="29" t="n">
-        <v>5.871</v>
+        <v>5.8774</v>
       </c>
       <c r="J3" s="31" t="inlineStr">
         <is>
@@ -13945,10 +13945,10 @@
         </is>
       </c>
       <c r="K3" s="29" t="n">
-        <v>1.3873</v>
+        <v>1.382</v>
       </c>
       <c r="L3" s="29" t="n">
-        <v>2.9355</v>
+        <v>2.9387</v>
       </c>
     </row>
     <row r="4">
@@ -13968,7 +13968,7 @@
         </is>
       </c>
       <c r="D4" s="24" t="n">
-        <v>1.285</v>
+        <v>1.31</v>
       </c>
       <c r="E4" s="24" t="n">
         <v>0.0481</v>
@@ -13991,7 +13991,7 @@
         </is>
       </c>
       <c r="K4" s="24" t="n">
-        <v>13.3487</v>
+        <v>13.6084</v>
       </c>
       <c r="L4" s="24" t="n">
         <v>0.0722</v>
@@ -14014,22 +14014,22 @@
         </is>
       </c>
       <c r="D5" s="14" t="n">
-        <v>86.3</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>53.5906</v>
+        <v>53.5908</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>80.38590000000001</v>
+        <v>80.38630000000001</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>123.2584</v>
+        <v>123.259</v>
       </c>
       <c r="H5" s="14" t="n">
-        <v>160.7718</v>
+        <v>160.7725</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>160.7718</v>
+        <v>160.7725</v>
       </c>
       <c r="J5" s="16" t="inlineStr">
         <is>
@@ -14037,10 +14037,10 @@
         </is>
       </c>
       <c r="K5" s="14" t="n">
-        <v>0.8052</v>
+        <v>0.8048</v>
       </c>
       <c r="L5" s="14" t="n">
-        <v>80.38590000000001</v>
+        <v>80.38630000000001</v>
       </c>
     </row>
     <row r="6">
@@ -14060,22 +14060,22 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>38.8</v>
+        <v>38.74</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>71.2572</v>
+        <v>71.2589</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>106.8858</v>
+        <v>106.8884</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>163.8916</v>
+        <v>163.8955</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>213.7717</v>
+        <v>213.7768</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>213.7717</v>
+        <v>213.7768</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
@@ -14083,10 +14083,10 @@
         </is>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.2723</v>
+        <v>0.2718</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>106.8858</v>
+        <v>106.8884</v>
       </c>
     </row>
     <row r="7">
@@ -14106,22 +14106,22 @@
         </is>
       </c>
       <c r="D7" s="19" t="n">
-        <v>28.92</v>
+        <v>28.97</v>
       </c>
       <c r="E7" s="19" t="n">
-        <v>11.5307</v>
+        <v>11.5306</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>17.2961</v>
+        <v>17.2959</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>26.5207</v>
+        <v>26.5204</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>34.5922</v>
+        <v>34.5918</v>
       </c>
       <c r="I7" s="19" t="n">
-        <v>34.5922</v>
+        <v>34.5918</v>
       </c>
       <c r="J7" s="21" t="inlineStr">
         <is>
@@ -14129,10 +14129,10 @@
         </is>
       </c>
       <c r="K7" s="19" t="n">
-        <v>1.254</v>
+        <v>1.2562</v>
       </c>
       <c r="L7" s="19" t="n">
-        <v>17.2961</v>
+        <v>17.2959</v>
       </c>
     </row>
     <row r="8">
@@ -14152,22 +14152,22 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.315</v>
+        <v>1.305</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.9004</v>
+        <v>1.9005</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.8506</v>
+        <v>2.8508</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.3709</v>
+        <v>4.3713</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.7011</v>
+        <v>5.7016</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5.7011</v>
+        <v>5.7016</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
@@ -14175,10 +14175,10 @@
         </is>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.346</v>
+        <v>0.3433</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>2.8506</v>
+        <v>2.8508</v>
       </c>
     </row>
     <row r="9">
@@ -14198,22 +14198,22 @@
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>34.42</v>
+        <v>34.96</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>20.424</v>
+        <v>20.3815</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>30.6361</v>
+        <v>30.5723</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>46.9753</v>
+        <v>46.8775</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>61.2721</v>
+        <v>61.1446</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>61.2721</v>
+        <v>61.1446</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -14221,10 +14221,10 @@
         </is>
       </c>
       <c r="K9" s="14" t="n">
-        <v>0.8426</v>
+        <v>0.8576</v>
       </c>
       <c r="L9" s="14" t="n">
-        <v>30.6361</v>
+        <v>30.5723</v>
       </c>
     </row>
     <row r="10">
@@ -14244,22 +14244,22 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>4.795</v>
+        <v>4.775</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>4.5643</v>
+        <v>4.565</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>6.8465</v>
+        <v>6.8475</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>10.4979</v>
+        <v>10.4995</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>13.6929</v>
+        <v>13.695</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>13.6929</v>
+        <v>13.695</v>
       </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
@@ -14267,10 +14267,10 @@
         </is>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.5253</v>
+        <v>0.523</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>6.8465</v>
+        <v>6.8475</v>
       </c>
     </row>
     <row r="11">
@@ -14290,7 +14290,7 @@
         </is>
       </c>
       <c r="D11" s="24" t="n">
-        <v>391</v>
+        <v>392.6</v>
       </c>
       <c r="E11" s="24" t="n">
         <v>78.36060000000001</v>
@@ -14313,7 +14313,7 @@
         </is>
       </c>
       <c r="K11" s="24" t="n">
-        <v>2.4949</v>
+        <v>2.5051</v>
       </c>
       <c r="L11" s="24" t="n">
         <v>117.5408</v>
@@ -14336,22 +14336,22 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>429.4</v>
+        <v>428.4</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>329.9478</v>
+        <v>329.9536</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>494.9216</v>
+        <v>494.9304</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>758.8799</v>
+        <v>758.8933</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>989.8433</v>
+        <v>989.8609</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>989.8433</v>
+        <v>989.8609</v>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
@@ -14359,10 +14359,10 @@
         </is>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.6506999999999999</v>
+        <v>0.6492</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>494.9216</v>
+        <v>494.9304</v>
       </c>
     </row>
     <row r="13">
@@ -14382,22 +14382,22 @@
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>5.815</v>
+        <v>5.825</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>5.7309</v>
+        <v>5.7308</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>8.596399999999999</v>
+        <v>8.5961</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>13.1812</v>
+        <v>13.1808</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>17.1928</v>
+        <v>17.1923</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>17.1928</v>
+        <v>17.1923</v>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
@@ -14405,10 +14405,10 @@
         </is>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.5073</v>
+        <v>0.5082</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>8.596399999999999</v>
+        <v>8.5961</v>
       </c>
     </row>
     <row r="14">
@@ -14428,22 +14428,22 @@
         </is>
       </c>
       <c r="D14" s="14" t="n">
-        <v>8.994999999999999</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>5.5846</v>
+        <v>5.5835</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>8.376899999999999</v>
+        <v>8.375299999999999</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>12.8445</v>
+        <v>12.8421</v>
       </c>
       <c r="H14" s="14" t="n">
-        <v>16.7537</v>
+        <v>16.7506</v>
       </c>
       <c r="I14" s="14" t="n">
-        <v>16.7537</v>
+        <v>16.7506</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -14451,10 +14451,10 @@
         </is>
       </c>
       <c r="K14" s="14" t="n">
-        <v>0.8053</v>
+        <v>0.8086</v>
       </c>
       <c r="L14" s="14" t="n">
-        <v>8.376899999999999</v>
+        <v>8.375299999999999</v>
       </c>
     </row>
     <row r="15">
@@ -14474,7 +14474,7 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>18.68</v>
+        <v>18.78</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>26.704</v>
@@ -14497,7 +14497,7 @@
         </is>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.3498</v>
+        <v>0.3516</v>
       </c>
       <c r="L15" s="4" t="n">
         <v>40.056</v>
@@ -14520,22 +14520,22 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>10.07</v>
+        <v>9.98</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>11.2646</v>
+        <v>11.2662</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>16.8969</v>
+        <v>16.8993</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>25.9086</v>
+        <v>25.9123</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>33.7938</v>
+        <v>33.7986</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>33.7938</v>
+        <v>33.7986</v>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
@@ -14543,10 +14543,10 @@
         </is>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.447</v>
+        <v>0.4429</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>16.8969</v>
+        <v>16.8993</v>
       </c>
     </row>
     <row r="17">
@@ -14566,22 +14566,22 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>24.88</v>
+        <v>24.38</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>35.8663</v>
+        <v>35.869</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>53.7994</v>
+        <v>53.8035</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>82.4924</v>
+        <v>82.4987</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>107.5988</v>
+        <v>107.607</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>107.5988</v>
+        <v>107.607</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
@@ -14589,10 +14589,10 @@
         </is>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.3468</v>
+        <v>0.3398</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>53.7994</v>
+        <v>53.8035</v>
       </c>
     </row>
     <row r="18">
@@ -14612,7 +14612,7 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>9.734999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>65.3927</v>
@@ -14635,7 +14635,7 @@
         </is>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.0745</v>
       </c>
       <c r="L18" s="4" t="n">
         <v>98.0891</v>
@@ -14658,22 +14658,22 @@
         </is>
       </c>
       <c r="D19" s="14" t="n">
-        <v>78.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>44.8062</v>
+        <v>44.8054</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>67.2093</v>
+        <v>67.2081</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>103.0542</v>
+        <v>103.0524</v>
       </c>
       <c r="H19" s="14" t="n">
-        <v>134.4185</v>
+        <v>134.4162</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>134.4185</v>
+        <v>134.4162</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -14681,10 +14681,10 @@
         </is>
       </c>
       <c r="K19" s="14" t="n">
-        <v>0.8782</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="L19" s="14" t="n">
-        <v>67.2093</v>
+        <v>67.2081</v>
       </c>
     </row>
     <row r="20">
@@ -14704,7 +14704,7 @@
         </is>
       </c>
       <c r="D20" s="29" t="n">
-        <v>5.815</v>
+        <v>5.67</v>
       </c>
       <c r="E20" s="29" t="n">
         <v>79.02</v>
@@ -14727,7 +14727,7 @@
         </is>
       </c>
       <c r="K20" s="29" t="n">
-        <v>0.0368</v>
+        <v>0.0359</v>
       </c>
       <c r="L20" s="29" t="n">
         <v>102.726</v>
@@ -14750,22 +14750,22 @@
         </is>
       </c>
       <c r="D21" s="24" t="n">
-        <v>62.35</v>
+        <v>63.15</v>
       </c>
       <c r="E21" s="24" t="n">
-        <v>3.4583</v>
+        <v>3.4589</v>
       </c>
       <c r="F21" s="24" t="n">
-        <v>5.1874</v>
+        <v>5.1883</v>
       </c>
       <c r="G21" s="24" t="n">
-        <v>7.9541</v>
+        <v>7.9554</v>
       </c>
       <c r="H21" s="24" t="n">
-        <v>10.3749</v>
+        <v>10.3766</v>
       </c>
       <c r="I21" s="24" t="n">
-        <v>10.3749</v>
+        <v>10.3766</v>
       </c>
       <c r="J21" s="26" t="inlineStr">
         <is>
@@ -14773,10 +14773,10 @@
         </is>
       </c>
       <c r="K21" s="24" t="n">
-        <v>9.0146</v>
+        <v>9.1287</v>
       </c>
       <c r="L21" s="24" t="n">
-        <v>5.1874</v>
+        <v>5.1883</v>
       </c>
     </row>
     <row r="22">
@@ -14796,10 +14796,10 @@
         </is>
       </c>
       <c r="D22" s="14" t="n">
-        <v>31.22</v>
+        <v>31.3</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>15.8147</v>
+        <v>15.8148</v>
       </c>
       <c r="F22" s="14" t="n">
         <v>23.7221</v>
@@ -14808,10 +14808,10 @@
         <v>36.3739</v>
       </c>
       <c r="H22" s="14" t="n">
-        <v>47.4442</v>
+        <v>47.4443</v>
       </c>
       <c r="I22" s="14" t="n">
-        <v>47.4442</v>
+        <v>47.4443</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         </is>
       </c>
       <c r="K22" s="14" t="n">
-        <v>0.9871</v>
+        <v>0.9896</v>
       </c>
       <c r="L22" s="14" t="n">
         <v>23.7221</v>
@@ -14842,7 +14842,7 @@
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>7.565</v>
+        <v>7.61</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>49.2437</v>
@@ -14865,7 +14865,7 @@
         </is>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="L23" s="4" t="n">
         <v>73.8655</v>
@@ -14888,22 +14888,22 @@
         </is>
       </c>
       <c r="D24" s="14" t="n">
-        <v>26</v>
+        <v>26.36</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>14.3826</v>
+        <v>14.382</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>21.5739</v>
+        <v>21.5729</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>33.0799</v>
+        <v>33.0785</v>
       </c>
       <c r="H24" s="14" t="n">
-        <v>43.1477</v>
+        <v>43.1459</v>
       </c>
       <c r="I24" s="14" t="n">
-        <v>43.1477</v>
+        <v>43.1459</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -14911,10 +14911,10 @@
         </is>
       </c>
       <c r="K24" s="14" t="n">
-        <v>0.9039</v>
+        <v>0.9164</v>
       </c>
       <c r="L24" s="14" t="n">
-        <v>21.5739</v>
+        <v>21.5729</v>
       </c>
     </row>
     <row r="25">
@@ -14934,7 +14934,7 @@
         </is>
       </c>
       <c r="D25" s="19" t="n">
-        <v>3.055</v>
+        <v>3.065</v>
       </c>
       <c r="E25" s="19" t="n">
         <v>1.1577</v>
@@ -14957,7 +14957,7 @@
         </is>
       </c>
       <c r="K25" s="19" t="n">
-        <v>1.3194</v>
+        <v>1.3237</v>
       </c>
       <c r="L25" s="19" t="n">
         <v>1.7366</v>
@@ -15012,7 +15012,7 @@
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>53.5</v>
+        <v>54</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>349.8471</v>
@@ -15035,7 +15035,7 @@
         </is>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.0765</v>
+        <v>0.0772</v>
       </c>
       <c r="L27" s="4" t="n">
         <v>524.7707</v>
@@ -15058,7 +15058,7 @@
         </is>
       </c>
       <c r="D28" s="24" t="n">
-        <v>188.9</v>
+        <v>188.8</v>
       </c>
       <c r="E28" s="24" t="n">
         <v>51.6526</v>
@@ -15070,10 +15070,10 @@
         <v>118.801</v>
       </c>
       <c r="H28" s="24" t="n">
-        <v>154.9578</v>
+        <v>154.9579</v>
       </c>
       <c r="I28" s="24" t="n">
-        <v>154.9578</v>
+        <v>154.9579</v>
       </c>
       <c r="J28" s="26" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         </is>
       </c>
       <c r="K28" s="24" t="n">
-        <v>1.8286</v>
+        <v>1.8276</v>
       </c>
       <c r="L28" s="24" t="n">
         <v>77.4789</v>
@@ -15104,22 +15104,22 @@
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="E29" s="4" t="n">
         <v>6.6214</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>9.9321</v>
+        <v>9.9322</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>15.2292</v>
+        <v>15.2293</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>19.8641</v>
+        <v>19.8643</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>19.8641</v>
+        <v>19.8643</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
@@ -15127,10 +15127,10 @@
         </is>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.2515</v>
+        <v>0.2469</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>9.9321</v>
+        <v>9.9322</v>
       </c>
     </row>
     <row r="30">
@@ -15150,22 +15150,22 @@
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>50.05</v>
+        <v>48.14</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>42.0645</v>
+        <v>42.1401</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>63.0967</v>
+        <v>63.2101</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>96.7483</v>
+        <v>96.9221</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>126.1934</v>
+        <v>126.4202</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>126.1934</v>
+        <v>126.4202</v>
       </c>
       <c r="J30" s="11" t="inlineStr">
         <is>
@@ -15173,10 +15173,10 @@
         </is>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.5949</v>
+        <v>0.5712</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>63.0967</v>
+        <v>63.2101</v>
       </c>
     </row>
     <row r="31">
@@ -15196,7 +15196,7 @@
         </is>
       </c>
       <c r="D31" s="24" t="n">
-        <v>73.95</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="E31" s="24" t="n">
         <v>6.9808</v>
@@ -15219,7 +15219,7 @@
         </is>
       </c>
       <c r="K31" s="24" t="n">
-        <v>5.2966</v>
+        <v>5.379</v>
       </c>
       <c r="L31" s="24" t="n">
         <v>10.4713</v>
@@ -15242,22 +15242,22 @@
         </is>
       </c>
       <c r="D32" s="19" t="n">
-        <v>543.5</v>
+        <v>547.5</v>
       </c>
       <c r="E32" s="19" t="n">
-        <v>191.3002</v>
+        <v>191.2906</v>
       </c>
       <c r="F32" s="19" t="n">
-        <v>286.9503</v>
+        <v>286.936</v>
       </c>
       <c r="G32" s="19" t="n">
-        <v>439.9904</v>
+        <v>439.9685</v>
       </c>
       <c r="H32" s="19" t="n">
-        <v>573.9005</v>
+        <v>573.8719</v>
       </c>
       <c r="I32" s="19" t="n">
-        <v>573.9005</v>
+        <v>573.8719</v>
       </c>
       <c r="J32" s="21" t="inlineStr">
         <is>
@@ -15265,10 +15265,10 @@
         </is>
       </c>
       <c r="K32" s="19" t="n">
-        <v>1.4205</v>
+        <v>1.4311</v>
       </c>
       <c r="L32" s="19" t="n">
-        <v>286.9503</v>
+        <v>286.936</v>
       </c>
     </row>
     <row r="33">
@@ -15288,7 +15288,7 @@
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>51.65</v>
+        <v>51.95</v>
       </c>
       <c r="E33" s="4" t="n">
         <v>294.269</v>
@@ -15311,7 +15311,7 @@
         </is>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.0878</v>
+        <v>0.0883</v>
       </c>
       <c r="L33" s="4" t="n">
         <v>441.4036</v>
@@ -15334,10 +15334,10 @@
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>4.35</v>
+        <v>4.365</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>4.1513</v>
+        <v>4.1512</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>6.2269</v>
@@ -15346,10 +15346,10 @@
         <v>9.5479</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>12.4538</v>
+        <v>12.4537</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>12.4538</v>
+        <v>12.4537</v>
       </c>
       <c r="J34" s="11" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         </is>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.5239</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="L34" s="9" t="n">
         <v>6.2269</v>
@@ -15380,22 +15380,22 @@
         </is>
       </c>
       <c r="D35" s="24" t="n">
-        <v>22.86</v>
+        <v>22.4</v>
       </c>
       <c r="E35" s="24" t="n">
-        <v>6.2173</v>
+        <v>6.2185</v>
       </c>
       <c r="F35" s="24" t="n">
-        <v>9.326000000000001</v>
+        <v>9.3277</v>
       </c>
       <c r="G35" s="24" t="n">
-        <v>14.2998</v>
+        <v>14.3025</v>
       </c>
       <c r="H35" s="24" t="n">
-        <v>18.6519</v>
+        <v>18.6554</v>
       </c>
       <c r="I35" s="24" t="n">
-        <v>18.6519</v>
+        <v>18.6554</v>
       </c>
       <c r="J35" s="26" t="inlineStr">
         <is>
@@ -15403,10 +15403,10 @@
         </is>
       </c>
       <c r="K35" s="24" t="n">
-        <v>1.8384</v>
+        <v>1.8011</v>
       </c>
       <c r="L35" s="24" t="n">
-        <v>9.326000000000001</v>
+        <v>9.3277</v>
       </c>
     </row>
     <row r="36">
@@ -15426,22 +15426,22 @@
         </is>
       </c>
       <c r="D36" s="14" t="n">
-        <v>105</v>
+        <v>106.2</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>68.08499999999999</v>
+        <v>68.0902</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>102.1276</v>
+        <v>102.1353</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>156.5956</v>
+        <v>156.6074</v>
       </c>
       <c r="H36" s="14" t="n">
-        <v>204.2551</v>
+        <v>204.2706</v>
       </c>
       <c r="I36" s="14" t="n">
-        <v>204.2551</v>
+        <v>204.2706</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -15449,10 +15449,10 @@
         </is>
       </c>
       <c r="K36" s="14" t="n">
-        <v>0.7711</v>
+        <v>0.7798</v>
       </c>
       <c r="L36" s="14" t="n">
-        <v>102.1276</v>
+        <v>102.1353</v>
       </c>
     </row>
     <row r="37">
@@ -15472,22 +15472,22 @@
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>304.8</v>
+        <v>305.8</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>215.4637</v>
+        <v>215.456</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>323.1955</v>
+        <v>323.1841</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>495.5665</v>
+        <v>495.5489</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>646.391</v>
+        <v>646.3681</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>646.391</v>
+        <v>646.3681</v>
       </c>
       <c r="J37" s="11" t="inlineStr">
         <is>
@@ -15495,10 +15495,10 @@
         </is>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.7073</v>
+        <v>0.7097</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>323.1955</v>
+        <v>323.1841</v>
       </c>
     </row>
     <row r="38">
@@ -15518,22 +15518,22 @@
         </is>
       </c>
       <c r="D38" s="24" t="n">
-        <v>105.8</v>
+        <v>107.5</v>
       </c>
       <c r="E38" s="24" t="n">
-        <v>34.0917</v>
+        <v>34.0858</v>
       </c>
       <c r="F38" s="24" t="n">
-        <v>51.1376</v>
+        <v>51.1286</v>
       </c>
       <c r="G38" s="24" t="n">
-        <v>78.411</v>
+        <v>78.3972</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>102.2752</v>
+        <v>102.2573</v>
       </c>
       <c r="I38" s="24" t="n">
-        <v>102.2752</v>
+        <v>102.2573</v>
       </c>
       <c r="J38" s="26" t="inlineStr">
         <is>
@@ -15541,10 +15541,10 @@
         </is>
       </c>
       <c r="K38" s="24" t="n">
-        <v>1.5517</v>
+        <v>1.5769</v>
       </c>
       <c r="L38" s="24" t="n">
-        <v>51.1376</v>
+        <v>51.1286</v>
       </c>
     </row>
     <row r="39">
@@ -15564,22 +15564,22 @@
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>182</v>
+        <v>182.1</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>150.0722</v>
+        <v>150.0721</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>225.1083</v>
+        <v>225.1082</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>345.1661</v>
+        <v>345.1659</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>450.2166</v>
+        <v>450.2164</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>450.2166</v>
+        <v>450.2164</v>
       </c>
       <c r="J39" s="11" t="inlineStr">
         <is>
@@ -15587,10 +15587,10 @@
         </is>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.6067</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>225.1083</v>
+        <v>225.1082</v>
       </c>
     </row>
     <row r="40">
@@ -15610,22 +15610,22 @@
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>84.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>63.1856</v>
+        <v>63.1866</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>94.77849999999999</v>
+        <v>94.7799</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>145.327</v>
+        <v>145.3292</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>189.5569</v>
+        <v>189.5598</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>189.5569</v>
+        <v>189.5598</v>
       </c>
       <c r="J40" s="11" t="inlineStr">
         <is>
@@ -15633,10 +15633,10 @@
         </is>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.6718</v>
+        <v>0.6679</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>94.77849999999999</v>
+        <v>94.7799</v>
       </c>
     </row>
     <row r="41">
@@ -15656,22 +15656,22 @@
         </is>
       </c>
       <c r="D41" s="14" t="n">
-        <v>163.23</v>
+        <v>162.73</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>100.1504</v>
+        <v>100.1505</v>
       </c>
       <c r="F41" s="14" t="n">
         <v>150.2257</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>230.346</v>
+        <v>230.3461</v>
       </c>
       <c r="H41" s="14" t="n">
-        <v>300.4513</v>
+        <v>300.4514</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>300.4513</v>
+        <v>300.4514</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         </is>
       </c>
       <c r="K41" s="14" t="n">
-        <v>0.8149</v>
+        <v>0.8124</v>
       </c>
       <c r="L41" s="14" t="n">
         <v>150.2257</v>
@@ -15702,7 +15702,7 @@
         </is>
       </c>
       <c r="D42" s="19" t="n">
-        <v>42.19</v>
+        <v>42.67</v>
       </c>
       <c r="E42" s="19" t="n">
         <v>14.2391</v>
@@ -15725,7 +15725,7 @@
         </is>
       </c>
       <c r="K42" s="19" t="n">
-        <v>1.4815</v>
+        <v>1.4983</v>
       </c>
       <c r="L42" s="19" t="n">
         <v>21.3586</v>
@@ -15748,22 +15748,22 @@
         </is>
       </c>
       <c r="D43" s="24" t="n">
-        <v>117.62</v>
+        <v>119.73</v>
       </c>
       <c r="E43" s="24" t="n">
-        <v>25.2763</v>
+        <v>25.2753</v>
       </c>
       <c r="F43" s="24" t="n">
-        <v>37.9144</v>
+        <v>37.913</v>
       </c>
       <c r="G43" s="24" t="n">
-        <v>58.1354</v>
+        <v>58.1333</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>75.8288</v>
+        <v>75.82599999999999</v>
       </c>
       <c r="I43" s="24" t="n">
-        <v>75.8288</v>
+        <v>75.82599999999999</v>
       </c>
       <c r="J43" s="26" t="inlineStr">
         <is>
@@ -15771,10 +15771,10 @@
         </is>
       </c>
       <c r="K43" s="24" t="n">
-        <v>2.3267</v>
+        <v>2.3685</v>
       </c>
       <c r="L43" s="24" t="n">
-        <v>37.9144</v>
+        <v>37.913</v>
       </c>
     </row>
     <row r="44">
@@ -15794,22 +15794,22 @@
         </is>
       </c>
       <c r="D44" s="14" t="n">
-        <v>1268.64</v>
+        <v>1275.16</v>
       </c>
       <c r="E44" s="14" t="n">
-        <v>593.4174</v>
+        <v>593.4173</v>
       </c>
       <c r="F44" s="14" t="n">
-        <v>890.126</v>
+        <v>890.1259</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>1364.8599</v>
+        <v>1364.8598</v>
       </c>
       <c r="H44" s="14" t="n">
-        <v>1780.2521</v>
+        <v>1780.2519</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>1780.2521</v>
+        <v>1780.2519</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -15817,10 +15817,10 @@
         </is>
       </c>
       <c r="K44" s="14" t="n">
-        <v>1.0689</v>
+        <v>1.0744</v>
       </c>
       <c r="L44" s="14" t="n">
-        <v>890.126</v>
+        <v>890.1259</v>
       </c>
     </row>
     <row r="45">
@@ -15840,22 +15840,22 @@
         </is>
       </c>
       <c r="D45" s="19" t="n">
-        <v>28.31</v>
+        <v>28.45</v>
       </c>
       <c r="E45" s="19" t="n">
-        <v>10.2852</v>
+        <v>10.2831</v>
       </c>
       <c r="F45" s="19" t="n">
-        <v>15.4277</v>
+        <v>15.4247</v>
       </c>
       <c r="G45" s="19" t="n">
-        <v>23.6558</v>
+        <v>23.6512</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>30.8555</v>
+        <v>30.8494</v>
       </c>
       <c r="I45" s="19" t="n">
-        <v>30.8555</v>
+        <v>30.8494</v>
       </c>
       <c r="J45" s="21" t="inlineStr">
         <is>
@@ -15863,10 +15863,10 @@
         </is>
       </c>
       <c r="K45" s="19" t="n">
-        <v>1.3763</v>
+        <v>1.3833</v>
       </c>
       <c r="L45" s="19" t="n">
-        <v>15.4277</v>
+        <v>15.4247</v>
       </c>
     </row>
     <row r="46">
@@ -15886,22 +15886,22 @@
         </is>
       </c>
       <c r="D46" s="24" t="n">
-        <v>64.2</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="E46" s="24" t="n">
-        <v>17.8758</v>
+        <v>17.876</v>
       </c>
       <c r="F46" s="24" t="n">
-        <v>26.8137</v>
+        <v>26.814</v>
       </c>
       <c r="G46" s="24" t="n">
-        <v>41.1143</v>
+        <v>41.1149</v>
       </c>
       <c r="H46" s="24" t="n">
-        <v>53.6273</v>
+        <v>53.6281</v>
       </c>
       <c r="I46" s="24" t="n">
-        <v>53.6273</v>
+        <v>53.6281</v>
       </c>
       <c r="J46" s="26" t="inlineStr">
         <is>
@@ -15909,10 +15909,10 @@
         </is>
       </c>
       <c r="K46" s="24" t="n">
-        <v>1.7957</v>
+        <v>1.7921</v>
       </c>
       <c r="L46" s="24" t="n">
-        <v>26.8137</v>
+        <v>26.814</v>
       </c>
     </row>
     <row r="47">
@@ -15932,22 +15932,22 @@
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>57.6</v>
+        <v>57.21</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>50.4689</v>
+        <v>50.4697</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>75.7033</v>
+        <v>75.7046</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>116.0784</v>
+        <v>116.0803</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>151.4066</v>
+        <v>151.4091</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>151.4066</v>
+        <v>151.4091</v>
       </c>
       <c r="J47" s="11" t="inlineStr">
         <is>
@@ -15955,56 +15955,56 @@
         </is>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.5706</v>
+        <v>0.5668</v>
       </c>
       <c r="L47" s="9" t="n">
-        <v>75.7033</v>
+        <v>75.7046</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="12" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>605117</t>
         </is>
       </c>
-      <c r="B48" s="13" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>德业股份</t>
         </is>
       </c>
-      <c r="C48" s="12" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="D48" s="14" t="n">
-        <v>84.91</v>
-      </c>
-      <c r="E48" s="14" t="n">
-        <v>56.5652</v>
-      </c>
-      <c r="F48" s="14" t="n">
-        <v>84.84780000000001</v>
-      </c>
-      <c r="G48" s="14" t="n">
-        <v>130.0999</v>
-      </c>
-      <c r="H48" s="14" t="n">
-        <v>169.6955</v>
-      </c>
-      <c r="I48" s="14" t="n">
-        <v>169.6955</v>
-      </c>
-      <c r="J48" s="16" t="inlineStr">
-        <is>
-          <t>合理</t>
-        </is>
-      </c>
-      <c r="K48" s="14" t="n">
-        <v>0.7506</v>
-      </c>
-      <c r="L48" s="14" t="n">
-        <v>84.84780000000001</v>
+      <c r="D48" s="9" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="E48" s="9" t="n">
+        <v>56.5645</v>
+      </c>
+      <c r="F48" s="9" t="n">
+        <v>84.8467</v>
+      </c>
+      <c r="G48" s="9" t="n">
+        <v>130.0983</v>
+      </c>
+      <c r="H48" s="9" t="n">
+        <v>169.6934</v>
+      </c>
+      <c r="I48" s="9" t="n">
+        <v>169.6934</v>
+      </c>
+      <c r="J48" s="11" t="inlineStr">
+        <is>
+          <t>便宜</t>
+        </is>
+      </c>
+      <c r="K48" s="9" t="n">
+        <v>0.7558</v>
+      </c>
+      <c r="L48" s="9" t="n">
+        <v>84.8467</v>
       </c>
     </row>
     <row r="49">
@@ -16024,22 +16024,22 @@
         </is>
       </c>
       <c r="D49" s="24" t="n">
-        <v>329.87</v>
+        <v>333.59</v>
       </c>
       <c r="E49" s="24" t="n">
-        <v>40.7932</v>
+        <v>40.793</v>
       </c>
       <c r="F49" s="24" t="n">
-        <v>61.1898</v>
+        <v>61.1895</v>
       </c>
       <c r="G49" s="24" t="n">
-        <v>93.82429999999999</v>
+        <v>93.82380000000001</v>
       </c>
       <c r="H49" s="24" t="n">
-        <v>122.3795</v>
+        <v>122.3789</v>
       </c>
       <c r="I49" s="24" t="n">
-        <v>122.3795</v>
+        <v>122.3789</v>
       </c>
       <c r="J49" s="26" t="inlineStr">
         <is>
@@ -16047,10 +16047,10 @@
         </is>
       </c>
       <c r="K49" s="24" t="n">
-        <v>4.0432</v>
+        <v>4.0888</v>
       </c>
       <c r="L49" s="24" t="n">
-        <v>61.1898</v>
+        <v>61.1895</v>
       </c>
     </row>
     <row r="50">
@@ -16070,7 +16070,7 @@
         </is>
       </c>
       <c r="D50" s="24" t="n">
-        <v>277.5</v>
+        <v>280.66</v>
       </c>
       <c r="E50" s="24" t="n">
         <v>5.2047</v>
@@ -16093,7 +16093,7 @@
         </is>
       </c>
       <c r="K50" s="24" t="n">
-        <v>26.6583</v>
+        <v>26.9619</v>
       </c>
       <c r="L50" s="24" t="n">
         <v>7.8071</v>
@@ -16116,7 +16116,7 @@
         </is>
       </c>
       <c r="D51" s="24" t="n">
-        <v>489.03</v>
+        <v>477.12</v>
       </c>
       <c r="E51" s="24" t="n">
         <v>3.3402</v>
@@ -16139,7 +16139,7 @@
         </is>
       </c>
       <c r="K51" s="24" t="n">
-        <v>73.2032</v>
+        <v>71.4203</v>
       </c>
       <c r="L51" s="24" t="n">
         <v>5.0103</v>
@@ -24573,7 +24573,7 @@
         </is>
       </c>
       <c r="G14" s="12" t="n">
-        <v>83.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
@@ -26516,58 +26516,58 @@
       </c>
     </row>
     <row r="48" ht="118" customHeight="1">
-      <c r="A48" s="12" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>605117</t>
         </is>
       </c>
-      <c r="B48" s="13" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>德业股份</t>
         </is>
       </c>
-      <c r="C48" s="12" t="n">
+      <c r="C48" s="7" t="n">
         <v>8.9</v>
       </c>
-      <c r="D48" s="12" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>★★★★☆</t>
         </is>
       </c>
-      <c r="E48" s="16" t="inlineStr">
-        <is>
-          <t>合理</t>
-        </is>
-      </c>
-      <c r="F48" s="12" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>便宜</t>
         </is>
       </c>
-      <c r="G48" s="12" t="n">
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>便宜</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="n">
         <v>91.5</v>
       </c>
-      <c r="H48" s="13" t="inlineStr">
+      <c r="H48" s="8" t="inlineStr">
         <is>
           <t>ROE中位35.87%、毛利率38.04%、負債權益比0.175924（規則式）</t>
         </is>
       </c>
-      <c r="I48" s="13" t="inlineStr">
+      <c r="I48" s="8" t="inlineStr">
         <is>
           <t>【規則式後備結論，未經 AI】依現有財報：獲利連續性 10/10，ROE 十年中位 35.87%，毛利率 38.04%，負債權益比 0.175924，流動比率 1.470908，利息保障 103.059121。多模型加權內在價值 113.1392，區間 55.5052~108.9394，現價/內在價值 0.7188，判定為「便宜」，估值信心 91.5/100，格雷厄姆檢查通過 3/7 項。請以此為基礎自行覆核假設，特別是成長率、營業利益率與折現率三個敏感變數。</t>
         </is>
       </c>
-      <c r="J48" s="13" t="inlineStr">
+      <c r="J48" s="8" t="inlineStr">
         <is>
           <t>未經 AI 覆核 / 模型假設敏感 / 資料完整度</t>
         </is>
       </c>
-      <c r="K48" s="12" t="inlineStr">
+      <c r="K48" s="7" t="inlineStr">
         <is>
           <t>qwen-plus</t>
         </is>
       </c>
-      <c r="L48" s="12" t="inlineStr">
+      <c r="L48" s="7" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>

--- a/docs/reports/內在價值報告_20260911.xlsx
+++ b/docs/reports/內在價值報告_20260911.xlsx
@@ -951,13 +951,13 @@
       </c>
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="4" t="n">
-        <v>428.03</v>
+        <v>431.58</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>6308.2365</v>
+        <v>6308.2336</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>564.5288</v>
+        <v>564.5172</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>5285.4917</v>
@@ -969,7 +969,7 @@
         <v>25</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>4731.1774</v>
+        <v>4731.1752</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>507</v>
+        <v>506.13</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>1600617.8442</v>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="4" t="n">
-        <v>188.3</v>
+        <v>189.59</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>142031.6652</v>
@@ -3611,25 +3611,25 @@
       </c>
       <c r="G25" s="8" t="inlineStr"/>
       <c r="H25" s="9" t="n">
-        <v>266.35</v>
+        <v>267.45</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>480.8077</v>
+        <v>480.8068</v>
       </c>
       <c r="J25" s="9" t="n">
         <v>9.3416</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>17.7689</v>
+        <v>17.7687</v>
       </c>
       <c r="L25" s="10" t="n">
-        <v>-44.6</v>
+        <v>-44.4</v>
       </c>
       <c r="M25" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>360.6058</v>
+        <v>360.6051</v>
       </c>
       <c r="O25" s="7" t="inlineStr">
         <is>
@@ -4819,10 +4819,10 @@
       </c>
       <c r="G35" s="13" t="inlineStr"/>
       <c r="H35" s="14" t="n">
-        <v>388.28</v>
+        <v>378.85</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>369.4225</v>
+        <v>369.4243</v>
       </c>
       <c r="J35" s="14" t="n">
         <v>64.4277</v>
@@ -4831,13 +4831,13 @@
         <v>314.2098</v>
       </c>
       <c r="L35" s="15" t="n">
-        <v>5.1</v>
+        <v>2.6</v>
       </c>
       <c r="M35" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N35" s="14" t="n">
-        <v>277.0669</v>
+        <v>277.0682</v>
       </c>
       <c r="O35" s="12" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="G41" s="23" t="inlineStr"/>
       <c r="H41" s="24" t="n">
-        <v>492.44</v>
+        <v>493.604</v>
       </c>
       <c r="I41" s="24" t="n">
         <v>82.8946</v>
@@ -5559,7 +5559,7 @@
         <v>86.59699999999999</v>
       </c>
       <c r="L41" s="25" t="n">
-        <v>494.1</v>
+        <v>495.5</v>
       </c>
       <c r="M41" s="25" t="n">
         <v>25</v>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="G42" s="23" t="inlineStr"/>
       <c r="H42" s="24" t="n">
-        <v>218.36</v>
+        <v>219.66</v>
       </c>
       <c r="I42" s="24" t="n">
         <v>46.2765</v>
@@ -5681,7 +5681,7 @@
         <v>21.2943</v>
       </c>
       <c r="L42" s="25" t="n">
-        <v>371.9</v>
+        <v>374.7</v>
       </c>
       <c r="M42" s="25" t="n">
         <v>25</v>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="G50" s="23" t="inlineStr"/>
       <c r="H50" s="24" t="n">
-        <v>251.89</v>
+        <v>255.065</v>
       </c>
       <c r="I50" s="24" t="n">
         <v>107.0856</v>
@@ -6647,7 +6647,7 @@
         <v>487.2973</v>
       </c>
       <c r="L50" s="25" t="n">
-        <v>135.2</v>
+        <v>138.2</v>
       </c>
       <c r="M50" s="25" t="n">
         <v>25</v>
@@ -6757,10 +6757,10 @@
       </c>
       <c r="G51" s="23" t="inlineStr"/>
       <c r="H51" s="24" t="n">
-        <v>332.6</v>
+        <v>339.95</v>
       </c>
       <c r="I51" s="24" t="n">
-        <v>62.8561</v>
+        <v>62.856</v>
       </c>
       <c r="J51" s="24" t="n">
         <v>2.0172</v>
@@ -6769,7 +6769,7 @@
         <v>15.3128</v>
       </c>
       <c r="L51" s="25" t="n">
-        <v>429.1</v>
+        <v>440.8</v>
       </c>
       <c r="M51" s="25" t="n">
         <v>25</v>
@@ -6879,25 +6879,25 @@
       </c>
       <c r="G52" s="23" t="inlineStr"/>
       <c r="H52" s="24" t="n">
-        <v>1123</v>
+        <v>1121.23</v>
       </c>
       <c r="I52" s="24" t="n">
-        <v>544.7494</v>
+        <v>544.7503</v>
       </c>
       <c r="J52" s="24" t="n">
-        <v>58.8509</v>
+        <v>58.8511</v>
       </c>
       <c r="K52" s="24" t="n">
         <v>202.834</v>
       </c>
       <c r="L52" s="25" t="n">
-        <v>106.1</v>
+        <v>105.8</v>
       </c>
       <c r="M52" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N52" s="24" t="n">
-        <v>408.5621</v>
+        <v>408.5627</v>
       </c>
       <c r="O52" s="22" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="G53" s="23" t="inlineStr"/>
       <c r="H53" s="24" t="n">
-        <v>367.21</v>
+        <v>369.888</v>
       </c>
       <c r="I53" s="24" t="n">
         <v>54.2597</v>
@@ -7013,13 +7013,13 @@
         <v>61.9902</v>
       </c>
       <c r="L53" s="25" t="n">
-        <v>576.8</v>
+        <v>581.7</v>
       </c>
       <c r="M53" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N53" s="24" t="n">
-        <v>40.6948</v>
+        <v>40.6947</v>
       </c>
       <c r="O53" s="22" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
       </c>
       <c r="G54" s="23" t="inlineStr"/>
       <c r="H54" s="24" t="n">
-        <v>284.95</v>
+        <v>287.91</v>
       </c>
       <c r="I54" s="24" t="n">
         <v>26.9669</v>
@@ -7135,7 +7135,7 @@
         <v>8.8208</v>
       </c>
       <c r="L54" s="25" t="n">
-        <v>956.7</v>
+        <v>967.6</v>
       </c>
       <c r="M54" s="25" t="n">
         <v>25</v>
@@ -7607,10 +7607,10 @@
       </c>
       <c r="G58" s="23" t="inlineStr"/>
       <c r="H58" s="24" t="n">
-        <v>326.57</v>
+        <v>334.84</v>
       </c>
       <c r="I58" s="24" t="n">
-        <v>46.6846</v>
+        <v>46.6843</v>
       </c>
       <c r="J58" s="24" t="n">
         <v>9.446</v>
@@ -7619,13 +7619,13 @@
         <v>17.6955</v>
       </c>
       <c r="L58" s="25" t="n">
-        <v>599.5</v>
+        <v>617.2</v>
       </c>
       <c r="M58" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N58" s="24" t="n">
-        <v>35.0135</v>
+        <v>35.0133</v>
       </c>
       <c r="O58" s="22" t="inlineStr">
         <is>
@@ -7729,10 +7729,10 @@
       </c>
       <c r="G59" s="23" t="inlineStr"/>
       <c r="H59" s="24" t="n">
-        <v>158.85</v>
+        <v>156.285</v>
       </c>
       <c r="I59" s="24" t="n">
-        <v>21.4774</v>
+        <v>21.4775</v>
       </c>
       <c r="J59" s="24" t="n">
         <v>4.7985</v>
@@ -7741,7 +7741,7 @@
         <v>5.0405</v>
       </c>
       <c r="L59" s="25" t="n">
-        <v>639.6</v>
+        <v>627.7</v>
       </c>
       <c r="M59" s="25" t="n">
         <v>25</v>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="G60" s="23" t="inlineStr"/>
       <c r="H60" s="24" t="n">
-        <v>977.41</v>
+        <v>973.4450000000001</v>
       </c>
       <c r="I60" s="24" t="n">
         <v>76.5334</v>
@@ -7861,7 +7861,7 @@
         <v>18.9283</v>
       </c>
       <c r="L60" s="25" t="n">
-        <v>1177.1</v>
+        <v>1171.9</v>
       </c>
       <c r="M60" s="25" t="n">
         <v>25</v>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="G61" s="23" t="inlineStr"/>
       <c r="H61" s="24" t="n">
-        <v>142.97</v>
+        <v>143.925</v>
       </c>
       <c r="I61" s="24" t="n">
         <v>20.2227</v>
@@ -7983,7 +7983,7 @@
         <v>13.4653</v>
       </c>
       <c r="L61" s="25" t="n">
-        <v>607</v>
+        <v>611.7</v>
       </c>
       <c r="M61" s="25" t="n">
         <v>25</v>
@@ -8093,7 +8093,7 @@
       </c>
       <c r="G62" s="23" t="inlineStr"/>
       <c r="H62" s="24" t="n">
-        <v>34.56</v>
+        <v>34.745</v>
       </c>
       <c r="I62" s="24" t="n">
         <v>4.3617</v>
@@ -8105,7 +8105,7 @@
         <v>5.2053</v>
       </c>
       <c r="L62" s="25" t="n">
-        <v>692.4</v>
+        <v>696.6</v>
       </c>
       <c r="M62" s="25" t="n">
         <v>25</v>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="G63" s="23" t="inlineStr"/>
       <c r="H63" s="24" t="n">
-        <v>363.56</v>
+        <v>364.38</v>
       </c>
       <c r="I63" s="24" t="n">
         <v>4.5288</v>
@@ -8227,7 +8227,7 @@
         <v>4.6574</v>
       </c>
       <c r="L63" s="25" t="n">
-        <v>7927.7</v>
+        <v>7945.8</v>
       </c>
       <c r="M63" s="25" t="n">
         <v>25</v>
@@ -8337,7 +8337,7 @@
       </c>
       <c r="G64" s="23" t="inlineStr"/>
       <c r="H64" s="24" t="n">
-        <v>105.73</v>
+        <v>105.95</v>
       </c>
       <c r="I64" s="24" t="n">
         <v>11.8315</v>
@@ -8349,7 +8349,7 @@
         <v>28.2934</v>
       </c>
       <c r="L64" s="25" t="n">
-        <v>793.6</v>
+        <v>795.5</v>
       </c>
       <c r="M64" s="25" t="n">
         <v>25</v>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="G65" s="23" t="inlineStr"/>
       <c r="H65" s="24" t="n">
-        <v>87.83</v>
+        <v>87.93000000000001</v>
       </c>
       <c r="I65" s="24" t="n">
         <v>14.0496</v>
@@ -8471,7 +8471,7 @@
         <v>11.4611</v>
       </c>
       <c r="L65" s="25" t="n">
-        <v>525.1</v>
+        <v>525.9</v>
       </c>
       <c r="M65" s="25" t="n">
         <v>25</v>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="G70" s="28" t="inlineStr"/>
       <c r="H70" s="29" t="n">
-        <v>100.32</v>
+        <v>103.09</v>
       </c>
       <c r="I70" s="29" t="n">
         <v>3056.102</v>
@@ -9081,7 +9081,7 @@
         <v>3056.102</v>
       </c>
       <c r="L70" s="30" t="n">
-        <v>-96.7</v>
+        <v>-96.59999999999999</v>
       </c>
       <c r="M70" s="30" t="n">
         <v>25</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="G71" s="28" t="inlineStr"/>
       <c r="H71" s="29" t="n">
-        <v>128.56</v>
+        <v>136.31</v>
       </c>
       <c r="I71" s="29" t="n">
         <v>21296.5965</v>
@@ -12594,10 +12594,10 @@
         </is>
       </c>
       <c r="C52" s="34" t="n">
-        <v>326.57</v>
+        <v>334.84</v>
       </c>
       <c r="D52" s="34" t="n">
-        <v>46.6846</v>
+        <v>46.6843</v>
       </c>
       <c r="E52" s="34" t="n">
         <v>9.446</v>
@@ -12608,10 +12608,10 @@
       <c r="G52" s="34" t="inlineStr"/>
       <c r="H52" s="34" t="inlineStr"/>
       <c r="I52" s="34" t="n">
-        <v>8.9003</v>
+        <v>8.8994</v>
       </c>
       <c r="J52" s="34" t="n">
-        <v>12.4165</v>
+        <v>12.4164</v>
       </c>
       <c r="K52" s="34" t="n">
         <v>494.7644</v>
@@ -12649,7 +12649,7 @@
         </is>
       </c>
       <c r="C53" s="34" t="n">
-        <v>251.89</v>
+        <v>255.065</v>
       </c>
       <c r="D53" s="34" t="n">
         <v>107.0856</v>
@@ -12684,7 +12684,7 @@
       </c>
       <c r="Q53" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 1.9, "BVPS": 2.657}, "graham_formula": {"g(上限10%)": -0.3274, "Y公司債": 0.053}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -1.8337, "net-net買點": 0.0}, "epv": {"常態營業利益率": 0.0332, "常態NOPAT": 2289056815.0, "WACC": 0.0878, "淨現金": -130244000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.1267, "永續g": 0.04, "目標營業利益率": 0.0332, "WACC": 0.0878, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": -0.791}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.088, "留存成長g": 0.083, "合理PB": 183.4}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 1.9, "BVPS": 2.657}, "graham_formula": {"g(上限10%)": -0.3274, "Y公司債": 0.053}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -1.8337, "net-net買點": 0.0}, "epv": {"常態營業利益率": 0.0332, "常態NOPAT": 2289056815.0, "WACC": 0.0878, "淨現金": -130244000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.1267, "永續g": 0.04, "目標營業利益率": 0.0332, "WACC": 0.0878, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": -0.792}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.088, "留存成長g": 0.083, "合理PB": 183.4}}</t>
         </is>
       </c>
     </row>
@@ -12700,7 +12700,7 @@
         </is>
       </c>
       <c r="C54" s="34" t="n">
-        <v>507</v>
+        <v>506.13</v>
       </c>
       <c r="D54" s="34" t="n">
         <v>1600617.8442</v>
@@ -12751,7 +12751,7 @@
         </is>
       </c>
       <c r="C55" s="34" t="n">
-        <v>284.95</v>
+        <v>287.91</v>
       </c>
       <c r="D55" s="34" t="n">
         <v>26.9669</v>
@@ -12790,7 +12790,7 @@
       </c>
       <c r="Q55" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 1.25, "BVPS": 1.7915}, "graham_formula": {"g(上限10%)": -0.0991, "Y公司債": 0.053}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -0.7283, "net-net買點": 0.0}, "epv": {"常態營業利益率": 0.3149, "常態NOPAT": 418630512.0, "WACC": 0.0878, "淨現金": -1788624000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.15, "永續g": 0.04, "目標營業利益率": 0.3149, "WACC": 0.0878, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": 0.698}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.088, "留存成長g": 0.083, "合理PB": 183.4}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 1.25, "BVPS": 1.7915}, "graham_formula": {"g(上限10%)": -0.0991, "Y公司債": 0.053}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -0.7283, "net-net買點": 0.0}, "epv": {"常態營業利益率": 0.3149, "常態NOPAT": 418630512.0, "WACC": 0.0879, "淨現金": -1788624000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.15, "永續g": 0.04, "目標營業利益率": 0.3149, "WACC": 0.0879, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": 0.698}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.088, "留存成長g": 0.083, "合理PB": 183.4}}</t>
         </is>
       </c>
     </row>
@@ -12806,10 +12806,10 @@
         </is>
       </c>
       <c r="C56" s="34" t="n">
-        <v>158.85</v>
+        <v>156.285</v>
       </c>
       <c r="D56" s="34" t="n">
-        <v>21.4774</v>
+        <v>21.4775</v>
       </c>
       <c r="E56" s="34" t="n">
         <v>3.6112</v>
@@ -12859,10 +12859,10 @@
         </is>
       </c>
       <c r="C57" s="34" t="n">
-        <v>332.6</v>
+        <v>339.95</v>
       </c>
       <c r="D57" s="34" t="n">
-        <v>62.8561</v>
+        <v>62.856</v>
       </c>
       <c r="E57" s="34" t="n">
         <v>14.6499</v>
@@ -12916,7 +12916,7 @@
         </is>
       </c>
       <c r="C58" s="34" t="n">
-        <v>100.32</v>
+        <v>103.09</v>
       </c>
       <c r="D58" s="34" t="n">
         <v>3056.102</v>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="L58" s="34" t="inlineStr"/>
       <c r="M58" s="34" t="n">
-        <v>8.24</v>
+        <v>8.25</v>
       </c>
       <c r="N58" s="34" t="n">
         <v>8.800000000000001</v>
@@ -12947,7 +12947,7 @@
       </c>
       <c r="Q58" s="33" t="inlineStr">
         <is>
-          <t>{"ncav": {"NCAV/股": 0.0, "NNWC/股": -11.4777, "net-net買點": 0.0}, "epv": {"常態營業利益率": 0.0424, "常態NOPAT": 324749100.0, "WACC": 0.0824, "淨現金": -35887000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": -0.0088, "永續g": 0.04, "目標營業利益率": 0.0424, "WACC": 0.0824, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": 0.687}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.088, "留存成長g": 0.083, "合理PB": 183.4}}</t>
+          <t>{"ncav": {"NCAV/股": 0.0, "NNWC/股": -11.4777, "net-net買點": 0.0}, "epv": {"常態營業利益率": 0.0424, "常態NOPAT": 324749100.0, "WACC": 0.0825, "淨現金": -35887000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": -0.0088, "永續g": 0.04, "目標營業利益率": 0.0424, "WACC": 0.0825, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": 0.687}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.088, "留存成長g": 0.083, "合理PB": 183.4}}</t>
         </is>
       </c>
     </row>
@@ -12963,10 +12963,10 @@
         </is>
       </c>
       <c r="C59" s="34" t="n">
-        <v>266.35</v>
+        <v>267.45</v>
       </c>
       <c r="D59" s="34" t="n">
-        <v>480.8077</v>
+        <v>480.8068</v>
       </c>
       <c r="E59" s="34" t="n">
         <v>9.3416</v>
@@ -12977,10 +12977,10 @@
       <c r="G59" s="34" t="inlineStr"/>
       <c r="H59" s="34" t="inlineStr"/>
       <c r="I59" s="34" t="n">
-        <v>15.4589</v>
+        <v>15.4561</v>
       </c>
       <c r="J59" s="34" t="n">
-        <v>17.7689</v>
+        <v>17.7687</v>
       </c>
       <c r="K59" s="34" t="n">
         <v>6466.5299</v>
@@ -13018,7 +13018,7 @@
         </is>
       </c>
       <c r="C60" s="34" t="n">
-        <v>87.83</v>
+        <v>87.93000000000001</v>
       </c>
       <c r="D60" s="34" t="n">
         <v>14.0496</v>
@@ -13071,10 +13071,10 @@
         </is>
       </c>
       <c r="C61" s="34" t="n">
-        <v>1123</v>
+        <v>1121.23</v>
       </c>
       <c r="D61" s="34" t="n">
-        <v>544.7494</v>
+        <v>544.7503</v>
       </c>
       <c r="E61" s="34" t="n">
         <v>83.318</v>
@@ -13085,10 +13085,10 @@
       <c r="G61" s="34" t="inlineStr"/>
       <c r="H61" s="34" t="inlineStr"/>
       <c r="I61" s="34" t="n">
-        <v>15.5683</v>
+        <v>15.5712</v>
       </c>
       <c r="J61" s="34" t="n">
-        <v>58.8509</v>
+        <v>58.8511</v>
       </c>
       <c r="K61" s="34" t="n">
         <v>6600.4801</v>
@@ -13126,7 +13126,7 @@
         </is>
       </c>
       <c r="C62" s="34" t="n">
-        <v>492.44</v>
+        <v>493.604</v>
       </c>
       <c r="D62" s="34" t="n">
         <v>82.8946</v>
@@ -13181,7 +13181,7 @@
         </is>
       </c>
       <c r="C63" s="34" t="n">
-        <v>128.56</v>
+        <v>136.31</v>
       </c>
       <c r="D63" s="34" t="n">
         <v>21296.5965</v>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="L63" s="34" t="inlineStr"/>
       <c r="M63" s="34" t="n">
-        <v>9.380000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="N63" s="34" t="n">
         <v>10.15</v>
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="C64" s="34" t="n">
-        <v>977.41</v>
+        <v>973.4450000000001</v>
       </c>
       <c r="D64" s="34" t="n">
         <v>76.5334</v>
@@ -13285,7 +13285,7 @@
         </is>
       </c>
       <c r="C65" s="34" t="n">
-        <v>218.36</v>
+        <v>219.66</v>
       </c>
       <c r="D65" s="34" t="n">
         <v>46.2765</v>
@@ -13342,7 +13342,7 @@
         </is>
       </c>
       <c r="C66" s="34" t="n">
-        <v>142.97</v>
+        <v>143.925</v>
       </c>
       <c r="D66" s="34" t="n">
         <v>20.2227</v>
@@ -13397,7 +13397,7 @@
         </is>
       </c>
       <c r="C67" s="34" t="n">
-        <v>34.56</v>
+        <v>34.745</v>
       </c>
       <c r="D67" s="34" t="n">
         <v>4.3617</v>
@@ -13452,7 +13452,7 @@
         </is>
       </c>
       <c r="C68" s="34" t="n">
-        <v>188.3</v>
+        <v>189.59</v>
       </c>
       <c r="D68" s="34" t="n">
         <v>142031.6652</v>
@@ -13503,7 +13503,7 @@
         </is>
       </c>
       <c r="C69" s="34" t="n">
-        <v>363.56</v>
+        <v>364.38</v>
       </c>
       <c r="D69" s="34" t="n">
         <v>4.5288</v>
@@ -13560,10 +13560,10 @@
         </is>
       </c>
       <c r="C70" s="34" t="n">
-        <v>428.03</v>
+        <v>431.58</v>
       </c>
       <c r="D70" s="34" t="n">
-        <v>6308.2365</v>
+        <v>6308.2336</v>
       </c>
       <c r="E70" s="34" t="n">
         <v>1397.4929</v>
@@ -13576,10 +13576,10 @@
       </c>
       <c r="H70" s="34" t="inlineStr"/>
       <c r="I70" s="34" t="n">
-        <v>564.5288</v>
+        <v>564.5172</v>
       </c>
       <c r="J70" s="34" t="n">
-        <v>908.5828</v>
+        <v>908.5816</v>
       </c>
       <c r="K70" s="34" t="n">
         <v>71261.0684</v>
@@ -13601,7 +13601,7 @@
       </c>
       <c r="Q70" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 223.39, "BVPS": 388.5554}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.053}, "ncav": {"NCAV/股": 100.5449, "NNWC/股": 48.9033, "net-net買點": 67.0635}, "epv": {"常態營業利益率": 0.4902, "常態NOPAT": 515111631753.0, "WACC": 0.0876, "淨現金": 3468786165000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.15, "永續g": 0.04, "目標營業利益率": 0.4902, "WACC": 0.0876, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": 0.642}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.088, "留存成長g": 0.083, "合理PB": 183.4}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 223.39, "BVPS": 388.5554}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.053}, "ncav": {"NCAV/股": 100.5449, "NNWC/股": 48.9033, "net-net買點": 67.0635}, "epv": {"常態營業利益率": 0.4902, "常態NOPAT": 515111631753.0, "WACC": 0.0877, "淨現金": 3468786165000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.15, "永續g": 0.04, "目標營業利益率": 0.4902, "WACC": 0.0877, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": 0.642}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.088, "留存成長g": 0.083, "合理PB": 183.4}}</t>
         </is>
       </c>
     </row>
@@ -13617,10 +13617,10 @@
         </is>
       </c>
       <c r="C71" s="34" t="n">
-        <v>388.28</v>
+        <v>378.85</v>
       </c>
       <c r="D71" s="34" t="n">
-        <v>369.4225</v>
+        <v>369.4243</v>
       </c>
       <c r="E71" s="34" t="n">
         <v>64.4277</v>
@@ -13631,7 +13631,7 @@
       <c r="G71" s="34" t="inlineStr"/>
       <c r="H71" s="34" t="inlineStr"/>
       <c r="I71" s="34" t="n">
-        <v>4.9336</v>
+        <v>4.9376</v>
       </c>
       <c r="J71" s="34" t="inlineStr"/>
       <c r="K71" s="34" t="n">
@@ -13654,7 +13654,7 @@
       </c>
       <c r="Q71" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 13.28, "BVPS": 13.892}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.053}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -22.0318, "net-net買點": 0.0}, "epv": {"常態營業利益率": 0.0771, "常態NOPAT": 6658990545.0, "WACC": 0.0867, "淨現金": -41860000000.0}, "damodaran_fcff": {"銷售/資本": 0.81, "g1": 0.11, "永續g": 0.04, "目標營業利益率": 0.0771, "WACC": 0.0867, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": 1.655}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.088, "留存成長g": 0.083, "合理PB": 183.4}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 13.28, "BVPS": 13.892}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.053}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -22.0318, "net-net買點": 0.0}, "epv": {"常態營業利益率": 0.0771, "常態NOPAT": 6658990545.0, "WACC": 0.0866, "淨現金": -41860000000.0}, "damodaran_fcff": {"銷售/資本": 0.81, "g1": 0.11, "永續g": 0.04, "目標營業利益率": 0.0771, "WACC": 0.0866, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": 1.655}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.088, "留存成長g": 0.083, "合理PB": 183.4}}</t>
         </is>
       </c>
     </row>
@@ -13670,7 +13670,7 @@
         </is>
       </c>
       <c r="C72" s="34" t="n">
-        <v>367.21</v>
+        <v>369.888</v>
       </c>
       <c r="D72" s="34" t="n">
         <v>54.2597</v>
@@ -13684,7 +13684,7 @@
       <c r="G72" s="34" t="inlineStr"/>
       <c r="H72" s="34" t="inlineStr"/>
       <c r="I72" s="34" t="n">
-        <v>4.9095</v>
+        <v>4.9094</v>
       </c>
       <c r="J72" s="34" t="n">
         <v>9.348100000000001</v>
@@ -13725,7 +13725,7 @@
         </is>
       </c>
       <c r="C73" s="34" t="n">
-        <v>105.73</v>
+        <v>105.95</v>
       </c>
       <c r="D73" s="34" t="n">
         <v>11.8315</v>
@@ -16162,22 +16162,22 @@
         </is>
       </c>
       <c r="D52" s="24" t="n">
-        <v>326.57</v>
+        <v>334.84</v>
       </c>
       <c r="E52" s="24" t="n">
-        <v>23.3423</v>
+        <v>23.3422</v>
       </c>
       <c r="F52" s="24" t="n">
-        <v>35.0135</v>
+        <v>35.0133</v>
       </c>
       <c r="G52" s="24" t="n">
-        <v>53.6873</v>
+        <v>53.687</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>70.0269</v>
+        <v>70.0265</v>
       </c>
       <c r="I52" s="24" t="n">
-        <v>70.0269</v>
+        <v>70.0265</v>
       </c>
       <c r="J52" s="26" t="inlineStr">
         <is>
@@ -16185,10 +16185,10 @@
         </is>
       </c>
       <c r="K52" s="24" t="n">
-        <v>6.9952</v>
+        <v>7.1724</v>
       </c>
       <c r="L52" s="24" t="n">
-        <v>35.0135</v>
+        <v>35.0133</v>
       </c>
     </row>
     <row r="53">
@@ -16208,7 +16208,7 @@
         </is>
       </c>
       <c r="D53" s="24" t="n">
-        <v>251.89</v>
+        <v>255.065</v>
       </c>
       <c r="E53" s="24" t="n">
         <v>53.5428</v>
@@ -16231,7 +16231,7 @@
         </is>
       </c>
       <c r="K53" s="24" t="n">
-        <v>2.3522</v>
+        <v>2.3819</v>
       </c>
       <c r="L53" s="24" t="n">
         <v>80.3142</v>
@@ -16254,7 +16254,7 @@
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>507</v>
+        <v>506.13</v>
       </c>
       <c r="E54" s="4" t="n">
         <v>800308.9221</v>
@@ -16300,7 +16300,7 @@
         </is>
       </c>
       <c r="D55" s="24" t="n">
-        <v>284.95</v>
+        <v>287.91</v>
       </c>
       <c r="E55" s="24" t="n">
         <v>13.4835</v>
@@ -16323,7 +16323,7 @@
         </is>
       </c>
       <c r="K55" s="24" t="n">
-        <v>10.5666</v>
+        <v>10.6764</v>
       </c>
       <c r="L55" s="24" t="n">
         <v>20.2252</v>
@@ -16346,7 +16346,7 @@
         </is>
       </c>
       <c r="D56" s="24" t="n">
-        <v>158.85</v>
+        <v>156.285</v>
       </c>
       <c r="E56" s="24" t="n">
         <v>10.7387</v>
@@ -16369,7 +16369,7 @@
         </is>
       </c>
       <c r="K56" s="24" t="n">
-        <v>7.3961</v>
+        <v>7.2767</v>
       </c>
       <c r="L56" s="24" t="n">
         <v>16.1081</v>
@@ -16392,7 +16392,7 @@
         </is>
       </c>
       <c r="D57" s="24" t="n">
-        <v>332.6</v>
+        <v>339.95</v>
       </c>
       <c r="E57" s="24" t="n">
         <v>31.428</v>
@@ -16401,7 +16401,7 @@
         <v>47.142</v>
       </c>
       <c r="G57" s="24" t="n">
-        <v>72.28449999999999</v>
+        <v>72.28440000000001</v>
       </c>
       <c r="H57" s="24" t="n">
         <v>94.2841</v>
@@ -16415,7 +16415,7 @@
         </is>
       </c>
       <c r="K57" s="24" t="n">
-        <v>5.2915</v>
+        <v>5.4084</v>
       </c>
       <c r="L57" s="24" t="n">
         <v>47.142</v>
@@ -16438,7 +16438,7 @@
         </is>
       </c>
       <c r="D58" s="29" t="n">
-        <v>100.32</v>
+        <v>103.09</v>
       </c>
       <c r="E58" s="29" t="n">
         <v>1528.051</v>
@@ -16461,7 +16461,7 @@
         </is>
       </c>
       <c r="K58" s="29" t="n">
-        <v>0.0328</v>
+        <v>0.0337</v>
       </c>
       <c r="L58" s="29" t="n">
         <v>2292.0765</v>
@@ -16484,22 +16484,22 @@
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>266.35</v>
+        <v>267.45</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>240.4039</v>
+        <v>240.4034</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>360.6058</v>
+        <v>360.6051</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>552.9289</v>
+        <v>552.9279</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>721.2116</v>
+        <v>721.2103</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>721.2116</v>
+        <v>721.2103</v>
       </c>
       <c r="J59" s="11" t="inlineStr">
         <is>
@@ -16507,10 +16507,10 @@
         </is>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.554</v>
+        <v>0.5563</v>
       </c>
       <c r="L59" s="9" t="n">
-        <v>360.6058</v>
+        <v>360.6051</v>
       </c>
     </row>
     <row r="60">
@@ -16530,7 +16530,7 @@
         </is>
       </c>
       <c r="D60" s="24" t="n">
-        <v>87.83</v>
+        <v>87.93000000000001</v>
       </c>
       <c r="E60" s="24" t="n">
         <v>7.0248</v>
@@ -16553,7 +16553,7 @@
         </is>
       </c>
       <c r="K60" s="24" t="n">
-        <v>6.2514</v>
+        <v>6.2585</v>
       </c>
       <c r="L60" s="24" t="n">
         <v>10.5372</v>
@@ -16576,22 +16576,22 @@
         </is>
       </c>
       <c r="D61" s="24" t="n">
-        <v>1123</v>
+        <v>1121.23</v>
       </c>
       <c r="E61" s="24" t="n">
-        <v>272.3747</v>
+        <v>272.3751</v>
       </c>
       <c r="F61" s="24" t="n">
-        <v>408.5621</v>
+        <v>408.5627</v>
       </c>
       <c r="G61" s="24" t="n">
-        <v>626.4618</v>
+        <v>626.4628</v>
       </c>
       <c r="H61" s="24" t="n">
-        <v>817.1241</v>
+        <v>817.1254</v>
       </c>
       <c r="I61" s="24" t="n">
-        <v>817.1241</v>
+        <v>817.1254</v>
       </c>
       <c r="J61" s="26" t="inlineStr">
         <is>
@@ -16599,10 +16599,10 @@
         </is>
       </c>
       <c r="K61" s="24" t="n">
-        <v>2.0615</v>
+        <v>2.0582</v>
       </c>
       <c r="L61" s="24" t="n">
-        <v>408.5621</v>
+        <v>408.5627</v>
       </c>
     </row>
     <row r="62">
@@ -16622,7 +16622,7 @@
         </is>
       </c>
       <c r="D62" s="24" t="n">
-        <v>492.44</v>
+        <v>493.604</v>
       </c>
       <c r="E62" s="24" t="n">
         <v>41.4473</v>
@@ -16645,7 +16645,7 @@
         </is>
       </c>
       <c r="K62" s="24" t="n">
-        <v>5.9406</v>
+        <v>5.9546</v>
       </c>
       <c r="L62" s="24" t="n">
         <v>62.1709</v>
@@ -16668,7 +16668,7 @@
         </is>
       </c>
       <c r="D63" s="29" t="n">
-        <v>128.56</v>
+        <v>136.31</v>
       </c>
       <c r="E63" s="29" t="n">
         <v>10648.2983</v>
@@ -16691,7 +16691,7 @@
         </is>
       </c>
       <c r="K63" s="29" t="n">
-        <v>0.006</v>
+        <v>0.0064</v>
       </c>
       <c r="L63" s="29" t="n">
         <v>15972.4474</v>
@@ -16714,7 +16714,7 @@
         </is>
       </c>
       <c r="D64" s="24" t="n">
-        <v>977.41</v>
+        <v>973.4450000000001</v>
       </c>
       <c r="E64" s="24" t="n">
         <v>38.2667</v>
@@ -16737,7 +16737,7 @@
         </is>
       </c>
       <c r="K64" s="24" t="n">
-        <v>12.771</v>
+        <v>12.7192</v>
       </c>
       <c r="L64" s="24" t="n">
         <v>57.4</v>
@@ -16760,7 +16760,7 @@
         </is>
       </c>
       <c r="D65" s="24" t="n">
-        <v>218.36</v>
+        <v>219.66</v>
       </c>
       <c r="E65" s="24" t="n">
         <v>23.1383</v>
@@ -16783,7 +16783,7 @@
         </is>
       </c>
       <c r="K65" s="24" t="n">
-        <v>4.7186</v>
+        <v>4.7467</v>
       </c>
       <c r="L65" s="24" t="n">
         <v>34.7074</v>
@@ -16806,7 +16806,7 @@
         </is>
       </c>
       <c r="D66" s="24" t="n">
-        <v>142.97</v>
+        <v>143.925</v>
       </c>
       <c r="E66" s="24" t="n">
         <v>10.1114</v>
@@ -16829,7 +16829,7 @@
         </is>
       </c>
       <c r="K66" s="24" t="n">
-        <v>7.0698</v>
+        <v>7.117</v>
       </c>
       <c r="L66" s="24" t="n">
         <v>15.167</v>
@@ -16852,7 +16852,7 @@
         </is>
       </c>
       <c r="D67" s="24" t="n">
-        <v>34.56</v>
+        <v>34.745</v>
       </c>
       <c r="E67" s="24" t="n">
         <v>2.1808</v>
@@ -16875,7 +16875,7 @@
         </is>
       </c>
       <c r="K67" s="24" t="n">
-        <v>7.9236</v>
+        <v>7.966</v>
       </c>
       <c r="L67" s="24" t="n">
         <v>3.2713</v>
@@ -16898,7 +16898,7 @@
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>188.3</v>
+        <v>189.59</v>
       </c>
       <c r="E68" s="4" t="n">
         <v>71015.83259999999</v>
@@ -16944,7 +16944,7 @@
         </is>
       </c>
       <c r="D69" s="24" t="n">
-        <v>363.56</v>
+        <v>364.38</v>
       </c>
       <c r="E69" s="24" t="n">
         <v>2.2644</v>
@@ -16967,7 +16967,7 @@
         </is>
       </c>
       <c r="K69" s="24" t="n">
-        <v>80.27760000000001</v>
+        <v>80.45869999999999</v>
       </c>
       <c r="L69" s="24" t="n">
         <v>3.3966</v>
@@ -16990,22 +16990,22 @@
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>428.03</v>
+        <v>431.58</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>3154.1183</v>
+        <v>3154.1168</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>4731.1774</v>
+        <v>4731.1752</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>7254.472</v>
+        <v>7254.4686</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>9462.354799999999</v>
+        <v>9462.350399999999</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>9462.354799999999</v>
+        <v>9462.350399999999</v>
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
@@ -17013,10 +17013,10 @@
         </is>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0.0679</v>
+        <v>0.0684</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>4731.1774</v>
+        <v>4731.1752</v>
       </c>
     </row>
     <row r="71">
@@ -17036,22 +17036,22 @@
         </is>
       </c>
       <c r="D71" s="14" t="n">
-        <v>388.28</v>
+        <v>378.85</v>
       </c>
       <c r="E71" s="14" t="n">
-        <v>184.7112</v>
+        <v>184.7121</v>
       </c>
       <c r="F71" s="14" t="n">
-        <v>277.0669</v>
+        <v>277.0682</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>424.8358</v>
+        <v>424.8379</v>
       </c>
       <c r="H71" s="14" t="n">
-        <v>554.1337</v>
+        <v>554.1364</v>
       </c>
       <c r="I71" s="14" t="n">
-        <v>554.1337</v>
+        <v>554.1364</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
@@ -17059,10 +17059,10 @@
         </is>
       </c>
       <c r="K71" s="14" t="n">
-        <v>1.051</v>
+        <v>1.0255</v>
       </c>
       <c r="L71" s="14" t="n">
-        <v>277.0669</v>
+        <v>277.0682</v>
       </c>
     </row>
     <row r="72">
@@ -17082,13 +17082,13 @@
         </is>
       </c>
       <c r="D72" s="24" t="n">
-        <v>367.21</v>
+        <v>369.888</v>
       </c>
       <c r="E72" s="24" t="n">
         <v>27.1298</v>
       </c>
       <c r="F72" s="24" t="n">
-        <v>40.6948</v>
+        <v>40.6947</v>
       </c>
       <c r="G72" s="24" t="n">
         <v>62.3986</v>
@@ -17105,10 +17105,10 @@
         </is>
       </c>
       <c r="K72" s="24" t="n">
-        <v>6.7676</v>
+        <v>6.817</v>
       </c>
       <c r="L72" s="24" t="n">
-        <v>40.6948</v>
+        <v>40.6947</v>
       </c>
     </row>
     <row r="73">
@@ -17128,7 +17128,7 @@
         </is>
       </c>
       <c r="D73" s="24" t="n">
-        <v>105.73</v>
+        <v>105.95</v>
       </c>
       <c r="E73" s="24" t="n">
         <v>5.9158</v>
@@ -17151,7 +17151,7 @@
         </is>
       </c>
       <c r="K73" s="24" t="n">
-        <v>8.936299999999999</v>
+        <v>8.9549</v>
       </c>
       <c r="L73" s="24" t="n">
         <v>8.873699999999999</v>
